--- a/files/ireland-epu-index.xlsx
+++ b/files/ireland-epu-index.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" r:id="R400bcd4ff3c5451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" r:id="Rfd3d6a445aac410b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,7 +334,7 @@
         <x:v>29952</x:v>
       </x:c>
       <x:c r="B2" s="9" t="n">
-        <x:v>79.41577728511994</x:v>
+        <x:v>79.4231462894064</x:v>
       </x:c>
       <x:c r="C2" s="9"/>
     </x:row>
@@ -343,7 +343,7 @@
         <x:v>29983</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>46.68176699245012</x:v>
+        <x:v>46.68609860202226</x:v>
       </x:c>
       <x:c r="C3" s="11"/>
     </x:row>
@@ -352,7 +352,7 @@
         <x:v>30011</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>46.46838951272717</x:v>
+        <x:v>46.4727013229645</x:v>
       </x:c>
       <x:c r="C4" s="11"/>
     </x:row>
@@ -361,7 +361,7 @@
         <x:v>30042</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>80.5160235761302</x:v>
+        <x:v>80.52349467246826</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
     </x:row>
@@ -370,7 +370,7 @@
         <x:v>30072</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>34.13796159377983</x:v>
+        <x:v>34.14112926138839</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
     </x:row>
@@ -379,7 +379,7 @@
         <x:v>30103</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>25.78370266958775</x:v>
+        <x:v>25.78609514400516</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
     </x:row>
@@ -388,7 +388,7 @@
         <x:v>30133</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>47.12485515670111</x:v>
+        <x:v>47.12922788050386</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
     </x:row>
@@ -397,7 +397,7 @@
         <x:v>30164</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>45.94550226678059</x:v>
+        <x:v>45.94976555821614</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
     </x:row>
@@ -406,7 +406,7 @@
         <x:v>30195</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>44.39760566634894</x:v>
+        <x:v>44.40172532817998</x:v>
       </x:c>
       <x:c r="C10" s="11"/>
     </x:row>
@@ -415,7 +415,7 @@
         <x:v>30225</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>38.46352679919969</x:v>
+        <x:v>38.46709583678322</x:v>
       </x:c>
       <x:c r="C11" s="11"/>
     </x:row>
@@ -424,7 +424,7 @@
         <x:v>30256</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>73.08408679231736</x:v>
+        <x:v>73.0908682779019</x:v>
       </x:c>
       <x:c r="C12" s="11"/>
     </x:row>
@@ -433,7 +433,7 @@
         <x:v>30286</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>56.66783001717535</x:v>
+        <x:v>56.67308823533521</x:v>
       </x:c>
       <x:c r="C13" s="11"/>
     </x:row>
@@ -442,7 +442,7 @@
         <x:v>30317</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>45.75139011539633</x:v>
+        <x:v>45.75563539513038</x:v>
       </x:c>
       <x:c r="C14" s="11"/>
     </x:row>
@@ -451,7 +451,7 @@
         <x:v>30348</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>50.30509124822622</x:v>
+        <x:v>50.30975906670903</x:v>
       </x:c>
       <x:c r="C15" s="11"/>
     </x:row>
@@ -460,7 +460,7 @@
         <x:v>30376</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>54.31107016751364</x:v>
+        <x:v>54.31610970150233</x:v>
       </x:c>
       <x:c r="C16" s="11"/>
     </x:row>
@@ -469,7 +469,7 @@
         <x:v>30407</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>48.64659527113625</x:v>
+        <x:v>48.65110919747846</x:v>
       </x:c>
       <x:c r="C17" s="11"/>
     </x:row>
@@ -478,7 +478,7 @@
         <x:v>30437</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>36.50990439581027</x:v>
+        <x:v>36.51329215641891</x:v>
       </x:c>
       <x:c r="C18" s="11"/>
     </x:row>
@@ -487,7 +487,7 @@
         <x:v>30468</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>49.63146974896732</x:v>
+        <x:v>49.63607506198981</x:v>
       </x:c>
       <x:c r="C19" s="11"/>
     </x:row>
@@ -496,7 +496,7 @@
         <x:v>30498</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>33.78864291700626</x:v>
+        <x:v>33.79177817127186</x:v>
       </x:c>
       <x:c r="C20" s="11"/>
     </x:row>
@@ -505,7 +505,7 @@
         <x:v>30529</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>19.59950958358653</x:v>
+        <x:v>19.60132822561298</x:v>
       </x:c>
       <x:c r="C21" s="11"/>
     </x:row>
@@ -514,7 +514,7 @@
         <x:v>30560</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>31.61252492235139</x:v>
+        <x:v>31.61545825423608</x:v>
       </x:c>
       <x:c r="C22" s="11"/>
     </x:row>
@@ -523,7 +523,7 @@
         <x:v>30590</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>14.32427926088208</x:v>
+        <x:v>14.32560841333619</x:v>
       </x:c>
       <x:c r="C23" s="11"/>
     </x:row>
@@ -532,7 +532,7 @@
         <x:v>30621</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>24.40911091613266</x:v>
+        <x:v>24.41137584193353</x:v>
       </x:c>
       <x:c r="C24" s="11"/>
     </x:row>
@@ -541,7 +541,7 @@
         <x:v>30651</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>42.52382841429652</x:v>
+        <x:v>42.52777420799865</x:v>
       </x:c>
       <x:c r="C25" s="11"/>
     </x:row>
@@ -550,7 +550,7 @@
         <x:v>30682</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>11.58898975377897</x:v>
+        <x:v>11.59006509822677</x:v>
       </x:c>
       <x:c r="C26" s="11"/>
     </x:row>
@@ -559,7 +559,7 @@
         <x:v>30713</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>46.44672592787276</x:v>
+        <x:v>46.45103572794216</x:v>
       </x:c>
       <x:c r="C27" s="11"/>
     </x:row>
@@ -568,7 +568,7 @@
         <x:v>30742</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>40.39855662654913</x:v>
+        <x:v>40.40230521589906</x:v>
       </x:c>
       <x:c r="C28" s="11"/>
     </x:row>
@@ -577,7 +577,7 @@
         <x:v>30773</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>46.46838951272717</x:v>
+        <x:v>46.4727013229645</x:v>
       </x:c>
       <x:c r="C29" s="11"/>
     </x:row>
@@ -586,7 +586,7 @@
         <x:v>30803</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>46.58427078333249</x:v>
+        <x:v>46.58859334621381</x:v>
       </x:c>
       <x:c r="C30" s="11"/>
     </x:row>
@@ -595,7 +595,7 @@
         <x:v>30834</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>78.06875870994784</x:v>
+        <x:v>78.07600272413795</x:v>
       </x:c>
       <x:c r="C31" s="11"/>
     </x:row>
@@ -604,7 +604,7 @@
         <x:v>30864</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>11.36997022679711</x:v>
+        <x:v>11.37102524838353</x:v>
       </x:c>
       <x:c r="C32" s="11"/>
     </x:row>
@@ -613,7 +613,7 @@
         <x:v>30895</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>22.55461086554538</x:v>
+        <x:v>22.55670371195235</x:v>
       </x:c>
       <x:c r="C33" s="11"/>
     </x:row>
@@ -622,7 +622,7 @@
         <x:v>30926</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>64.82529447450295</x:v>
+        <x:v>64.83130962525995</x:v>
       </x:c>
       <x:c r="C34" s="11"/>
     </x:row>
@@ -631,7 +631,7 @@
         <x:v>30956</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>50.00212153461366</x:v>
+        <x:v>50.00676124048216</x:v>
       </x:c>
       <x:c r="C35" s="11"/>
     </x:row>
@@ -640,7 +640,7 @@
         <x:v>30987</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>20.08795610841339</x:v>
+        <x:v>20.0898200734809</x:v>
       </x:c>
       <x:c r="C36" s="11"/>
     </x:row>
@@ -649,7 +649,7 @@
         <x:v>31017</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>70.07049170153216</x:v>
+        <x:v>70.07699355508514</x:v>
       </x:c>
       <x:c r="C37" s="11"/>
     </x:row>
@@ -658,7 +658,7 @@
         <x:v>31048</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>29.5667815513079</x:v>
+        <x:v>29.56952505829651</x:v>
       </x:c>
       <x:c r="C38" s="11"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>31079</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>15.6098375399986</x:v>
+        <x:v>15.61128597963711</x:v>
       </x:c>
       <x:c r="C39" s="11"/>
     </x:row>
@@ -676,7 +676,7 @@
         <x:v>31107</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>41.58453423294392</x:v>
+        <x:v>41.58839286936969</x:v>
       </x:c>
       <x:c r="C40" s="11"/>
     </x:row>
@@ -685,7 +685,7 @@
         <x:v>31138</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>41.86529041711413</x:v>
+        <x:v>41.86917510495682</x:v>
       </x:c>
       <x:c r="C41" s="11"/>
     </x:row>
@@ -694,7 +694,7 @@
         <x:v>31168</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>30.06231420300579</x:v>
+        <x:v>30.06510369055846</x:v>
       </x:c>
       <x:c r="C42" s="11"/>
     </x:row>
@@ -703,7 +703,7 @@
         <x:v>31199</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>23.71016752229625</x:v>
+        <x:v>23.71236759301365</x:v>
       </x:c>
       <x:c r="C43" s="11"/>
     </x:row>
@@ -712,7 +712,7 @@
         <x:v>31229</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>22.34217507967506</x:v>
+        <x:v>22.34424821412717</x:v>
       </x:c>
       <x:c r="C44" s="11"/>
     </x:row>
@@ -721,7 +721,7 @@
         <x:v>31260</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>37.99703551307668</x:v>
+        <x:v>38.00056126484969</x:v>
       </x:c>
       <x:c r="C45" s="11"/>
     </x:row>
@@ -730,7 +730,7 @@
         <x:v>31291</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>20.82355720995047</x:v>
+        <x:v>20.82548943157677</x:v>
       </x:c>
       <x:c r="C46" s="11"/>
     </x:row>
@@ -739,7 +739,7 @@
         <x:v>31321</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>24.42443004120749</x:v>
+        <x:v>24.42669638847274</x:v>
       </x:c>
       <x:c r="C47" s="11"/>
     </x:row>
@@ -748,7 +748,7 @@
         <x:v>31352</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>22.47280278152678</x:v>
+        <x:v>22.47488803694689</x:v>
       </x:c>
       <x:c r="C48" s="11"/>
     </x:row>
@@ -757,7 +757,7 @@
         <x:v>31382</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>20.76107091674732</x:v>
+        <x:v>20.76299734025921</x:v>
       </x:c>
       <x:c r="C49" s="11"/>
     </x:row>
@@ -766,7 +766,7 @@
         <x:v>31413</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>59.93035798561539</x:v>
+        <x:v>59.93591893433342</x:v>
       </x:c>
       <x:c r="C50" s="11"/>
     </x:row>
@@ -775,7 +775,7 @@
         <x:v>31444</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>37.65971087172808</x:v>
+        <x:v>37.66320532308683</x:v>
       </x:c>
       <x:c r="C51" s="11"/>
     </x:row>
@@ -784,7 +784,7 @@
         <x:v>31472</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>42.48900849338411</x:v>
+        <x:v>42.4929510561395</x:v>
       </x:c>
       <x:c r="C52" s="11"/>
     </x:row>
@@ -793,7 +793,7 @@
         <x:v>31503</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>41.56371594296498</x:v>
+        <x:v>41.56757264765785</x:v>
       </x:c>
       <x:c r="C53" s="11"/>
     </x:row>
@@ -802,7 +802,7 @@
         <x:v>31533</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>30.24169108647615</x:v>
+        <x:v>30.24449721844217</x:v>
       </x:c>
       <x:c r="C54" s="11"/>
     </x:row>
@@ -811,7 +811,7 @@
         <x:v>31564</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>26.22016251770861</x:v>
+        <x:v>26.22259549131397</x:v>
       </x:c>
       <x:c r="C55" s="11"/>
     </x:row>
@@ -820,7 +820,7 @@
         <x:v>31594</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>31.81790595148411</x:v>
+        <x:v>31.82085834071152</x:v>
       </x:c>
       <x:c r="C56" s="11"/>
     </x:row>
@@ -829,7 +829,7 @@
         <x:v>31625</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>103.88875983439</x:v>
+        <x:v>103.8983996911377</x:v>
       </x:c>
       <x:c r="C57" s="11"/>
     </x:row>
@@ -838,7 +838,7 @@
         <x:v>31656</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>89.22996218827954</x:v>
+        <x:v>89.23824185255185</x:v>
       </x:c>
       <x:c r="C58" s="11"/>
     </x:row>
@@ -847,7 +847,7 @@
         <x:v>31686</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>45.42762234409747</x:v>
+        <x:v>45.43183758136167</x:v>
       </x:c>
       <x:c r="C59" s="11"/>
     </x:row>
@@ -856,7 +856,7 @@
         <x:v>31717</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>59.00425288371653</x:v>
+        <x:v>59.00972789897525</x:v>
       </x:c>
       <x:c r="C60" s="11"/>
     </x:row>
@@ -865,7 +865,7 @@
         <x:v>31747</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>63.9399166912881</x:v>
+        <x:v>63.94584968768101</x:v>
       </x:c>
       <x:c r="C61" s="11"/>
     </x:row>
@@ -874,7 +874,7 @@
         <x:v>31778</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>48.40708106793553</x:v>
+        <x:v>48.41157276971166</x:v>
       </x:c>
       <x:c r="C62" s="11"/>
     </x:row>
@@ -883,7 +883,7 @@
         <x:v>31809</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>70.87950136261173</x:v>
+        <x:v>70.88607828431694</x:v>
       </x:c>
       <x:c r="C63" s="11"/>
     </x:row>
@@ -892,7 +892,7 @@
         <x:v>31837</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>53.13845532262707</x:v>
+        <x:v>53.14338604947297</x:v>
       </x:c>
       <x:c r="C64" s="11"/>
     </x:row>
@@ -901,7 +901,7 @@
         <x:v>31868</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
-        <x:v>69.99389064519733</x:v>
+        <x:v>70.00038539092448</x:v>
       </x:c>
       <x:c r="C65" s="11"/>
     </x:row>
@@ -910,7 +910,7 @@
         <x:v>31898</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
-        <x:v>61.25964237703233</x:v>
+        <x:v>61.2653266702886</x:v>
       </x:c>
       <x:c r="C66" s="11"/>
     </x:row>
@@ -919,7 +919,7 @@
         <x:v>31929</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>68.42598016159826</x:v>
+        <x:v>68.43232942062906</x:v>
       </x:c>
       <x:c r="C67" s="11"/>
     </x:row>
@@ -928,7 +928,7 @@
         <x:v>31959</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>26.6032820418074</x:v>
+        <x:v>26.60575056514245</x:v>
       </x:c>
       <x:c r="C68" s="11"/>
     </x:row>
@@ -937,7 +937,7 @@
         <x:v>31990</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>27.98042686575645</x:v>
+        <x:v>27.98302317460791</x:v>
       </x:c>
       <x:c r="C69" s="11"/>
     </x:row>
@@ -946,7 +946,7 @@
         <x:v>32021</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>18.66955758850293</x:v>
+        <x:v>18.67128994011616</x:v>
       </x:c>
       <x:c r="C70" s="11"/>
     </x:row>
@@ -955,7 +955,7 @@
         <x:v>32051</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>37.67802250786138</x:v>
+        <x:v>37.68151865836015</x:v>
       </x:c>
       <x:c r="C71" s="11"/>
     </x:row>
@@ -964,7 +964,7 @@
         <x:v>32082</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>34.65915184711998</x:v>
+        <x:v>34.66236787606609</x:v>
       </x:c>
       <x:c r="C72" s="11"/>
     </x:row>
@@ -973,7 +973,7 @@
         <x:v>32112</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>35.25914040037055</x:v>
+        <x:v>35.26241210236264</x:v>
       </x:c>
       <x:c r="C73" s="11"/>
     </x:row>
@@ -982,7 +982,7 @@
         <x:v>32143</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>67.97777505136943</x:v>
+        <x:v>67.98408272136729</x:v>
       </x:c>
       <x:c r="C74" s="11"/>
     </x:row>
@@ -991,7 +991,7 @@
         <x:v>32174</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>27.88269834634355</x:v>
+        <x:v>27.88528558694808</x:v>
       </x:c>
       <x:c r="C75" s="11"/>
     </x:row>
@@ -1000,7 +1000,7 @@
         <x:v>32203</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>35.67324087485213</x:v>
+        <x:v>35.67655100130187</x:v>
       </x:c>
       <x:c r="C76" s="11"/>
     </x:row>
@@ -1009,7 +1009,7 @@
         <x:v>32234</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>42.92205747212022</x:v>
+        <x:v>42.92604021756839</x:v>
       </x:c>
       <x:c r="C77" s="11"/>
     </x:row>
@@ -1018,7 +1018,7 @@
         <x:v>32264</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>33.21826724302715</x:v>
+        <x:v>33.22134957203117</x:v>
       </x:c>
       <x:c r="C78" s="11"/>
     </x:row>
@@ -1027,7 +1027,7 @@
         <x:v>32295</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>11.81325022710196</x:v>
+        <x:v>11.81434638071949</x:v>
       </x:c>
       <x:c r="C79" s="11"/>
     </x:row>
@@ -1036,7 +1036,7 @@
         <x:v>32325</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>50.67903576808551</x:v>
+        <x:v>50.68373828494771</x:v>
       </x:c>
       <x:c r="C80" s="11"/>
     </x:row>
@@ -1045,7 +1045,7 @@
         <x:v>32356</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
-        <x:v>11.89789661737927</x:v>
+        <x:v>11.89900062535061</x:v>
       </x:c>
       <x:c r="C81" s="11"/>
     </x:row>
@@ -1054,7 +1054,7 @@
         <x:v>32387</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
-        <x:v>11.31727407252897</x:v>
+        <x:v>11.31832420442974</x:v>
       </x:c>
       <x:c r="C82" s="11"/>
     </x:row>
@@ -1063,7 +1063,7 @@
         <x:v>32417</x:v>
       </x:c>
       <x:c r="B83" s="11" t="n">
-        <x:v>49.20787256761056</x:v>
+        <x:v>49.21243857497426</x:v>
       </x:c>
       <x:c r="C83" s="11"/>
     </x:row>
@@ -1072,7 +1072,7 @@
         <x:v>32448</x:v>
       </x:c>
       <x:c r="B84" s="11" t="n">
-        <x:v>49.39524190627828</x:v>
+        <x:v>49.39982529967669</x:v>
       </x:c>
       <x:c r="C84" s="11"/>
     </x:row>
@@ -1081,7 +1081,7 @@
         <x:v>32478</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>45.89752477669857</x:v>
+        <x:v>45.90178361629417</x:v>
       </x:c>
       <x:c r="C85" s="11"/>
     </x:row>
@@ -1090,7 +1090,7 @@
         <x:v>32509</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>60.90015661221646</x:v>
+        <x:v>60.90580754872382</x:v>
       </x:c>
       <x:c r="C86" s="11"/>
     </x:row>
@@ -1099,7 +1099,7 @@
         <x:v>32540</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
-        <x:v>38.48135462158635</x:v>
+        <x:v>38.48492531341673</x:v>
       </x:c>
       <x:c r="C87" s="11"/>
     </x:row>
@@ -1108,7 +1108,7 @@
         <x:v>32568</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>33.5132626195126</x:v>
+        <x:v>33.51637232119077</x:v>
       </x:c>
       <x:c r="C88" s="11"/>
     </x:row>
@@ -1117,7 +1117,7 @@
         <x:v>32599</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>67.42570865950668</x:v>
+        <x:v>67.43196510316453</x:v>
       </x:c>
       <x:c r="C89" s="11"/>
     </x:row>
@@ -1126,7 +1126,7 @@
         <x:v>32629</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>47.8736355307953</x:v>
+        <x:v>47.8780777340639</x:v>
       </x:c>
       <x:c r="C90" s="11"/>
     </x:row>
@@ -1135,7 +1135,7 @@
         <x:v>32660</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
-        <x:v>65.33855398431731</x:v>
+        <x:v>65.34461676051671</x:v>
       </x:c>
       <x:c r="C91" s="11"/>
     </x:row>
@@ -1144,7 +1144,7 @@
         <x:v>32690</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
-        <x:v>44.42136040453319</x:v>
+        <x:v>44.42548227057067</x:v>
       </x:c>
       <x:c r="C92" s="11"/>
     </x:row>
@@ -1153,7 +1153,7 @@
         <x:v>32721</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
-        <x:v>28.49516838140875</x:v>
+        <x:v>28.49781245321821</x:v>
       </x:c>
       <x:c r="C93" s="11"/>
     </x:row>
@@ -1162,7 +1162,7 @@
         <x:v>32752</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
-        <x:v>18.0224723435758</x:v>
+        <x:v>18.02414465203254</x:v>
       </x:c>
       <x:c r="C94" s="11"/>
     </x:row>
@@ -1171,7 +1171,7 @@
         <x:v>32782</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
-        <x:v>72.32014163420953</x:v>
+        <x:v>72.32685223318516</x:v>
       </x:c>
       <x:c r="C95" s="11"/>
     </x:row>
@@ -1180,7 +1180,7 @@
         <x:v>32813</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
-        <x:v>83.06505512363435</x:v>
+        <x:v>83.07276274506911</x:v>
       </x:c>
       <x:c r="C96" s="11"/>
     </x:row>
@@ -1189,7 +1189,7 @@
         <x:v>32843</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
-        <x:v>45.83136770415266</x:v>
+        <x:v>45.83562040502158</x:v>
       </x:c>
       <x:c r="C97" s="11"/>
     </x:row>
@@ -1198,7 +1198,7 @@
         <x:v>32874</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
-        <x:v>26.61692824957442</x:v>
+        <x:v>26.61939803914355</x:v>
       </x:c>
       <x:c r="C98" s="11"/>
     </x:row>
@@ -1207,7 +1207,7 @@
         <x:v>32905</x:v>
       </x:c>
       <x:c r="B99" s="11" t="n">
-        <x:v>46.93540850280481</x:v>
+        <x:v>46.9397636478184</x:v>
       </x:c>
       <x:c r="C99" s="11"/>
     </x:row>
@@ -1216,7 +1216,7 @@
         <x:v>32933</x:v>
       </x:c>
       <x:c r="B100" s="11" t="n">
-        <x:v>71.53676245353371</x:v>
+        <x:v>71.543400362614</x:v>
       </x:c>
       <x:c r="C100" s="11"/>
     </x:row>
@@ -1225,7 +1225,7 @@
         <x:v>32964</x:v>
       </x:c>
       <x:c r="B101" s="11" t="n">
-        <x:v>81.60132802197526</x:v>
+        <x:v>81.60889982390846</x:v>
       </x:c>
       <x:c r="C101" s="11"/>
     </x:row>
@@ -1234,7 +1234,7 @@
         <x:v>32994</x:v>
       </x:c>
       <x:c r="B102" s="11" t="n">
-        <x:v>62.12785427493579</x:v>
+        <x:v>62.13361912973053</x:v>
       </x:c>
       <x:c r="C102" s="11"/>
     </x:row>
@@ -1243,7 +1243,7 @@
         <x:v>33025</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>43.73751483052288</x:v>
+        <x:v>43.7415732424063</x:v>
       </x:c>
       <x:c r="C103" s="11"/>
     </x:row>
@@ -1252,7 +1252,7 @@
         <x:v>33055</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>63.26405074630876</x:v>
+        <x:v>63.26992102897885</x:v>
       </x:c>
       <x:c r="C104" s="11"/>
     </x:row>
@@ -1261,7 +1261,7 @@
         <x:v>33086</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>100.7309661127317</x:v>
+        <x:v>100.7403129572309</x:v>
       </x:c>
       <x:c r="C105" s="11"/>
     </x:row>
@@ -1270,7 +1270,7 @@
         <x:v>33117</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>111.0236996470614</x:v>
+        <x:v>111.0340015561602</x:v>
       </x:c>
       <x:c r="C106" s="11"/>
     </x:row>
@@ -1279,7 +1279,7 @@
         <x:v>33147</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>135.3870789951008</x:v>
+        <x:v>135.3996415865599</x:v>
       </x:c>
       <x:c r="C107" s="11"/>
     </x:row>
@@ -1288,7 +1288,7 @@
         <x:v>33178</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
-        <x:v>94.9582789143618</x:v>
+        <x:v>94.96709011017546</x:v>
       </x:c>
       <x:c r="C108" s="11"/>
     </x:row>
@@ -1297,7 +1297,7 @@
         <x:v>33208</x:v>
       </x:c>
       <x:c r="B109" s="11" t="n">
-        <x:v>88.67665964867561</x:v>
+        <x:v>88.68488797190555</x:v>
       </x:c>
       <x:c r="C109" s="11"/>
     </x:row>
@@ -1306,7 +1306,7 @@
         <x:v>33239</x:v>
       </x:c>
       <x:c r="B110" s="11" t="n">
-        <x:v>121.8544852192845</x:v>
+        <x:v>121.8657921189284</x:v>
       </x:c>
       <x:c r="C110" s="11"/>
     </x:row>
@@ -1315,7 +1315,7 @@
         <x:v>33270</x:v>
       </x:c>
       <x:c r="B111" s="11" t="n">
-        <x:v>129.5892652384067</x:v>
+        <x:v>129.6012898496825</x:v>
       </x:c>
       <x:c r="C111" s="11"/>
     </x:row>
@@ -1324,7 +1324,7 @@
         <x:v>33298</x:v>
       </x:c>
       <x:c r="B112" s="11" t="n">
-        <x:v>84.76112567235585</x:v>
+        <x:v>84.76899067248247</x:v>
       </x:c>
       <x:c r="C112" s="11"/>
     </x:row>
@@ -1333,7 +1333,7 @@
         <x:v>33329</x:v>
       </x:c>
       <x:c r="B113" s="11" t="n">
-        <x:v>65.63124315895061</x:v>
+        <x:v>65.63733309383127</x:v>
       </x:c>
       <x:c r="C113" s="11"/>
     </x:row>
@@ -1342,7 +1342,7 @@
         <x:v>33359</x:v>
       </x:c>
       <x:c r="B114" s="11" t="n">
-        <x:v>59.04181203496238</x:v>
+        <x:v>59.04729053534151</x:v>
       </x:c>
       <x:c r="C114" s="11"/>
     </x:row>
@@ -1351,7 +1351,7 @@
         <x:v>33390</x:v>
       </x:c>
       <x:c r="B115" s="11" t="n">
-        <x:v>54.88069975943451</x:v>
+        <x:v>54.88579214945569</x:v>
       </x:c>
       <x:c r="C115" s="11"/>
     </x:row>
@@ -1360,7 +1360,7 @@
         <x:v>33420</x:v>
       </x:c>
       <x:c r="B116" s="11" t="n">
-        <x:v>60.65746204548339</x:v>
+        <x:v>60.66309046231817</x:v>
       </x:c>
       <x:c r="C116" s="11"/>
     </x:row>
@@ -1369,7 +1369,7 @@
         <x:v>33451</x:v>
       </x:c>
       <x:c r="B117" s="11" t="n">
-        <x:v>96.84867027829985</x:v>
+        <x:v>96.85765688386887</x:v>
       </x:c>
       <x:c r="C117" s="11"/>
     </x:row>
@@ -1378,7 +1378,7 @@
         <x:v>33482</x:v>
       </x:c>
       <x:c r="B118" s="11" t="n">
-        <x:v>56.19823280420072</x:v>
+        <x:v>56.20344744835057</x:v>
       </x:c>
       <x:c r="C118" s="11"/>
     </x:row>
@@ -1387,7 +1387,7 @@
         <x:v>33512</x:v>
       </x:c>
       <x:c r="B119" s="11" t="n">
-        <x:v>94.29133741745888</x:v>
+        <x:v>94.30008672765085</x:v>
       </x:c>
       <x:c r="C119" s="11"/>
     </x:row>
@@ -1396,7 +1396,7 @@
         <x:v>33543</x:v>
       </x:c>
       <x:c r="B120" s="11" t="n">
-        <x:v>132.2367523510329</x:v>
+        <x:v>132.2490226231151</x:v>
       </x:c>
       <x:c r="C120" s="11"/>
     </x:row>
@@ -1405,7 +1405,7 @@
         <x:v>33573</x:v>
       </x:c>
       <x:c r="B121" s="11" t="n">
-        <x:v>133.1280974572592</x:v>
+        <x:v>133.1404504374143</x:v>
       </x:c>
       <x:c r="C121" s="11"/>
     </x:row>
@@ -1414,7 +1414,7 @@
         <x:v>33604</x:v>
       </x:c>
       <x:c r="B122" s="11" t="n">
-        <x:v>105.8405078720731</x:v>
+        <x:v>105.850328831873</x:v>
       </x:c>
       <x:c r="C122" s="11"/>
     </x:row>
@@ -1423,7 +1423,7 @@
         <x:v>33635</x:v>
       </x:c>
       <x:c r="B123" s="11" t="n">
-        <x:v>58.4074410691224</x:v>
+        <x:v>58.41286070610528</x:v>
       </x:c>
       <x:c r="C123" s="11"/>
     </x:row>
@@ -1432,7 +1432,7 @@
         <x:v>33664</x:v>
       </x:c>
       <x:c r="B124" s="11" t="n">
-        <x:v>62.96020419317938</x:v>
+        <x:v>62.96604628187303</x:v>
       </x:c>
       <x:c r="C124" s="11"/>
     </x:row>
@@ -1441,7 +1441,7 @@
         <x:v>33695</x:v>
       </x:c>
       <x:c r="B125" s="11" t="n">
-        <x:v>95.36261584646765</x:v>
+        <x:v>95.37146456077812</x:v>
       </x:c>
       <x:c r="C125" s="11"/>
     </x:row>
@@ -1450,7 +1450,7 @@
         <x:v>33725</x:v>
       </x:c>
       <x:c r="B126" s="11" t="n">
-        <x:v>81.07765878522709</x:v>
+        <x:v>81.08518199579744</x:v>
       </x:c>
       <x:c r="C126" s="11"/>
     </x:row>
@@ -1459,7 +1459,7 @@
         <x:v>33756</x:v>
       </x:c>
       <x:c r="B127" s="11" t="n">
-        <x:v>177.2540771679235</x:v>
+        <x:v>177.2705246056883</x:v>
       </x:c>
       <x:c r="C127" s="11"/>
     </x:row>
@@ -1468,7 +1468,7 @@
         <x:v>33786</x:v>
       </x:c>
       <x:c r="B128" s="11" t="n">
-        <x:v>53.09767369920218</x:v>
+        <x:v>53.10260064191389</x:v>
       </x:c>
       <x:c r="C128" s="11"/>
     </x:row>
@@ -1477,7 +1477,7 @@
         <x:v>33817</x:v>
       </x:c>
       <x:c r="B129" s="11" t="n">
-        <x:v>69.1368853405315</x:v>
+        <x:v>69.14330056458198</x:v>
       </x:c>
       <x:c r="C129" s="11"/>
     </x:row>
@@ -1486,7 +1486,7 @@
         <x:v>33848</x:v>
       </x:c>
       <x:c r="B130" s="11" t="n">
-        <x:v>165.4679075158396</x:v>
+        <x:v>165.4832613127984</x:v>
       </x:c>
       <x:c r="C130" s="11"/>
     </x:row>
@@ -1495,7 +1495,7 @@
         <x:v>33878</x:v>
       </x:c>
       <x:c r="B131" s="11" t="n">
-        <x:v>149.1843960397779</x:v>
+        <x:v>149.1982388867722</x:v>
       </x:c>
       <x:c r="C131" s="11"/>
     </x:row>
@@ -1504,7 +1504,7 @@
         <x:v>33909</x:v>
       </x:c>
       <x:c r="B132" s="11" t="n">
-        <x:v>124.1437535943114</x:v>
+        <x:v>124.1552729155804</x:v>
       </x:c>
       <x:c r="C132" s="11"/>
     </x:row>
@@ -1513,7 +1513,7 @@
         <x:v>33939</x:v>
       </x:c>
       <x:c r="B133" s="11" t="n">
-        <x:v>184.931850646388</x:v>
+        <x:v>184.9490105061375</x:v>
       </x:c>
       <x:c r="C133" s="11"/>
     </x:row>
@@ -1522,7 +1522,7 @@
         <x:v>33970</x:v>
       </x:c>
       <x:c r="B134" s="11" t="n">
-        <x:v>150.8572779001318</x:v>
+        <x:v>150.8712759741354</x:v>
       </x:c>
       <x:c r="C134" s="11"/>
     </x:row>
@@ -1531,7 +1531,7 @@
         <x:v>34001</x:v>
       </x:c>
       <x:c r="B135" s="11" t="n">
-        <x:v>139.6617227936003</x:v>
+        <x:v>139.6746820300279</x:v>
       </x:c>
       <x:c r="C135" s="11"/>
     </x:row>
@@ -1540,7 +1540,7 @@
         <x:v>34029</x:v>
       </x:c>
       <x:c r="B136" s="11" t="n">
-        <x:v>53.43715249693576</x:v>
+        <x:v>53.4421109399463</x:v>
       </x:c>
       <x:c r="C136" s="11"/>
     </x:row>
@@ -1549,7 +1549,7 @@
         <x:v>34060</x:v>
       </x:c>
       <x:c r="B137" s="11" t="n">
-        <x:v>42.56525126689184</x:v>
+        <x:v>42.56920090422793</x:v>
       </x:c>
       <x:c r="C137" s="11"/>
     </x:row>
@@ -1558,7 +1558,7 @@
         <x:v>34090</x:v>
       </x:c>
       <x:c r="B138" s="11" t="n">
-        <x:v>60.44982922534925</x:v>
+        <x:v>60.45543837589723</x:v>
       </x:c>
       <x:c r="C138" s="11"/>
     </x:row>
@@ -1567,7 +1567,7 @@
         <x:v>34121</x:v>
       </x:c>
       <x:c r="B139" s="11" t="n">
-        <x:v>59.98809436132409</x:v>
+        <x:v>59.99366066741082</x:v>
       </x:c>
       <x:c r="C139" s="11"/>
     </x:row>
@@ -1576,7 +1576,7 @@
         <x:v>34151</x:v>
       </x:c>
       <x:c r="B140" s="11" t="n">
-        <x:v>77.37033045111133</x:v>
+        <x:v>77.37750965801743</x:v>
       </x:c>
       <x:c r="C140" s="11"/>
     </x:row>
@@ -1585,7 +1585,7 @@
         <x:v>34182</x:v>
       </x:c>
       <x:c r="B141" s="11" t="n">
-        <x:v>86.50403800767549</x:v>
+        <x:v>86.51206473295183</x:v>
       </x:c>
       <x:c r="C141" s="11"/>
     </x:row>
@@ -1594,7 +1594,7 @@
         <x:v>34213</x:v>
       </x:c>
       <x:c r="B142" s="11" t="n">
-        <x:v>62.76076222165311</x:v>
+        <x:v>62.76658580409028</x:v>
       </x:c>
       <x:c r="C142" s="11"/>
     </x:row>
@@ -1603,7 +1603,7 @@
         <x:v>34243</x:v>
       </x:c>
       <x:c r="B143" s="11" t="n">
-        <x:v>55.0658194213102</x:v>
+        <x:v>55.07092898861816</x:v>
       </x:c>
       <x:c r="C143" s="11"/>
     </x:row>
@@ -1612,7 +1612,7 @@
         <x:v>34274</x:v>
       </x:c>
       <x:c r="B144" s="11" t="n">
-        <x:v>25.60347119533487</x:v>
+        <x:v>25.60584694604129</x:v>
       </x:c>
       <x:c r="C144" s="11"/>
     </x:row>
@@ -1621,7 +1621,7 @@
         <x:v>34304</x:v>
       </x:c>
       <x:c r="B145" s="11" t="n">
-        <x:v>60.3018031639109</x:v>
+        <x:v>60.30739857909397</x:v>
       </x:c>
       <x:c r="C145" s="11"/>
     </x:row>
@@ -1630,7 +1630,7 @@
         <x:v>34335</x:v>
       </x:c>
       <x:c r="B146" s="11" t="n">
-        <x:v>46.38656788687516</x:v>
+        <x:v>46.39087210486908</x:v>
       </x:c>
       <x:c r="C146" s="11"/>
     </x:row>
@@ -1639,7 +1639,7 @@
         <x:v>34366</x:v>
       </x:c>
       <x:c r="B147" s="11" t="n">
-        <x:v>42.43767418944228</x:v>
+        <x:v>42.44161198887835</x:v>
       </x:c>
       <x:c r="C147" s="11"/>
     </x:row>
@@ -1648,7 +1648,7 @@
         <x:v>34394</x:v>
       </x:c>
       <x:c r="B148" s="11" t="n">
-        <x:v>28.84263421784699</x:v>
+        <x:v>28.84531053107403</x:v>
       </x:c>
       <x:c r="C148" s="11"/>
     </x:row>
@@ -1657,7 +1657,7 @@
         <x:v>34425</x:v>
       </x:c>
       <x:c r="B149" s="11" t="n">
-        <x:v>40.34541211153904</x:v>
+        <x:v>40.34915576959985</x:v>
       </x:c>
       <x:c r="C149" s="11"/>
     </x:row>
@@ -1666,7 +1666,7 @@
         <x:v>34455</x:v>
       </x:c>
       <x:c r="B150" s="11" t="n">
-        <x:v>53.58661096992635</x:v>
+        <x:v>53.59158328121553</x:v>
       </x:c>
       <x:c r="C150" s="11"/>
     </x:row>
@@ -1675,7 +1675,7 @@
         <x:v>34486</x:v>
       </x:c>
       <x:c r="B151" s="11" t="n">
-        <x:v>42.1439200995292</x:v>
+        <x:v>42.14783064147034</x:v>
       </x:c>
       <x:c r="C151" s="11"/>
     </x:row>
@@ -1684,7 +1684,7 @@
         <x:v>34516</x:v>
       </x:c>
       <x:c r="B152" s="11" t="n">
-        <x:v>42.21248860894475</x:v>
+        <x:v>42.21640551337023</x:v>
       </x:c>
       <x:c r="C152" s="11"/>
     </x:row>
@@ -1693,7 +1693,7 @@
         <x:v>34547</x:v>
       </x:c>
       <x:c r="B153" s="11" t="n">
-        <x:v>44.51186070988233</x:v>
+        <x:v>44.51599097345945</x:v>
       </x:c>
       <x:c r="C153" s="11"/>
     </x:row>
@@ -1702,7 +1702,7 @@
         <x:v>34578</x:v>
       </x:c>
       <x:c r="B154" s="11" t="n">
-        <x:v>52.03061787930177</x:v>
+        <x:v>52.03544580971165</x:v>
       </x:c>
       <x:c r="C154" s="11"/>
     </x:row>
@@ -1711,7 +1711,7 @@
         <x:v>34608</x:v>
       </x:c>
       <x:c r="B155" s="11" t="n">
-        <x:v>23.42650186119428</x:v>
+        <x:v>23.42867561052386</x:v>
       </x:c>
       <x:c r="C155" s="11"/>
     </x:row>
@@ -1720,7 +1720,7 @@
         <x:v>34639</x:v>
       </x:c>
       <x:c r="B156" s="11" t="n">
-        <x:v>18.53865724278147</x:v>
+        <x:v>18.54037744812803</x:v>
       </x:c>
       <x:c r="C156" s="11"/>
     </x:row>
@@ -1729,7 +1729,7 @@
         <x:v>34669</x:v>
       </x:c>
       <x:c r="B157" s="11" t="n">
-        <x:v>99.18663098429607</x:v>
+        <x:v>99.19583452966035</x:v>
       </x:c>
       <x:c r="C157" s="11"/>
     </x:row>
@@ -1738,7 +1738,7 @@
         <x:v>34700</x:v>
       </x:c>
       <x:c r="B158" s="11" t="n">
-        <x:v>38.22445791716047</x:v>
+        <x:v>38.22800477149934</x:v>
       </x:c>
       <x:c r="C158" s="11"/>
     </x:row>
@@ -1747,7 +1747,7 @@
         <x:v>34731</x:v>
       </x:c>
       <x:c r="B159" s="11" t="n">
-        <x:v>65.51730002846634</x:v>
+        <x:v>65.5233793905434</x:v>
       </x:c>
       <x:c r="C159" s="11"/>
     </x:row>
@@ -1756,7 +1756,7 @@
         <x:v>34759</x:v>
       </x:c>
       <x:c r="B160" s="11" t="n">
-        <x:v>62.11678689317098</x:v>
+        <x:v>62.12255072102138</x:v>
       </x:c>
       <x:c r="C160" s="11"/>
     </x:row>
@@ -1765,7 +1765,7 @@
         <x:v>34790</x:v>
       </x:c>
       <x:c r="B161" s="11" t="n">
-        <x:v>16.41105408105802</x:v>
+        <x:v>16.41257686572378</x:v>
       </x:c>
       <x:c r="C161" s="11"/>
     </x:row>
@@ -1774,7 +1774,7 @@
         <x:v>34820</x:v>
       </x:c>
       <x:c r="B162" s="11" t="n">
-        <x:v>21.00089104453774</x:v>
+        <x:v>21.00283972100251</x:v>
       </x:c>
       <x:c r="C162" s="11"/>
     </x:row>
@@ -1783,7 +1783,7 @@
         <x:v>34851</x:v>
       </x:c>
       <x:c r="B163" s="11" t="n">
-        <x:v>21.82073238963219</x:v>
+        <x:v>21.82275713932312</x:v>
       </x:c>
       <x:c r="C163" s="11"/>
     </x:row>
@@ -1792,7 +1792,7 @@
         <x:v>34881</x:v>
       </x:c>
       <x:c r="B164" s="11" t="n">
-        <x:v>12.88118368784742</x:v>
+        <x:v>12.88237893520323</x:v>
       </x:c>
       <x:c r="C164" s="11"/>
     </x:row>
@@ -1801,7 +1801,7 @@
         <x:v>34912</x:v>
       </x:c>
       <x:c r="B165" s="11" t="n">
-        <x:v>11.54601185741784</x:v>
+        <x:v>11.54708321393889</x:v>
       </x:c>
       <x:c r="C165" s="11"/>
     </x:row>
@@ -1810,7 +1810,7 @@
         <x:v>34943</x:v>
       </x:c>
       <x:c r="B166" s="11" t="n">
-        <x:v>32.01969932141981</x:v>
+        <x:v>32.02267043509038</x:v>
       </x:c>
       <x:c r="C166" s="11"/>
     </x:row>
@@ -1819,7 +1819,7 @@
         <x:v>34973</x:v>
       </x:c>
       <x:c r="B167" s="11" t="n">
-        <x:v>29.55625581917855</x:v>
+        <x:v>29.55899834948259</x:v>
       </x:c>
       <x:c r="C167" s="11"/>
     </x:row>
@@ -1828,7 +1828,7 @@
         <x:v>35004</x:v>
       </x:c>
       <x:c r="B168" s="11" t="n">
-        <x:v>28.76269620511782</x:v>
+        <x:v>28.76536510088225</x:v>
       </x:c>
       <x:c r="C168" s="11"/>
     </x:row>
@@ -1837,7 +1837,7 @@
         <x:v>35034</x:v>
       </x:c>
       <x:c r="B169" s="11" t="n">
-        <x:v>54.85392324399994</x:v>
+        <x:v>54.85901314942343</x:v>
       </x:c>
       <x:c r="C169" s="11"/>
     </x:row>
@@ -1846,7 +1846,7 @@
         <x:v>35065</x:v>
       </x:c>
       <x:c r="B170" s="11" t="n">
-        <x:v>51.08092038314553</x:v>
+        <x:v>51.0856601909536</x:v>
       </x:c>
       <x:c r="C170" s="11"/>
     </x:row>
@@ -1855,7 +1855,7 @@
         <x:v>35096</x:v>
       </x:c>
       <x:c r="B171" s="11" t="n">
-        <x:v>28.62880089519743</x:v>
+        <x:v>28.63145736679192</x:v>
       </x:c>
       <x:c r="C171" s="11"/>
     </x:row>
@@ -1864,7 +1864,7 @@
         <x:v>35125</x:v>
       </x:c>
       <x:c r="B172" s="11" t="n">
-        <x:v>32.90521857339495</x:v>
+        <x:v>32.9082718545565</x:v>
       </x:c>
       <x:c r="C172" s="11"/>
     </x:row>
@@ -1873,7 +1873,7 @@
         <x:v>35156</x:v>
       </x:c>
       <x:c r="B173" s="11" t="n">
-        <x:v>33.82502448403852</x:v>
+        <x:v>33.82816311415628</x:v>
       </x:c>
       <x:c r="C173" s="11"/>
     </x:row>
@@ -1882,7 +1882,7 @@
         <x:v>35186</x:v>
       </x:c>
       <x:c r="B174" s="11" t="n">
-        <x:v>12.26223748465033</x:v>
+        <x:v>12.26337529987641</x:v>
       </x:c>
       <x:c r="C174" s="11"/>
     </x:row>
@@ -1891,7 +1891,7 @@
         <x:v>35217</x:v>
       </x:c>
       <x:c r="B175" s="11" t="n">
-        <x:v>14.20986808467695</x:v>
+        <x:v>14.21118662089741</x:v>
       </x:c>
       <x:c r="C175" s="11"/>
     </x:row>
@@ -1900,7 +1900,7 @@
         <x:v>35247</x:v>
       </x:c>
       <x:c r="B176" s="11" t="n">
-        <x:v>28.60625409394112</x:v>
+        <x:v>28.60890847341386</x:v>
       </x:c>
       <x:c r="C176" s="11"/>
     </x:row>
@@ -1909,7 +1909,7 @@
         <x:v>35278</x:v>
       </x:c>
       <x:c r="B177" s="11" t="n">
-        <x:v>33.97729592636487</x:v>
+        <x:v>33.9804486857772</x:v>
       </x:c>
       <x:c r="C177" s="11"/>
     </x:row>
@@ -1918,7 +1918,7 @@
         <x:v>35309</x:v>
       </x:c>
       <x:c r="B178" s="11" t="n">
-        <x:v>43.20141670702201</x:v>
+        <x:v>43.20542537426394</x:v>
       </x:c>
       <x:c r="C178" s="11"/>
     </x:row>
@@ -1927,7 +1927,7 @@
         <x:v>35339</x:v>
       </x:c>
       <x:c r="B179" s="11" t="n">
-        <x:v>57.11130681726687</x:v>
+        <x:v>57.11660618571894</x:v>
       </x:c>
       <x:c r="C179" s="11"/>
     </x:row>
@@ -1936,7 +1936,7 @@
         <x:v>35370</x:v>
       </x:c>
       <x:c r="B180" s="11" t="n">
-        <x:v>24.58742031473026</x:v>
+        <x:v>24.58970178589237</x:v>
       </x:c>
       <x:c r="C180" s="11"/>
     </x:row>
@@ -1945,7 +1945,7 @@
         <x:v>35400</x:v>
       </x:c>
       <x:c r="B181" s="11" t="n">
-        <x:v>69.16979983010089</x:v>
+        <x:v>69.17621810829279</x:v>
       </x:c>
       <x:c r="C181" s="11"/>
     </x:row>
@@ -1954,7 +1954,7 @@
         <x:v>35431</x:v>
       </x:c>
       <x:c r="B182" s="11" t="n">
-        <x:v>47.74460207846079</x:v>
+        <x:v>47.74903230869209</x:v>
       </x:c>
       <x:c r="C182" s="11"/>
     </x:row>
@@ -1963,7 +1963,7 @@
         <x:v>35462</x:v>
       </x:c>
       <x:c r="B183" s="11" t="n">
-        <x:v>93.71608119315866</x:v>
+        <x:v>93.7247771252219</x:v>
       </x:c>
       <x:c r="C183" s="11"/>
     </x:row>
@@ -1972,7 +1972,7 @@
         <x:v>35490</x:v>
       </x:c>
       <x:c r="B184" s="11" t="n">
-        <x:v>33.81124927553352</x:v>
+        <x:v>33.8143866274472</x:v>
       </x:c>
       <x:c r="C184" s="11"/>
     </x:row>
@@ -1981,7 +1981,7 @@
         <x:v>35521</x:v>
       </x:c>
       <x:c r="B185" s="11" t="n">
-        <x:v>44.70622422933219</x:v>
+        <x:v>44.7103725279353</x:v>
       </x:c>
       <x:c r="C185" s="11" t="n">
         <x:v>67.64241648750661</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>35551</x:v>
       </x:c>
       <x:c r="B186" s="11" t="n">
-        <x:v>85.69727765903441</x:v>
+        <x:v>85.70522952487259</x:v>
       </x:c>
       <x:c r="C186" s="11" t="n">
         <x:v>111.6840002379332</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>35582</x:v>
       </x:c>
       <x:c r="B187" s="11" t="n">
-        <x:v>114.9910285264162</x:v>
+        <x:v>115.0016985646767</x:v>
       </x:c>
       <x:c r="C187" s="11" t="n">
         <x:v>154.9586363503532</x:v>
@@ -2014,10 +2014,10 @@
         <x:v>35612</x:v>
       </x:c>
       <x:c r="B188" s="11" t="n">
-        <x:v>54.13853299302483</x:v>
+        <x:v>54.14355651725801</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>97.5396415314606</x:v>
+        <x:v>97.53964153146063</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -2025,7 +2025,7 @@
         <x:v>35643</x:v>
       </x:c>
       <x:c r="B189" s="11" t="n">
-        <x:v>36.98976279620074</x:v>
+        <x:v>36.99319508295682</x:v>
       </x:c>
       <x:c r="C189" s="11" t="n">
         <x:v>68.94368050985187</x:v>
@@ -2036,10 +2036,10 @@
         <x:v>35674</x:v>
       </x:c>
       <x:c r="B190" s="11" t="n">
-        <x:v>63.43207358355249</x:v>
+        <x:v>63.43795945709191</x:v>
       </x:c>
       <x:c r="C190" s="11" t="n">
-        <x:v>98.77268933870594</x:v>
+        <x:v>98.77268933870593</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -2047,10 +2047,10 @@
         <x:v>35704</x:v>
       </x:c>
       <x:c r="B191" s="11" t="n">
-        <x:v>61.23882960961291</x:v>
+        <x:v>61.24451197164874</x:v>
       </x:c>
       <x:c r="C191" s="11" t="n">
-        <x:v>86.71841812069302</x:v>
+        <x:v>86.718418120693</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -2058,10 +2058,10 @@
         <x:v>35735</x:v>
       </x:c>
       <x:c r="B192" s="11" t="n">
-        <x:v>55.64579262471349</x:v>
+        <x:v>55.65095600783953</x:v>
       </x:c>
       <x:c r="C192" s="11" t="n">
-        <x:v>50.3258308322667</x:v>
+        <x:v>50.32583083226664</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -2069,10 +2069,10 @@
         <x:v>35765</x:v>
       </x:c>
       <x:c r="B193" s="11" t="n">
-        <x:v>51.11236769715116</x:v>
+        <x:v>51.11711042296115</x:v>
       </x:c>
       <x:c r="C193" s="11" t="n">
-        <x:v>21.00644001839203</x:v>
+        <x:v>21.00644001839197</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -2080,10 +2080,10 @@
         <x:v>35796</x:v>
       </x:c>
       <x:c r="B194" s="11" t="n">
-        <x:v>97.06266670883902</x:v>
+        <x:v>97.07167317117539</x:v>
       </x:c>
       <x:c r="C194" s="11" t="n">
-        <x:v>108.2427097862724</x:v>
+        <x:v>108.2427097862725</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -2091,10 +2091,10 @@
         <x:v>35827</x:v>
       </x:c>
       <x:c r="B195" s="11" t="n">
-        <x:v>40.73774415901498</x:v>
+        <x:v>40.74152422163718</x:v>
       </x:c>
       <x:c r="C195" s="11" t="n">
-        <x:v>42.25739112113386</x:v>
+        <x:v>42.25739112113391</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -2102,10 +2102,10 @@
         <x:v>35855</x:v>
       </x:c>
       <x:c r="B196" s="11" t="n">
-        <x:v>57.53801695347848</x:v>
+        <x:v>57.54335591644099</x:v>
       </x:c>
       <x:c r="C196" s="11" t="n">
-        <x:v>63.86038406948391</x:v>
+        <x:v>63.86038406948393</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -2113,10 +2113,10 @@
         <x:v>35886</x:v>
       </x:c>
       <x:c r="B197" s="11" t="n">
-        <x:v>53.06470582290977</x:v>
+        <x:v>53.0696297065263</x:v>
       </x:c>
       <x:c r="C197" s="11" t="n">
-        <x:v>67.41472768454103</x:v>
+        <x:v>67.41472768454105</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -2124,10 +2124,10 @@
         <x:v>35916</x:v>
       </x:c>
       <x:c r="B198" s="11" t="n">
-        <x:v>65.06545657999415</x:v>
+        <x:v>65.07149401543619</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>81.90926711854148</x:v>
+        <x:v>81.90926711854149</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -2135,7 +2135,7 @@
         <x:v>35947</x:v>
       </x:c>
       <x:c r="B199" s="11" t="n">
-        <x:v>49.47766543270114</x:v>
+        <x:v>49.48225647419342</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
         <x:v>56.13231300732826</x:v>
@@ -2146,10 +2146,10 @@
         <x:v>35977</x:v>
       </x:c>
       <x:c r="B200" s="11" t="n">
-        <x:v>71.03885062075865</x:v>
+        <x:v>71.04544232851025</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>70.18937552207205</x:v>
+        <x:v>70.18937552207203</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -2157,10 +2157,10 @@
         <x:v>36008</x:v>
       </x:c>
       <x:c r="B201" s="11" t="n">
-        <x:v>109.1955000474439</x:v>
+        <x:v>109.2056323175723</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>87.6446005458595</x:v>
+        <x:v>87.64460054585946</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -2168,10 +2168,10 @@
         <x:v>36039</x:v>
       </x:c>
       <x:c r="B202" s="11" t="n">
-        <x:v>148.0562143847447</x:v>
+        <x:v>148.0699525475599</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>102.9950327889628</x:v>
+        <x:v>102.9950327889626</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -2179,10 +2179,10 @@
         <x:v>36069</x:v>
       </x:c>
       <x:c r="B203" s="11" t="n">
-        <x:v>64.79066673398975</x:v>
+        <x:v>64.79667867163246</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
-        <x:v>29.58817673052354</x:v>
+        <x:v>29.58817673052359</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -2190,10 +2190,10 @@
         <x:v>36100</x:v>
       </x:c>
       <x:c r="B204" s="11" t="n">
-        <x:v>85.01757108143714</x:v>
+        <x:v>85.02545987717949</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
-        <x:v>99.89411913667224</x:v>
+        <x:v>99.89411913667232</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -2201,7 +2201,7 @@
         <x:v>36130</x:v>
       </x:c>
       <x:c r="B205" s="11" t="n">
-        <x:v>123.041810879298</x:v>
+        <x:v>123.0532279511039</x:v>
       </x:c>
       <x:c r="C205" s="11" t="n">
         <x:v>162.8123634567349</x:v>
@@ -2212,7 +2212,7 @@
         <x:v>36161</x:v>
       </x:c>
       <x:c r="B206" s="11" t="n">
-        <x:v>87.24449432133324</x:v>
+        <x:v>87.25258975368435</x:v>
       </x:c>
       <x:c r="C206" s="11" t="n">
         <x:v>114.4487146096298</x:v>
@@ -2223,7 +2223,7 @@
         <x:v>36192</x:v>
       </x:c>
       <x:c r="B207" s="11" t="n">
-        <x:v>58.65610195523897</x:v>
+        <x:v>58.6615446655103</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
         <x:v>90.38987602970603</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>36220</x:v>
       </x:c>
       <x:c r="B208" s="11" t="n">
-        <x:v>40.55467106099675</x:v>
+        <x:v>40.55843413623319</x:v>
       </x:c>
       <x:c r="C208" s="11" t="n">
         <x:v>77.22453414937107</x:v>
@@ -2245,7 +2245,7 @@
         <x:v>36251</x:v>
       </x:c>
       <x:c r="B209" s="11" t="n">
-        <x:v>61.37388475037703</x:v>
+        <x:v>61.37957964420371</x:v>
       </x:c>
       <x:c r="C209" s="11" t="n">
         <x:v>112.0057602351625</x:v>
@@ -2256,10 +2256,10 @@
         <x:v>36281</x:v>
       </x:c>
       <x:c r="B210" s="11" t="n">
-        <x:v>48.35599434359065</x:v>
+        <x:v>48.36048130502042</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>72.39083723189825</x:v>
+        <x:v>72.39083723189822</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -2267,10 +2267,10 @@
         <x:v>36312</x:v>
       </x:c>
       <x:c r="B211" s="11" t="n">
-        <x:v>55.23571104139933</x:v>
+        <x:v>55.24083637298134</x:v>
       </x:c>
       <x:c r="C211" s="11" t="n">
-        <x:v>87.4447123237535</x:v>
+        <x:v>87.44471232375349</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -2278,10 +2278,10 @@
         <x:v>36342</x:v>
       </x:c>
       <x:c r="B212" s="11" t="n">
-        <x:v>52.61313219016004</x:v>
+        <x:v>52.61801417217781</x:v>
       </x:c>
       <x:c r="C212" s="11" t="n">
-        <x:v>91.7846457625918</x:v>
+        <x:v>91.78464576259181</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -2289,7 +2289,7 @@
         <x:v>36373</x:v>
       </x:c>
       <x:c r="B213" s="11" t="n">
-        <x:v>63.96265223118068</x:v>
+        <x:v>63.96858733720845</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
         <x:v>125.6451274187022</x:v>
@@ -2300,10 +2300,10 @@
         <x:v>36404</x:v>
       </x:c>
       <x:c r="B214" s="11" t="n">
-        <x:v>37.68315295754927</x:v>
+        <x:v>37.68664958410339</x:v>
       </x:c>
       <x:c r="C214" s="11" t="n">
-        <x:v>79.98982731485678</x:v>
+        <x:v>79.9898273148568</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -2311,10 +2311,10 @@
         <x:v>36434</x:v>
       </x:c>
       <x:c r="B215" s="11" t="n">
-        <x:v>53.95141646607017</x:v>
+        <x:v>53.95642262772707</x:v>
       </x:c>
       <x:c r="C215" s="11" t="n">
-        <x:v>99.71330810450132</x:v>
+        <x:v>99.7133081045013</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -2322,7 +2322,7 @@
         <x:v>36465</x:v>
       </x:c>
       <x:c r="B216" s="11" t="n">
-        <x:v>51.8199440056147</x:v>
+        <x:v>51.82475238755788</x:v>
       </x:c>
       <x:c r="C216" s="11" t="n">
         <x:v>102.3349936539656</x:v>
@@ -2333,7 +2333,7 @@
         <x:v>36495</x:v>
       </x:c>
       <x:c r="B217" s="11" t="n">
-        <x:v>63.3573890385169</x:v>
+        <x:v>63.36326798206395</x:v>
       </x:c>
       <x:c r="C217" s="11" t="n">
         <x:v>127.65943984786</x:v>
@@ -2344,7 +2344,7 @@
         <x:v>36526</x:v>
       </x:c>
       <x:c r="B218" s="11" t="n">
-        <x:v>43.03223355014126</x:v>
+        <x:v>43.03622651884757</x:v>
       </x:c>
       <x:c r="C218" s="11" t="n">
         <x:v>93.86154676790949</x:v>
@@ -2355,10 +2355,10 @@
         <x:v>36557</x:v>
       </x:c>
       <x:c r="B219" s="11" t="n">
-        <x:v>34.99492803318907</x:v>
+        <x:v>34.99817521886799</x:v>
       </x:c>
       <x:c r="C219" s="11" t="n">
-        <x:v>85.13650052977857</x:v>
+        <x:v>85.1365005297786</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -2366,7 +2366,7 @@
         <x:v>36586</x:v>
       </x:c>
       <x:c r="B220" s="11" t="n">
-        <x:v>52.73726480694263</x:v>
+        <x:v>52.74215830724827</x:v>
       </x:c>
       <x:c r="C220" s="11" t="n">
         <x:v>112.2833949098791</x:v>
@@ -2377,7 +2377,7 @@
         <x:v>36617</x:v>
       </x:c>
       <x:c r="B221" s="11" t="n">
-        <x:v>70.69174109410152</x:v>
+        <x:v>70.69830059349756</x:v>
       </x:c>
       <x:c r="C221" s="11" t="n">
         <x:v>123.8260605053116</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>36647</x:v>
       </x:c>
       <x:c r="B222" s="11" t="n">
-        <x:v>64.99354780499324</x:v>
+        <x:v>64.99957856800708</x:v>
       </x:c>
       <x:c r="C222" s="11" t="n">
         <x:v>103.9682769537645</x:v>
@@ -2399,10 +2399,10 @@
         <x:v>36678</x:v>
       </x:c>
       <x:c r="B223" s="11" t="n">
-        <x:v>50.46314726710973</x:v>
+        <x:v>50.46782975163902</x:v>
       </x:c>
       <x:c r="C223" s="11" t="n">
-        <x:v>69.4572414068205</x:v>
+        <x:v>69.45724140682046</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -2410,10 +2410,10 @@
         <x:v>36708</x:v>
       </x:c>
       <x:c r="B224" s="11" t="n">
-        <x:v>33.50424640680892</x:v>
+        <x:v>33.50735527187108</x:v>
       </x:c>
       <x:c r="C224" s="11" t="n">
-        <x:v>80.18186071203422</x:v>
+        <x:v>80.18186071203425</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -2421,10 +2421,10 @@
         <x:v>36739</x:v>
       </x:c>
       <x:c r="B225" s="11" t="n">
-        <x:v>37.84500118337991</x:v>
+        <x:v>37.84851282786008</x:v>
       </x:c>
       <x:c r="C225" s="11" t="n">
-        <x:v>93.24971145704694</x:v>
+        <x:v>93.24971145704696</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -2432,7 +2432,7 @@
         <x:v>36770</x:v>
       </x:c>
       <x:c r="B226" s="11" t="n">
-        <x:v>30.67560413673473</x:v>
+        <x:v>30.67845053157088</x:v>
       </x:c>
       <x:c r="C226" s="11" t="n">
         <x:v>65.6019211692969</x:v>
@@ -2443,7 +2443,7 @@
         <x:v>36800</x:v>
       </x:c>
       <x:c r="B227" s="11" t="n">
-        <x:v>65.22180610597196</x:v>
+        <x:v>65.22785804911469</x:v>
       </x:c>
       <x:c r="C227" s="11" t="n">
         <x:v>117.3340756224134</x:v>
@@ -2454,7 +2454,7 @@
         <x:v>36831</x:v>
       </x:c>
       <x:c r="B228" s="11" t="n">
-        <x:v>81.4391607416442</x:v>
+        <x:v>81.44671749604623</x:v>
       </x:c>
       <x:c r="C228" s="11" t="n">
         <x:v>101.8535166145087</x:v>
@@ -2465,10 +2465,10 @@
         <x:v>36861</x:v>
       </x:c>
       <x:c r="B229" s="11" t="n">
-        <x:v>65.15298858436186</x:v>
+        <x:v>65.15903414191435</x:v>
       </x:c>
       <x:c r="C229" s="11" t="n">
-        <x:v>82.87419551958456</x:v>
+        <x:v>82.8741955195845</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -2476,10 +2476,10 @@
         <x:v>36892</x:v>
       </x:c>
       <x:c r="B230" s="11" t="n">
-        <x:v>58.54973384772394</x:v>
+        <x:v>58.5551666880794</x:v>
       </x:c>
       <x:c r="C230" s="11" t="n">
-        <x:v>71.91550977980532</x:v>
+        <x:v>71.9155097798053</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -2487,10 +2487,10 @@
         <x:v>36923</x:v>
       </x:c>
       <x:c r="B231" s="11" t="n">
-        <x:v>70.65477994259277</x:v>
+        <x:v>70.66133601235693</x:v>
       </x:c>
       <x:c r="C231" s="11" t="n">
-        <x:v>82.60445933479424</x:v>
+        <x:v>82.60445933479423</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -2498,7 +2498,7 @@
         <x:v>36951</x:v>
       </x:c>
       <x:c r="B232" s="11" t="n">
-        <x:v>85.8810182957305</x:v>
+        <x:v>85.88898721089548</x:v>
       </x:c>
       <x:c r="C232" s="11" t="n">
         <x:v>91.02835883535984</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>36982</x:v>
       </x:c>
       <x:c r="B233" s="11" t="n">
-        <x:v>108.5072177319843</x:v>
+        <x:v>108.5172861362726</x:v>
       </x:c>
       <x:c r="C233" s="11" t="n">
         <x:v>128.0730694602136</x:v>
@@ -2520,10 +2520,10 @@
         <x:v>37012</x:v>
       </x:c>
       <x:c r="B234" s="11" t="n">
-        <x:v>65.5839064332212</x:v>
+        <x:v>65.58999197571855</x:v>
       </x:c>
       <x:c r="C234" s="11" t="n">
-        <x:v>95.19467746879151</x:v>
+        <x:v>95.19467746879157</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -2531,7 +2531,7 @@
         <x:v>37043</x:v>
       </x:c>
       <x:c r="B235" s="11" t="n">
-        <x:v>104.8597767020206</x:v>
+        <x:v>104.8695066595984</x:v>
       </x:c>
       <x:c r="C235" s="11" t="n">
         <x:v>159.4871670180582</x:v>
@@ -2542,10 +2542,10 @@
         <x:v>37073</x:v>
       </x:c>
       <x:c r="B236" s="11" t="n">
-        <x:v>78.31122948284401</x:v>
+        <x:v>78.31849599594082</x:v>
       </x:c>
       <x:c r="C236" s="11" t="n">
-        <x:v>90.82060119591493</x:v>
+        <x:v>90.82060119591488</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -2553,7 +2553,7 @@
         <x:v>37104</x:v>
       </x:c>
       <x:c r="B237" s="11" t="n">
-        <x:v>86.01416909060752</x:v>
+        <x:v>86.02215036085875</x:v>
       </x:c>
       <x:c r="C237" s="11" t="n">
         <x:v>121.8605293632929</x:v>
@@ -2564,10 +2564,10 @@
         <x:v>37135</x:v>
       </x:c>
       <x:c r="B238" s="11" t="n">
-        <x:v>142.7689137338293</x:v>
+        <x:v>142.7821612870642</x:v>
       </x:c>
       <x:c r="C238" s="11" t="n">
-        <x:v>102.4546777707316</x:v>
+        <x:v>102.4546777707315</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -2575,10 +2575,10 @@
         <x:v>37165</x:v>
       </x:c>
       <x:c r="B239" s="11" t="n">
-        <x:v>183.444704239362</x:v>
+        <x:v>183.4617261065284</x:v>
       </x:c>
       <x:c r="C239" s="11" t="n">
-        <x:v>159.8702972006245</x:v>
+        <x:v>159.8702972006244</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -2586,7 +2586,7 @@
         <x:v>37196</x:v>
       </x:c>
       <x:c r="B240" s="11" t="n">
-        <x:v>164.8503537353992</x:v>
+        <x:v>164.8656502294314</x:v>
       </x:c>
       <x:c r="C240" s="11" t="n">
         <x:v>182.1632607298961</x:v>
@@ -2597,10 +2597,10 @@
         <x:v>37226</x:v>
       </x:c>
       <x:c r="B241" s="11" t="n">
-        <x:v>162.6577123943466</x:v>
+        <x:v>162.6728054327936</x:v>
       </x:c>
       <x:c r="C241" s="11" t="n">
-        <x:v>205.3986622015249</x:v>
+        <x:v>205.398662201525</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -2608,10 +2608,10 @@
         <x:v>37257</x:v>
       </x:c>
       <x:c r="B242" s="11" t="n">
-        <x:v>80.913303637214</x:v>
+        <x:v>80.92081159724054</x:v>
       </x:c>
       <x:c r="C242" s="11" t="n">
-        <x:v>91.41612634405301</x:v>
+        <x:v>91.41612634405304</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -2619,10 +2619,10 @@
         <x:v>37288</x:v>
       </x:c>
       <x:c r="B243" s="11" t="n">
-        <x:v>72.8625138468803</x:v>
+        <x:v>72.8692747726713</x:v>
       </x:c>
       <x:c r="C243" s="11" t="n">
-        <x:v>87.3355243605431</x:v>
+        <x:v>87.33552436054313</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -2630,7 +2630,7 @@
         <x:v>37316</x:v>
       </x:c>
       <x:c r="B244" s="11" t="n">
-        <x:v>90.58052652314646</x:v>
+        <x:v>90.5889315065268</x:v>
       </x:c>
       <x:c r="C244" s="11" t="n">
         <x:v>138.8637262829773</x:v>
@@ -2641,7 +2641,7 @@
         <x:v>37347</x:v>
       </x:c>
       <x:c r="B245" s="11" t="n">
-        <x:v>75.23802284120049</x:v>
+        <x:v>75.24500419089918</x:v>
       </x:c>
       <x:c r="C245" s="11" t="n">
         <x:v>106.6280924218638</x:v>
@@ -2652,7 +2652,7 @@
         <x:v>37377</x:v>
       </x:c>
       <x:c r="B246" s="11" t="n">
-        <x:v>78.65651299461169</x:v>
+        <x:v>78.6638115466278</x:v>
       </x:c>
       <x:c r="C246" s="11" t="n">
         <x:v>112.9434618550594</x:v>
@@ -2663,7 +2663,7 @@
         <x:v>37408</x:v>
       </x:c>
       <x:c r="B247" s="11" t="n">
-        <x:v>96.09204004175062</x:v>
+        <x:v>96.10095643946363</x:v>
       </x:c>
       <x:c r="C247" s="11" t="n">
         <x:v>111.7177992894964</x:v>
@@ -2674,7 +2674,7 @@
         <x:v>37438</x:v>
       </x:c>
       <x:c r="B248" s="11" t="n">
-        <x:v>79.31305115923195</x:v>
+        <x:v>79.32041063154266</x:v>
       </x:c>
       <x:c r="C248" s="11" t="n">
         <x:v>91.66624808502418</x:v>
@@ -2685,10 +2685,10 @@
         <x:v>37469</x:v>
       </x:c>
       <x:c r="B249" s="11" t="n">
-        <x:v>101.8277055552811</x:v>
+        <x:v>101.8371541664308</x:v>
       </x:c>
       <x:c r="C249" s="11" t="n">
-        <x:v>109.531570659209</x:v>
+        <x:v>109.5315706592089</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -2696,10 +2696,10 @@
         <x:v>37500</x:v>
       </x:c>
       <x:c r="B250" s="11" t="n">
-        <x:v>176.1959308066056</x:v>
+        <x:v>176.2122800587788</x:v>
       </x:c>
       <x:c r="C250" s="11" t="n">
-        <x:v>184.2954009298288</x:v>
+        <x:v>184.2954009298287</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -2707,10 +2707,10 @@
         <x:v>37530</x:v>
       </x:c>
       <x:c r="B251" s="11" t="n">
-        <x:v>91.13449242159443</x:v>
+        <x:v>91.14294880757032</x:v>
       </x:c>
       <x:c r="C251" s="11" t="n">
-        <x:v>60.21429648214022</x:v>
+        <x:v>60.21429648214023</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -2718,7 +2718,7 @@
         <x:v>37561</x:v>
       </x:c>
       <x:c r="B252" s="11" t="n">
-        <x:v>151.1350532695495</x:v>
+        <x:v>151.1490771183797</x:v>
       </x:c>
       <x:c r="C252" s="11" t="n">
         <x:v>161.4865269602663</x:v>
@@ -2729,7 +2729,7 @@
         <x:v>37591</x:v>
       </x:c>
       <x:c r="B253" s="11" t="n">
-        <x:v>187.8360239730148</x:v>
+        <x:v>187.8534533115307</x:v>
       </x:c>
       <x:c r="C253" s="11" t="n">
         <x:v>223.9262067641156</x:v>
@@ -2740,10 +2740,10 @@
         <x:v>37622</x:v>
       </x:c>
       <x:c r="B254" s="11" t="n">
-        <x:v>163.8352690598373</x:v>
+        <x:v>163.8504713639795</x:v>
       </x:c>
       <x:c r="C254" s="11" t="n">
-        <x:v>188.8802872709831</x:v>
+        <x:v>188.8802872709832</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -2751,10 +2751,10 @@
         <x:v>37653</x:v>
       </x:c>
       <x:c r="B255" s="11" t="n">
-        <x:v>171.399999007296</x:v>
+        <x:v>171.4159032440933</x:v>
       </x:c>
       <x:c r="C255" s="11" t="n">
-        <x:v>170.9542400209729</x:v>
+        <x:v>170.9542400209728</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -2762,10 +2762,10 @@
         <x:v>37681</x:v>
       </x:c>
       <x:c r="B256" s="11" t="n">
-        <x:v>179.0071638552663</x:v>
+        <x:v>179.0237739622608</x:v>
       </x:c>
       <x:c r="C256" s="11" t="n">
-        <x:v>148.2718110014324</x:v>
+        <x:v>148.2718110014323</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -2773,7 +2773,7 @@
         <x:v>37712</x:v>
       </x:c>
       <x:c r="B257" s="11" t="n">
-        <x:v>147.6411190208759</x:v>
+        <x:v>147.6548186669175</x:v>
       </x:c>
       <x:c r="C257" s="11" t="n">
         <x:v>135.2465845812064</x:v>
@@ -2784,10 +2784,10 @@
         <x:v>37742</x:v>
       </x:c>
       <x:c r="B258" s="11" t="n">
-        <x:v>110.0032726168325</x:v>
+        <x:v>110.0134798403232</x:v>
       </x:c>
       <x:c r="C258" s="11" t="n">
-        <x:v>103.5274259225223</x:v>
+        <x:v>103.5274259225224</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -2795,10 +2795,10 @@
         <x:v>37773</x:v>
       </x:c>
       <x:c r="B259" s="11" t="n">
-        <x:v>75.55606485309194</x:v>
+        <x:v>75.56307571396623</x:v>
       </x:c>
       <x:c r="C259" s="11" t="n">
-        <x:v>95.36196327257308</x:v>
+        <x:v>95.36196327257315</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -2806,7 +2806,7 @@
         <x:v>37803</x:v>
       </x:c>
       <x:c r="B260" s="11" t="n">
-        <x:v>79.42706508884942</x:v>
+        <x:v>79.43443514053322</x:v>
       </x:c>
       <x:c r="C260" s="11" t="n">
         <x:v>115.1292550705642</x:v>
@@ -2817,10 +2817,10 @@
         <x:v>37834</x:v>
       </x:c>
       <x:c r="B261" s="11" t="n">
-        <x:v>70.12121840884507</x:v>
+        <x:v>70.12772496933833</x:v>
       </x:c>
       <x:c r="C261" s="11" t="n">
-        <x:v>118.51652136268</x:v>
+        <x:v>118.5165213626801</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -2828,7 +2828,7 @@
         <x:v>37865</x:v>
       </x:c>
       <x:c r="B262" s="11" t="n">
-        <x:v>72.33109923142685</x:v>
+        <x:v>72.3378108471599</x:v>
       </x:c>
       <x:c r="C262" s="11" t="n">
         <x:v>113.7244849436983</x:v>
@@ -2839,10 +2839,10 @@
         <x:v>37895</x:v>
       </x:c>
       <x:c r="B263" s="11" t="n">
-        <x:v>85.81538305823375</x:v>
+        <x:v>85.82334588309321</x:v>
       </x:c>
       <x:c r="C263" s="11" t="n">
-        <x:v>129.823174731404</x:v>
+        <x:v>129.8231747314039</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -2850,10 +2850,10 @@
         <x:v>37926</x:v>
       </x:c>
       <x:c r="B264" s="11" t="n">
-        <x:v>55.52174939550102</x:v>
+        <x:v>55.52690126863345</x:v>
       </x:c>
       <x:c r="C264" s="11" t="n">
-        <x:v>83.61554294099072</x:v>
+        <x:v>83.61554294099071</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -2861,7 +2861,7 @@
         <x:v>37956</x:v>
       </x:c>
       <x:c r="B265" s="11" t="n">
-        <x:v>62.91779246923652</x:v>
+        <x:v>62.92363062253867</x:v>
       </x:c>
       <x:c r="C265" s="11" t="n">
         <x:v>104.852407753693</x:v>
@@ -2872,7 +2872,7 @@
         <x:v>37987</x:v>
       </x:c>
       <x:c r="B266" s="11" t="n">
-        <x:v>67.85860055826824</x:v>
+        <x:v>67.86489717004339</x:v>
       </x:c>
       <x:c r="C266" s="11" t="n">
         <x:v>105.6962454717874</x:v>
@@ -2883,10 +2883,10 @@
         <x:v>38018</x:v>
       </x:c>
       <x:c r="B267" s="11" t="n">
-        <x:v>26.81638326746528</x:v>
+        <x:v>26.81887156450147</x:v>
       </x:c>
       <x:c r="C267" s="11" t="n">
-        <x:v>42.34656466217312</x:v>
+        <x:v>42.34656466217313</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -2894,7 +2894,7 @@
         <x:v>38047</x:v>
       </x:c>
       <x:c r="B268" s="11" t="n">
-        <x:v>49.70528514385487</x:v>
+        <x:v>49.70989730622117</x:v>
       </x:c>
       <x:c r="C268" s="11" t="n">
         <x:v>76.74845660557868</x:v>
@@ -2905,10 +2905,10 @@
         <x:v>38078</x:v>
       </x:c>
       <x:c r="B269" s="11" t="n">
-        <x:v>46.97776208671392</x:v>
+        <x:v>46.9821211617242</x:v>
       </x:c>
       <x:c r="C269" s="11" t="n">
-        <x:v>69.92274673958585</x:v>
+        <x:v>69.92274673958583</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -2916,10 +2916,10 @@
         <x:v>38108</x:v>
       </x:c>
       <x:c r="B270" s="11" t="n">
-        <x:v>55.88121713197189</x:v>
+        <x:v>55.88640236018038</x:v>
       </x:c>
       <x:c r="C270" s="11" t="n">
-        <x:v>50.50335911935552</x:v>
+        <x:v>50.50335911935551</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -2927,10 +2927,10 @@
         <x:v>38139</x:v>
       </x:c>
       <x:c r="B271" s="11" t="n">
-        <x:v>43.96850130865752</x:v>
+        <x:v>43.97258115381787</x:v>
       </x:c>
       <x:c r="C271" s="11" t="n">
-        <x:v>61.4568649991183</x:v>
+        <x:v>61.45686499911832</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -2938,7 +2938,7 @@
         <x:v>38169</x:v>
       </x:c>
       <x:c r="B272" s="11" t="n">
-        <x:v>53.17929963878588</x:v>
+        <x:v>53.18423415558324</x:v>
       </x:c>
       <x:c r="C272" s="11" t="n">
         <x:v>80.23303849252633</x:v>
@@ -2949,10 +2949,10 @@
         <x:v>38200</x:v>
       </x:c>
       <x:c r="B273" s="11" t="n">
-        <x:v>48.77179071605469</x:v>
+        <x:v>48.7763162593048</x:v>
       </x:c>
       <x:c r="C273" s="11" t="n">
-        <x:v>82.83532570719045</x:v>
+        <x:v>82.83532570719049</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -2960,10 +2960,10 @@
         <x:v>38231</x:v>
       </x:c>
       <x:c r="B274" s="11" t="n">
-        <x:v>49.53670799288338</x:v>
+        <x:v>49.54130451294546</x:v>
       </x:c>
       <x:c r="C274" s="11" t="n">
-        <x:v>78.0150270155981</x:v>
+        <x:v>78.01502701559811</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -2971,10 +2971,10 @@
         <x:v>38261</x:v>
       </x:c>
       <x:c r="B275" s="11" t="n">
-        <x:v>67.79802358522021</x:v>
+        <x:v>67.80431457604712</x:v>
       </x:c>
       <x:c r="C275" s="11" t="n">
-        <x:v>89.76321923156598</x:v>
+        <x:v>89.76321923156596</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -2982,7 +2982,7 @@
         <x:v>38292</x:v>
       </x:c>
       <x:c r="B276" s="11" t="n">
-        <x:v>74.98019282075516</x:v>
+        <x:v>74.9871502463598</x:v>
       </x:c>
       <x:c r="C276" s="11" t="n">
         <x:v>103.2827215546372</x:v>
@@ -2993,7 +2993,7 @@
         <x:v>38322</x:v>
       </x:c>
       <x:c r="B277" s="11" t="n">
-        <x:v>67.03855224875764</x:v>
+        <x:v>67.04477276810238</x:v>
       </x:c>
       <x:c r="C277" s="11" t="n">
         <x:v>109.1806546708208</x:v>
@@ -3004,10 +3004,10 @@
         <x:v>38353</x:v>
       </x:c>
       <x:c r="B278" s="11" t="n">
-        <x:v>31.88307319357625</x:v>
+        <x:v>31.88603162968379</x:v>
       </x:c>
       <x:c r="C278" s="11" t="n">
-        <x:v>70.66938711731548</x:v>
+        <x:v>70.66938711731551</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -3015,7 +3015,7 @@
         <x:v>38384</x:v>
       </x:c>
       <x:c r="B279" s="11" t="n">
-        <x:v>53.33873731973138</x:v>
+        <x:v>53.34368663077989</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
         <x:v>102.5887898729971</x:v>
@@ -3026,10 +3026,10 @@
         <x:v>38412</x:v>
       </x:c>
       <x:c r="B280" s="11" t="n">
-        <x:v>25.7756977944963</x:v>
+        <x:v>25.7780895261399</x:v>
       </x:c>
       <x:c r="C280" s="11" t="n">
-        <x:v>62.88396231307768</x:v>
+        <x:v>62.8839623130777</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -3037,10 +3037,10 @@
         <x:v>38443</x:v>
       </x:c>
       <x:c r="B281" s="11" t="n">
-        <x:v>46.38926070981064</x:v>
+        <x:v>46.39356517767209</x:v>
       </x:c>
       <x:c r="C281" s="11" t="n">
-        <x:v>76.66442776036972</x:v>
+        <x:v>76.66442776036969</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -3048,7 +3048,7 @@
         <x:v>38473</x:v>
       </x:c>
       <x:c r="B282" s="11" t="n">
-        <x:v>62.54745952915853</x:v>
+        <x:v>62.55326331920044</x:v>
       </x:c>
       <x:c r="C282" s="11" t="n">
         <x:v>102.7732232752676</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>38504</x:v>
       </x:c>
       <x:c r="B283" s="11" t="n">
-        <x:v>73.13090555387555</x:v>
+        <x:v>73.13769138378142</x:v>
       </x:c>
       <x:c r="C283" s="11" t="n">
         <x:v>122.0232220499722</x:v>
@@ -3070,10 +3070,10 @@
         <x:v>38534</x:v>
       </x:c>
       <x:c r="B284" s="11" t="n">
-        <x:v>35.7798321824136</x:v>
+        <x:v>35.78315219948998</x:v>
       </x:c>
       <x:c r="C284" s="11" t="n">
-        <x:v>79.59193194225327</x:v>
+        <x:v>79.5919319422533</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -3081,10 +3081,10 @@
         <x:v>38565</x:v>
       </x:c>
       <x:c r="B285" s="11" t="n">
-        <x:v>42.1367903549683</x:v>
+        <x:v>42.14070023533915</x:v>
       </x:c>
       <x:c r="C285" s="11" t="n">
-        <x:v>87.07942155179451</x:v>
+        <x:v>87.07942155179452</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -3092,7 +3092,7 @@
         <x:v>38596</x:v>
       </x:c>
       <x:c r="B286" s="11" t="n">
-        <x:v>81.07765878522709</x:v>
+        <x:v>81.08518199579744</x:v>
       </x:c>
       <x:c r="C286" s="11" t="n">
         <x:v>117.910184121683</x:v>
@@ -3103,7 +3103,7 @@
         <x:v>38626</x:v>
       </x:c>
       <x:c r="B287" s="11" t="n">
-        <x:v>37.20904288448493</x:v>
+        <x:v>37.21249551827992</x:v>
       </x:c>
       <x:c r="C287" s="11" t="n">
         <x:v>79.1268156712388</x:v>
@@ -3114,7 +3114,7 @@
         <x:v>38657</x:v>
       </x:c>
       <x:c r="B288" s="11" t="n">
-        <x:v>66.58141690551147</x:v>
+        <x:v>66.58759500718533</x:v>
       </x:c>
       <x:c r="C288" s="11" t="n">
         <x:v>115.8168297854517</x:v>
@@ -3125,10 +3125,10 @@
         <x:v>38687</x:v>
       </x:c>
       <x:c r="B289" s="11" t="n">
-        <x:v>49.57311196715705</x:v>
+        <x:v>49.57771186515046</x:v>
       </x:c>
       <x:c r="C289" s="11" t="n">
-        <x:v>98.22237566205062</x:v>
+        <x:v>98.22237566205065</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -3136,7 +3136,7 @@
         <x:v>38718</x:v>
       </x:c>
       <x:c r="B290" s="11" t="n">
-        <x:v>58.89667351582511</x:v>
+        <x:v>58.90213854877489</x:v>
       </x:c>
       <x:c r="C290" s="11" t="n">
         <x:v>106.4000371970356</x:v>
@@ -3147,10 +3147,10 @@
         <x:v>38749</x:v>
       </x:c>
       <x:c r="B291" s="11" t="n">
-        <x:v>28.02008862506667</x:v>
+        <x:v>28.02268861413992</x:v>
       </x:c>
       <x:c r="C291" s="11" t="n">
-        <x:v>82.98404450562606</x:v>
+        <x:v>82.98404450562609</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -3158,7 +3158,7 @@
         <x:v>38777</x:v>
       </x:c>
       <x:c r="B292" s="11" t="n">
-        <x:v>41.63988401809194</x:v>
+        <x:v>41.64374779043424</x:v>
       </x:c>
       <x:c r="C292" s="11" t="n">
         <x:v>95.6634388470679</x:v>
@@ -3169,10 +3169,10 @@
         <x:v>38808</x:v>
       </x:c>
       <x:c r="B293" s="11" t="n">
-        <x:v>66.76176271057128</x:v>
+        <x:v>66.76795754656487</x:v>
       </x:c>
       <x:c r="C293" s="11" t="n">
-        <x:v>114.8301834716221</x:v>
+        <x:v>114.830183471622</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -3180,10 +3180,10 @@
         <x:v>38838</x:v>
       </x:c>
       <x:c r="B294" s="11" t="n">
-        <x:v>46.3784015693836</x:v>
+        <x:v>46.38270502962345</x:v>
       </x:c>
       <x:c r="C294" s="11" t="n">
-        <x:v>90.04393028137399</x:v>
+        <x:v>90.04393028137397</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -3191,10 +3191,10 @@
         <x:v>38869</x:v>
       </x:c>
       <x:c r="B295" s="11" t="n">
-        <x:v>48.67828686414678</x:v>
+        <x:v>48.68280373115761</x:v>
       </x:c>
       <x:c r="C295" s="11" t="n">
-        <x:v>87.30188351779503</x:v>
+        <x:v>87.301883517795</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -3202,7 +3202,7 @@
         <x:v>38899</x:v>
       </x:c>
       <x:c r="B296" s="11" t="n">
-        <x:v>45.38930476198907</x:v>
+        <x:v>45.3935164437579</x:v>
       </x:c>
       <x:c r="C296" s="11" t="n">
         <x:v>85.93090657579111</x:v>
@@ -3213,10 +3213,10 @@
         <x:v>38930</x:v>
       </x:c>
       <x:c r="B297" s="11" t="n">
-        <x:v>27.88327461374762</x:v>
+        <x:v>27.8858619078241</x:v>
       </x:c>
       <x:c r="C297" s="11" t="n">
-        <x:v>76.57169050003975</x:v>
+        <x:v>76.57169050003978</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -3224,7 +3224,7 @@
         <x:v>38961</x:v>
       </x:c>
       <x:c r="B298" s="11" t="n">
-        <x:v>33.33943282645218</x:v>
+        <x:v>33.34252639843252</x:v>
       </x:c>
       <x:c r="C298" s="11" t="n">
         <x:v>81.19760625867836</x:v>
@@ -3235,10 +3235,10 @@
         <x:v>38991</x:v>
       </x:c>
       <x:c r="B299" s="11" t="n">
-        <x:v>39.28688307744018</x:v>
+        <x:v>39.29052851440115</x:v>
       </x:c>
       <x:c r="C299" s="11" t="n">
-        <x:v>86.50854192984873</x:v>
+        <x:v>86.50854192984875</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -3246,7 +3246,7 @@
         <x:v>39022</x:v>
       </x:c>
       <x:c r="B300" s="11" t="n">
-        <x:v>24.0624642825058</x:v>
+        <x:v>24.06469704290307</x:v>
       </x:c>
       <x:c r="C300" s="11" t="n">
         <x:v>67.73798001959366</x:v>
@@ -3257,7 +3257,7 @@
         <x:v>39052</x:v>
       </x:c>
       <x:c r="B301" s="11" t="n">
-        <x:v>56.14755811276322</x:v>
+        <x:v>56.15276805479931</x:v>
       </x:c>
       <x:c r="C301" s="11" t="n">
         <x:v>119.0481308108179</x:v>
@@ -3268,7 +3268,7 @@
         <x:v>39083</x:v>
       </x:c>
       <x:c r="B302" s="11" t="n">
-        <x:v>45.74527892991375</x:v>
+        <x:v>45.74952364258979</x:v>
       </x:c>
       <x:c r="C302" s="11" t="n">
         <x:v>104.3625368271335</x:v>
@@ -3279,7 +3279,7 @@
         <x:v>39114</x:v>
       </x:c>
       <x:c r="B303" s="11" t="n">
-        <x:v>54.05740350301629</x:v>
+        <x:v>54.06241949922945</x:v>
       </x:c>
       <x:c r="C303" s="11" t="n">
         <x:v>114.1570651956294</x:v>
@@ -3290,7 +3290,7 @@
         <x:v>39142</x:v>
       </x:c>
       <x:c r="B304" s="11" t="n">
-        <x:v>64.62555134913572</x:v>
+        <x:v>64.6315479656921</x:v>
       </x:c>
       <x:c r="C304" s="11" t="n">
         <x:v>128.4091355192489</x:v>
@@ -3301,7 +3301,7 @@
         <x:v>39173</x:v>
       </x:c>
       <x:c r="B305" s="11" t="n">
-        <x:v>96.24372439856475</x:v>
+        <x:v>96.25265487109657</x:v>
       </x:c>
       <x:c r="C305" s="11" t="n">
         <x:v>172.2137859749045</x:v>
@@ -3312,7 +3312,7 @@
         <x:v>39203</x:v>
       </x:c>
       <x:c r="B306" s="11" t="n">
-        <x:v>79.55740018788677</x:v>
+        <x:v>79.5647823333879</x:v>
       </x:c>
       <x:c r="C306" s="11" t="n">
         <x:v>158.5992203266933</x:v>
@@ -3323,7 +3323,7 @@
         <x:v>39234</x:v>
       </x:c>
       <x:c r="B307" s="11" t="n">
-        <x:v>43.68279627279414</x:v>
+        <x:v>43.68684960733273</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
         <x:v>104.1623598688283</x:v>
@@ -3334,10 +3334,10 @@
         <x:v>39264</x:v>
       </x:c>
       <x:c r="B308" s="11" t="n">
-        <x:v>37.71779487261446</x:v>
+        <x:v>37.72129471359813</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
-        <x:v>103.0468209815274</x:v>
+        <x:v>103.0468209815275</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -3345,10 +3345,10 @@
         <x:v>39295</x:v>
       </x:c>
       <x:c r="B309" s="11" t="n">
-        <x:v>58.53793897789159</x:v>
+        <x:v>58.54337072379895</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
-        <x:v>95.50240781792603</x:v>
+        <x:v>95.502407817926</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -3356,10 +3356,10 @@
         <x:v>39326</x:v>
       </x:c>
       <x:c r="B310" s="11" t="n">
-        <x:v>64.04091273768762</x:v>
+        <x:v>64.04685510552189</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>71.86675119064743</x:v>
+        <x:v>71.86675119064739</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -3367,10 +3367,10 @@
         <x:v>39356</x:v>
       </x:c>
       <x:c r="B311" s="11" t="n">
-        <x:v>58.54119226040906</x:v>
+        <x:v>58.54662430818909</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
-        <x:v>93.5256554324231</x:v>
+        <x:v>93.52565543242308</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
@@ -3378,7 +3378,7 @@
         <x:v>39387</x:v>
       </x:c>
       <x:c r="B312" s="11" t="n">
-        <x:v>86.21550115028785</x:v>
+        <x:v>86.2235011021772</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
         <x:v>129.0717472629741</x:v>
@@ -3389,7 +3389,7 @@
         <x:v>39417</x:v>
       </x:c>
       <x:c r="B313" s="11" t="n">
-        <x:v>131.3971342376294</x:v>
+        <x:v>131.4093266013955</x:v>
       </x:c>
       <x:c r="C313" s="11" t="n">
         <x:v>175.7741035366301</x:v>
@@ -3400,10 +3400,10 @@
         <x:v>39448</x:v>
       </x:c>
       <x:c r="B314" s="11" t="n">
-        <x:v>126.9071344763917</x:v>
+        <x:v>126.9189102122708</x:v>
       </x:c>
       <x:c r="C314" s="11" t="n">
-        <x:v>121.4736915584612</x:v>
+        <x:v>121.4736915584611</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -3411,7 +3411,7 @@
         <x:v>39479</x:v>
       </x:c>
       <x:c r="B315" s="11" t="n">
-        <x:v>100.1567136040916</x:v>
+        <x:v>100.166007163597</x:v>
       </x:c>
       <x:c r="C315" s="11" t="n">
         <x:v>106.3455346191326</x:v>
@@ -3422,7 +3422,7 @@
         <x:v>39508</x:v>
       </x:c>
       <x:c r="B316" s="11" t="n">
-        <x:v>114.776904615945</x:v>
+        <x:v>114.7875547856092</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
         <x:v>108.0255685478136</x:v>
@@ -3433,10 +3433,10 @@
         <x:v>39539</x:v>
       </x:c>
       <x:c r="B317" s="11" t="n">
-        <x:v>89.53115882618124</x:v>
+        <x:v>89.53946643854387</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
-        <x:v>103.8910386673777</x:v>
+        <x:v>103.8910386673778</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
@@ -3444,10 +3444,10 @@
         <x:v>39569</x:v>
       </x:c>
       <x:c r="B318" s="11" t="n">
-        <x:v>56.10280661965603</x:v>
+        <x:v>56.10801240919302</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>76.11918109013368</x:v>
+        <x:v>76.11918109013372</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -3455,7 +3455,7 @@
         <x:v>39600</x:v>
       </x:c>
       <x:c r="B319" s="11" t="n">
-        <x:v>206.1361765394164</x:v>
+        <x:v>206.155303952387</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
         <x:v>284.3356968661188</x:v>
@@ -3466,10 +3466,10 @@
         <x:v>39630</x:v>
       </x:c>
       <x:c r="B320" s="11" t="n">
-        <x:v>162.0679964516763</x:v>
+        <x:v>162.0830347702747</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
-        <x:v>217.4701837276595</x:v>
+        <x:v>217.4701837276596</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -3477,10 +3477,10 @@
         <x:v>39661</x:v>
       </x:c>
       <x:c r="B321" s="11" t="n">
-        <x:v>138.8986689820225</x:v>
+        <x:v>138.9115574145494</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
-        <x:v>188.9880807786955</x:v>
+        <x:v>188.9880807786956</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
@@ -3488,7 +3488,7 @@
         <x:v>39692</x:v>
       </x:c>
       <x:c r="B322" s="11" t="n">
-        <x:v>220.3753743120115</x:v>
+        <x:v>220.3958229827096</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
         <x:v>229.0676363751273</x:v>
@@ -3499,10 +3499,10 @@
         <x:v>39722</x:v>
       </x:c>
       <x:c r="B323" s="11" t="n">
-        <x:v>270.0439838686855</x:v>
+        <x:v>270.0690412986154</x:v>
       </x:c>
       <x:c r="C323" s="11" t="n">
-        <x:v>203.8271888172036</x:v>
+        <x:v>203.8271888172035</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -3510,10 +3510,10 @@
         <x:v>39753</x:v>
       </x:c>
       <x:c r="B324" s="11" t="n">
-        <x:v>172.0100606272221</x:v>
+        <x:v>172.026021471747</x:v>
       </x:c>
       <x:c r="C324" s="11" t="n">
-        <x:v>153.3537457706474</x:v>
+        <x:v>153.3537457706473</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -3521,10 +3521,10 @@
         <x:v>39783</x:v>
       </x:c>
       <x:c r="B325" s="11" t="n">
-        <x:v>215.4998275321183</x:v>
+        <x:v>215.519823799952</x:v>
       </x:c>
       <x:c r="C325" s="11" t="n">
-        <x:v>218.6680261218018</x:v>
+        <x:v>218.6680261218019</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -3532,7 +3532,7 @@
         <x:v>39814</x:v>
       </x:c>
       <x:c r="B326" s="11" t="n">
-        <x:v>145.0708717378953</x:v>
+        <x:v>145.0843328902283</x:v>
       </x:c>
       <x:c r="C326" s="11" t="n">
         <x:v>125.4927104547351</x:v>
@@ -3543,10 +3543,10 @@
         <x:v>39845</x:v>
       </x:c>
       <x:c r="B327" s="11" t="n">
-        <x:v>166.5275180310543</x:v>
+        <x:v>166.5429701494637</x:v>
       </x:c>
       <x:c r="C327" s="11" t="n">
-        <x:v>143.7934012783273</x:v>
+        <x:v>143.7934012783274</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -3554,7 +3554,7 @@
         <x:v>39873</x:v>
       </x:c>
       <x:c r="B328" s="11" t="n">
-        <x:v>155.3058894809467</x:v>
+        <x:v>155.3203003424206</x:v>
       </x:c>
       <x:c r="C328" s="11" t="n">
         <x:v>148.1829959454552</x:v>
@@ -3565,10 +3565,10 @@
         <x:v>39904</x:v>
       </x:c>
       <x:c r="B329" s="11" t="n">
-        <x:v>161.3837766605797</x:v>
+        <x:v>161.3987514903003</x:v>
       </x:c>
       <x:c r="C329" s="11" t="n">
-        <x:v>196.1832366518394</x:v>
+        <x:v>196.1832366518395</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
@@ -3576,10 +3576,10 @@
         <x:v>39934</x:v>
       </x:c>
       <x:c r="B330" s="11" t="n">
-        <x:v>129.2103492581774</x:v>
+        <x:v>129.2223387097711</x:v>
       </x:c>
       <x:c r="C330" s="11" t="n">
-        <x:v>142.1082413841261</x:v>
+        <x:v>142.1082413841262</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -3587,7 +3587,7 @@
         <x:v>39965</x:v>
       </x:c>
       <x:c r="B331" s="11" t="n">
-        <x:v>128.6621841401124</x:v>
+        <x:v>128.674122727366</x:v>
       </x:c>
       <x:c r="C331" s="11" t="n">
         <x:v>156.9574315453123</x:v>
@@ -3598,7 +3598,7 @@
         <x:v>39995</x:v>
       </x:c>
       <x:c r="B332" s="11" t="n">
-        <x:v>101.9666625770541</x:v>
+        <x:v>101.9761240820509</x:v>
       </x:c>
       <x:c r="C332" s="11" t="n">
         <x:v>120.4606054476244</x:v>
@@ -3609,7 +3609,7 @@
         <x:v>40026</x:v>
       </x:c>
       <x:c r="B333" s="11" t="n">
-        <x:v>86.06987451842151</x:v>
+        <x:v>86.07786095758945</x:v>
       </x:c>
       <x:c r="C333" s="11" t="n">
         <x:v>107.9161117690122</x:v>
@@ -3620,10 +3620,10 @@
         <x:v>40057</x:v>
       </x:c>
       <x:c r="B334" s="11" t="n">
-        <x:v>181.9627175542209</x:v>
+        <x:v>181.9796019075758</x:v>
       </x:c>
       <x:c r="C334" s="11" t="n">
-        <x:v>247.0546293016913</x:v>
+        <x:v>247.0546293016912</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -3631,7 +3631,7 @@
         <x:v>40087</x:v>
       </x:c>
       <x:c r="B335" s="11" t="n">
-        <x:v>141.0706094250815</x:v>
+        <x:v>141.0836993923535</x:v>
       </x:c>
       <x:c r="C335" s="11" t="n">
         <x:v>196.0238151419967</x:v>
@@ -3642,7 +3642,7 @@
         <x:v>40118</x:v>
       </x:c>
       <x:c r="B336" s="11" t="n">
-        <x:v>95.41155224421307</x:v>
+        <x:v>95.42040549934072</x:v>
       </x:c>
       <x:c r="C336" s="11" t="n">
         <x:v>109.4810976171643</x:v>
@@ -3653,7 +3653,7 @@
         <x:v>40148</x:v>
       </x:c>
       <x:c r="B337" s="11" t="n">
-        <x:v>121.505740757879</x:v>
+        <x:v>121.5170152974615</x:v>
       </x:c>
       <x:c r="C337" s="11" t="n">
         <x:v>143.9781361573145</x:v>
@@ -3664,10 +3664,10 @@
         <x:v>40179</x:v>
       </x:c>
       <x:c r="B338" s="11" t="n">
-        <x:v>114.6144687180917</x:v>
+        <x:v>114.6251038152996</x:v>
       </x:c>
       <x:c r="C338" s="11" t="n">
-        <x:v>123.3033784709783</x:v>
+        <x:v>123.3033784709782</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -3675,10 +3675,10 @@
         <x:v>40210</x:v>
       </x:c>
       <x:c r="B339" s="11" t="n">
-        <x:v>91.61497098634783</x:v>
+        <x:v>91.62347195601632</x:v>
       </x:c>
       <x:c r="C339" s="11" t="n">
-        <x:v>74.86724012042984</x:v>
+        <x:v>74.86724012042981</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -3686,10 +3686,10 @@
         <x:v>40238</x:v>
       </x:c>
       <x:c r="B340" s="11" t="n">
-        <x:v>87.07479185942694</x:v>
+        <x:v>87.08287154505602</x:v>
       </x:c>
       <x:c r="C340" s="11" t="n">
-        <x:v>89.11805832579442</x:v>
+        <x:v>89.11805832579445</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -3697,10 +3697,10 @@
         <x:v>40269</x:v>
       </x:c>
       <x:c r="B341" s="11" t="n">
-        <x:v>132.2796565117031</x:v>
+        <x:v>132.29193076487</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
-        <x:v>152.7549432509209</x:v>
+        <x:v>152.754943250921</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -3708,10 +3708,10 @@
         <x:v>40299</x:v>
       </x:c>
       <x:c r="B342" s="11" t="n">
-        <x:v>146.9314981536621</x:v>
+        <x:v>146.9451319538555</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
-        <x:v>94.60686588844395</x:v>
+        <x:v>94.60686588844389</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -3719,10 +3719,10 @@
         <x:v>40330</x:v>
       </x:c>
       <x:c r="B343" s="11" t="n">
-        <x:v>104.1913224267779</x:v>
+        <x:v>104.2009903583631</x:v>
       </x:c>
       <x:c r="C343" s="11" t="n">
-        <x:v>40.06140055356862</x:v>
+        <x:v>40.06140055356867</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -3730,7 +3730,7 @@
         <x:v>40360</x:v>
       </x:c>
       <x:c r="B344" s="11" t="n">
-        <x:v>141.7849899608741</x:v>
+        <x:v>141.7981462156448</x:v>
       </x:c>
       <x:c r="C344" s="11" t="n">
         <x:v>123.6664366843627</x:v>
@@ -3741,10 +3741,10 @@
         <x:v>40391</x:v>
       </x:c>
       <x:c r="B345" s="11" t="n">
-        <x:v>124.4973933830792</x:v>
+        <x:v>124.5089455186479</x:v>
       </x:c>
       <x:c r="C345" s="11" t="n">
-        <x:v>104.0488771715708</x:v>
+        <x:v>104.0488771715709</x:v>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -3752,7 +3752,7 @@
         <x:v>40422</x:v>
       </x:c>
       <x:c r="B346" s="11" t="n">
-        <x:v>192.0203200639535</x:v>
+        <x:v>192.0381376640578</x:v>
       </x:c>
       <x:c r="C346" s="11" t="n">
         <x:v>212.6908475691023</x:v>
@@ -3763,7 +3763,7 @@
         <x:v>40452</x:v>
       </x:c>
       <x:c r="B347" s="11" t="n">
-        <x:v>133.3512855499083</x:v>
+        <x:v>133.3636592397268</x:v>
       </x:c>
       <x:c r="C347" s="11" t="n">
         <x:v>132.957822669873</x:v>
@@ -3774,10 +3774,10 @@
         <x:v>40483</x:v>
       </x:c>
       <x:c r="B348" s="11" t="n">
-        <x:v>238.5733407933119</x:v>
+        <x:v>238.5954780565994</x:v>
       </x:c>
       <x:c r="C348" s="11" t="n">
-        <x:v>277.7565902279657</x:v>
+        <x:v>277.7565902279658</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -3785,7 +3785,7 @@
         <x:v>40513</x:v>
       </x:c>
       <x:c r="B349" s="11" t="n">
-        <x:v>184.9664730020712</x:v>
+        <x:v>184.9836360744354</x:v>
       </x:c>
       <x:c r="C349" s="11" t="n">
         <x:v>198.5996052923425</x:v>
@@ -3796,7 +3796,7 @@
         <x:v>40544</x:v>
       </x:c>
       <x:c r="B350" s="11" t="n">
-        <x:v>121.7429664924313</x:v>
+        <x:v>121.7542630442325</x:v>
       </x:c>
       <x:c r="C350" s="11" t="n">
         <x:v>136.2676983185303</x:v>
@@ -3807,10 +3807,10 @@
         <x:v>40575</x:v>
       </x:c>
       <x:c r="B351" s="11" t="n">
-        <x:v>92.54214302109997</x:v>
+        <x:v>92.5507300232287</x:v>
       </x:c>
       <x:c r="C351" s="11" t="n">
-        <x:v>92.65478460363727</x:v>
+        <x:v>92.65478460363732</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -3818,7 +3818,7 @@
         <x:v>40603</x:v>
       </x:c>
       <x:c r="B352" s="11" t="n">
-        <x:v>132.8528193330684</x:v>
+        <x:v>132.8651467701168</x:v>
       </x:c>
       <x:c r="C352" s="11" t="n">
         <x:v>130.8132552491234</x:v>
@@ -3829,7 +3829,7 @@
         <x:v>40634</x:v>
       </x:c>
       <x:c r="B353" s="11" t="n">
-        <x:v>96.93202554325316</x:v>
+        <x:v>96.94101988337223</x:v>
       </x:c>
       <x:c r="C353" s="11" t="n">
         <x:v>87.84814355339792</x:v>
@@ -3840,10 +3840,10 @@
         <x:v>40664</x:v>
       </x:c>
       <x:c r="B354" s="11" t="n">
-        <x:v>68.62258332418321</x:v>
+        <x:v>68.62895082605691</x:v>
       </x:c>
       <x:c r="C354" s="11" t="n">
-        <x:v>58.19762822453856</x:v>
+        <x:v>58.19762822453863</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -3851,7 +3851,7 @@
         <x:v>40695</x:v>
       </x:c>
       <x:c r="B355" s="11" t="n">
-        <x:v>117.4625394947444</x:v>
+        <x:v>117.473438864953</x:v>
       </x:c>
       <x:c r="C355" s="11" t="n">
         <x:v>104.4786056642876</x:v>
@@ -3862,10 +3862,10 @@
         <x:v>40725</x:v>
       </x:c>
       <x:c r="B356" s="11" t="n">
-        <x:v>121.5535020678724</x:v>
+        <x:v>121.5647810392354</x:v>
       </x:c>
       <x:c r="C356" s="11" t="n">
-        <x:v>66.66887332220715</x:v>
+        <x:v>66.66887332220713</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -3873,10 +3873,10 @@
         <x:v>40756</x:v>
       </x:c>
       <x:c r="B357" s="11" t="n">
-        <x:v>134.8121151322687</x:v>
+        <x:v>134.8246243727274</x:v>
       </x:c>
       <x:c r="C357" s="11" t="n">
-        <x:v>-2.002580165095651</x:v>
+        <x:v>-2.002580165095821</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -3884,7 +3884,7 @@
         <x:v>40787</x:v>
       </x:c>
       <x:c r="B358" s="11" t="n">
-        <x:v>181.6707277813404</x:v>
+        <x:v>181.6875850409115</x:v>
       </x:c>
       <x:c r="C358" s="11" t="n">
         <x:v>103.1138862580066</x:v>
@@ -3895,10 +3895,10 @@
         <x:v>40817</x:v>
       </x:c>
       <x:c r="B359" s="11" t="n">
-        <x:v>146.3992554594493</x:v>
+        <x:v>146.4128398727472</x:v>
       </x:c>
       <x:c r="C359" s="11" t="n">
-        <x:v>61.89670727974701</x:v>
+        <x:v>61.89670727974707</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -3906,10 +3906,10 @@
         <x:v>40848</x:v>
       </x:c>
       <x:c r="B360" s="11" t="n">
-        <x:v>224.9754448620891</x:v>
+        <x:v>224.9963203741625</x:v>
       </x:c>
       <x:c r="C360" s="11" t="n">
-        <x:v>120.4994582437208</x:v>
+        <x:v>120.4994582437209</x:v>
       </x:c>
     </x:row>
     <x:row r="361">
@@ -3917,7 +3917,7 @@
         <x:v>40878</x:v>
       </x:c>
       <x:c r="B361" s="11" t="n">
-        <x:v>230.1154745153486</x:v>
+        <x:v>230.1368269716999</x:v>
       </x:c>
       <x:c r="C361" s="11" t="n">
         <x:v>173.8516673876594</x:v>
@@ -3928,10 +3928,10 @@
         <x:v>40909</x:v>
       </x:c>
       <x:c r="B362" s="11" t="n">
-        <x:v>199.3517288230506</x:v>
+        <x:v>199.3702267058949</x:v>
       </x:c>
       <x:c r="C362" s="11" t="n">
-        <x:v>163.1251089412562</x:v>
+        <x:v>163.1251089412563</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -3939,10 +3939,10 @@
         <x:v>40940</x:v>
       </x:c>
       <x:c r="B363" s="11" t="n">
-        <x:v>123.992815327053</x:v>
+        <x:v>124.0043206427329</x:v>
       </x:c>
       <x:c r="C363" s="11" t="n">
-        <x:v>54.94662044927996</x:v>
+        <x:v>54.94662044928008</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -3950,10 +3950,10 @@
         <x:v>40969</x:v>
       </x:c>
       <x:c r="B364" s="11" t="n">
-        <x:v>115.4675467531663</x:v>
+        <x:v>115.4782610076388</x:v>
       </x:c>
       <x:c r="C364" s="11" t="n">
-        <x:v>58.42606392976853</x:v>
+        <x:v>58.42606392976859</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -3961,10 +3961,10 @@
         <x:v>41000</x:v>
       </x:c>
       <x:c r="B365" s="11" t="n">
-        <x:v>140.6004088731839</x:v>
+        <x:v>140.613455210462</x:v>
       </x:c>
       <x:c r="C365" s="11" t="n">
-        <x:v>86.81993270188894</x:v>
+        <x:v>86.81993270188899</x:v>
       </x:c>
     </x:row>
     <x:row r="366">
@@ -3972,10 +3972,10 @@
         <x:v>41030</x:v>
       </x:c>
       <x:c r="B366" s="11" t="n">
-        <x:v>196.4498294110938</x:v>
+        <x:v>196.4680580261687</x:v>
       </x:c>
       <x:c r="C366" s="11" t="n">
-        <x:v>117.7793283990476</x:v>
+        <x:v>117.7793283990475</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -3983,7 +3983,7 @@
         <x:v>41061</x:v>
       </x:c>
       <x:c r="B367" s="11" t="n">
-        <x:v>143.5228216297139</x:v>
+        <x:v>143.5361391381984</x:v>
       </x:c>
       <x:c r="C367" s="11" t="n">
         <x:v>18.30350919008424</x:v>
@@ -3994,10 +3994,10 @@
         <x:v>41091</x:v>
       </x:c>
       <x:c r="B368" s="11" t="n">
-        <x:v>112.0533419786962</x:v>
+        <x:v>112.0637394284924</x:v>
       </x:c>
       <x:c r="C368" s="11" t="n">
-        <x:v>29.29510648515856</x:v>
+        <x:v>29.29510648515864</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -4005,10 +4005,10 @@
         <x:v>41122</x:v>
       </x:c>
       <x:c r="B369" s="11" t="n">
-        <x:v>149.7360695106556</x:v>
+        <x:v>149.7499635475307</x:v>
       </x:c>
       <x:c r="C369" s="11" t="n">
-        <x:v>141.8368795565374</x:v>
+        <x:v>141.8368795565375</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -4016,10 +4016,10 @@
         <x:v>41153</x:v>
       </x:c>
       <x:c r="B370" s="11" t="n">
-        <x:v>120.4286663708624</x:v>
+        <x:v>120.4398409685184</x:v>
       </x:c>
       <x:c r="C370" s="11" t="n">
-        <x:v>75.44459932536995</x:v>
+        <x:v>75.44459932537</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -4027,10 +4027,10 @@
         <x:v>41183</x:v>
       </x:c>
       <x:c r="B371" s="11" t="n">
-        <x:v>137.1292326177202</x:v>
+        <x:v>137.141956863928</x:v>
       </x:c>
       <x:c r="C371" s="11" t="n">
-        <x:v>86.11681032931764</x:v>
+        <x:v>86.11681032931766</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -4038,7 +4038,7 @@
         <x:v>41214</x:v>
       </x:c>
       <x:c r="B372" s="11" t="n">
-        <x:v>91.02606984266608</x:v>
+        <x:v>91.03451616809132</x:v>
       </x:c>
       <x:c r="C372" s="11" t="n">
         <x:v>16.94171244112289</x:v>
@@ -4049,10 +4049,10 @@
         <x:v>41244</x:v>
       </x:c>
       <x:c r="B373" s="11" t="n">
-        <x:v>103.0766081892549</x:v>
+        <x:v>103.086172686305</x:v>
       </x:c>
       <x:c r="C373" s="11" t="n">
-        <x:v>25.49122584246328</x:v>
+        <x:v>25.49122584246318</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -4060,10 +4060,10 @@
         <x:v>41275</x:v>
       </x:c>
       <x:c r="B374" s="11" t="n">
-        <x:v>132.5841094663463</x:v>
+        <x:v>132.5964119697577</x:v>
       </x:c>
       <x:c r="C374" s="11" t="n">
-        <x:v>78.61602837596263</x:v>
+        <x:v>78.61602837596264</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -4071,10 +4071,10 @@
         <x:v>41306</x:v>
       </x:c>
       <x:c r="B375" s="11" t="n">
-        <x:v>77.50515552284591</x:v>
+        <x:v>77.51234724019473</x:v>
       </x:c>
       <x:c r="C375" s="11" t="n">
-        <x:v>25.9719609465692</x:v>
+        <x:v>25.97196094656925</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -4082,10 +4082,10 @@
         <x:v>41334</x:v>
       </x:c>
       <x:c r="B376" s="11" t="n">
-        <x:v>99.48277643525756</x:v>
+        <x:v>99.4920074600116</x:v>
       </x:c>
       <x:c r="C376" s="11" t="n">
-        <x:v>23.77395220684012</x:v>
+        <x:v>23.77395220684014</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -4093,10 +4093,10 @@
         <x:v>41365</x:v>
       </x:c>
       <x:c r="B377" s="11" t="n">
-        <x:v>102.8353410973121</x:v>
+        <x:v>102.8448832071453</x:v>
       </x:c>
       <x:c r="C377" s="11" t="n">
-        <x:v>46.49027454710354</x:v>
+        <x:v>46.49027454710356</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -4104,10 +4104,10 @@
         <x:v>41395</x:v>
       </x:c>
       <x:c r="B378" s="11" t="n">
-        <x:v>56.86987808952833</x:v>
+        <x:v>56.87515505576523</x:v>
       </x:c>
       <x:c r="C378" s="11" t="n">
-        <x:v>10.87620787881703</x:v>
+        <x:v>10.87620787881704</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -4115,10 +4115,10 @@
         <x:v>41426</x:v>
       </x:c>
       <x:c r="B379" s="11" t="n">
-        <x:v>70.84508047034161</x:v>
+        <x:v>70.85165419812603</x:v>
       </x:c>
       <x:c r="C379" s="11" t="n">
-        <x:v>14.40340281853732</x:v>
+        <x:v>14.40340281853733</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -4126,10 +4126,10 @@
         <x:v>41456</x:v>
       </x:c>
       <x:c r="B380" s="11" t="n">
-        <x:v>84.87777553860829</x:v>
+        <x:v>84.88565136269703</x:v>
       </x:c>
       <x:c r="C380" s="11" t="n">
-        <x:v>41.24902974289369</x:v>
+        <x:v>41.24902974289367</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -4137,7 +4137,7 @@
         <x:v>41487</x:v>
       </x:c>
       <x:c r="B381" s="11" t="n">
-        <x:v>56.9278130801375</x:v>
+        <x:v>56.93309542217263</x:v>
       </x:c>
       <x:c r="C381" s="11" t="n">
         <x:v>5.63449134333635</x:v>
@@ -4148,10 +4148,10 @@
         <x:v>41518</x:v>
       </x:c>
       <x:c r="B382" s="11" t="n">
-        <x:v>72.16448570022861</x:v>
+        <x:v>72.17118185586209</x:v>
       </x:c>
       <x:c r="C382" s="11" t="n">
-        <x:v>20.42313854072103</x:v>
+        <x:v>20.42313854072104</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -4159,10 +4159,10 @@
         <x:v>41548</x:v>
       </x:c>
       <x:c r="B383" s="11" t="n">
-        <x:v>88.51121811948033</x:v>
+        <x:v>88.51943109136097</x:v>
       </x:c>
       <x:c r="C383" s="11" t="n">
-        <x:v>35.66818435086712</x:v>
+        <x:v>35.66818435086707</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
@@ -4170,10 +4170,10 @@
         <x:v>41579</x:v>
       </x:c>
       <x:c r="B384" s="11" t="n">
-        <x:v>80.78683607570211</x:v>
+        <x:v>80.79433230078084</x:v>
       </x:c>
       <x:c r="C384" s="11" t="n">
-        <x:v>65.18223638768251</x:v>
+        <x:v>65.18223638768256</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -4181,10 +4181,10 @@
         <x:v>41609</x:v>
       </x:c>
       <x:c r="B385" s="11" t="n">
-        <x:v>71.81965622497626</x:v>
+        <x:v>71.82632038382057</x:v>
       </x:c>
       <x:c r="C385" s="11" t="n">
-        <x:v>48.64548732412213</x:v>
+        <x:v>48.64548732412217</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -4192,10 +4192,10 @@
         <x:v>41640</x:v>
       </x:c>
       <x:c r="B386" s="11" t="n">
-        <x:v>47.60899618931629</x:v>
+        <x:v>47.61341383665271</x:v>
       </x:c>
       <x:c r="C386" s="11" t="n">
-        <x:v>5.92507244291204</x:v>
+        <x:v>5.925072442912054</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -4203,10 +4203,10 @@
         <x:v>41671</x:v>
       </x:c>
       <x:c r="B387" s="11" t="n">
-        <x:v>60.54303047884279</x:v>
+        <x:v>60.54864827755188</x:v>
       </x:c>
       <x:c r="C387" s="11" t="n">
-        <x:v>43.48058190710496</x:v>
+        <x:v>43.48058190710499</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -4214,7 +4214,7 @@
         <x:v>41699</x:v>
       </x:c>
       <x:c r="B388" s="11" t="n">
-        <x:v>62.38281021206128</x:v>
+        <x:v>62.38859872426337</x:v>
       </x:c>
       <x:c r="C388" s="11" t="n">
         <x:v>32.11462428349323</x:v>
@@ -4225,10 +4225,10 @@
         <x:v>41730</x:v>
       </x:c>
       <x:c r="B389" s="11" t="n">
-        <x:v>57.93108634095972</x:v>
+        <x:v>57.93646177690152</x:v>
       </x:c>
       <x:c r="C389" s="11" t="n">
-        <x:v>49.39347015856951</x:v>
+        <x:v>49.39347015856958</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
@@ -4236,10 +4236,10 @@
         <x:v>41760</x:v>
       </x:c>
       <x:c r="B390" s="11" t="n">
-        <x:v>54.27162284751983</x:v>
+        <x:v>54.27665872118458</x:v>
       </x:c>
       <x:c r="C390" s="11" t="n">
-        <x:v>37.14025291399012</x:v>
+        <x:v>37.14025291399011</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -4247,10 +4247,10 @@
         <x:v>41791</x:v>
       </x:c>
       <x:c r="B391" s="11" t="n">
-        <x:v>54.97336374512335</x:v>
+        <x:v>54.97846473345246</x:v>
       </x:c>
       <x:c r="C391" s="11" t="n">
-        <x:v>57.04854881790281</x:v>
+        <x:v>57.04854881790286</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -4258,10 +4258,10 @@
         <x:v>41821</x:v>
       </x:c>
       <x:c r="B392" s="11" t="n">
-        <x:v>41.73546338176252</x:v>
+        <x:v>41.73933602293121</x:v>
       </x:c>
       <x:c r="C392" s="11" t="n">
-        <x:v>30.31308100222391</x:v>
+        <x:v>30.31308100222392</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -4269,10 +4269,10 @@
         <x:v>41852</x:v>
       </x:c>
       <x:c r="B393" s="11" t="n">
-        <x:v>74.17126800530039</x:v>
+        <x:v>74.17815037062562</x:v>
       </x:c>
       <x:c r="C393" s="11" t="n">
-        <x:v>56.75428836986619</x:v>
+        <x:v>56.75428836986614</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -4280,10 +4280,10 @@
         <x:v>41883</x:v>
       </x:c>
       <x:c r="B394" s="11" t="n">
-        <x:v>92.95868602137455</x:v>
+        <x:v>92.96731167460331</x:v>
       </x:c>
       <x:c r="C394" s="11" t="n">
-        <x:v>57.41749451847978</x:v>
+        <x:v>57.41749451847971</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -4291,7 +4291,7 @@
         <x:v>41913</x:v>
       </x:c>
       <x:c r="B395" s="11" t="n">
-        <x:v>66.90050168901897</x:v>
+        <x:v>66.90670939862737</x:v>
       </x:c>
       <x:c r="C395" s="11" t="n">
         <x:v>33.68275509603231</x:v>
@@ -4302,7 +4302,7 @@
         <x:v>41944</x:v>
       </x:c>
       <x:c r="B396" s="11" t="n">
-        <x:v>73.3929371806592</x:v>
+        <x:v>73.39974732452693</x:v>
       </x:c>
       <x:c r="C396" s="11" t="n">
         <x:v>37.18878264097032</x:v>
@@ -4313,10 +4313,10 @@
         <x:v>41974</x:v>
       </x:c>
       <x:c r="B397" s="11" t="n">
-        <x:v>119.8261174772528</x:v>
+        <x:v>119.8372361642883</x:v>
       </x:c>
       <x:c r="C397" s="11" t="n">
-        <x:v>78.14799741273346</x:v>
+        <x:v>78.14799741273347</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -4324,10 +4324,10 @@
         <x:v>42005</x:v>
       </x:c>
       <x:c r="B398" s="11" t="n">
-        <x:v>89.37777660041934</x:v>
+        <x:v>89.38606998041759</x:v>
       </x:c>
       <x:c r="C398" s="11" t="n">
-        <x:v>39.69490057248865</x:v>
+        <x:v>39.69490057248868</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -4335,10 +4335,10 @@
         <x:v>42036</x:v>
       </x:c>
       <x:c r="B399" s="11" t="n">
-        <x:v>57.5952289948474</x:v>
+        <x:v>57.60057326652554</x:v>
       </x:c>
       <x:c r="C399" s="11" t="n">
-        <x:v>1.890771340520871</x:v>
+        <x:v>1.890771340520914</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -4346,10 +4346,10 @@
         <x:v>42064</x:v>
       </x:c>
       <x:c r="B400" s="11" t="n">
-        <x:v>65.22017698629902</x:v>
+        <x:v>65.22622877827546</x:v>
       </x:c>
       <x:c r="C400" s="11" t="n">
-        <x:v>33.73740573304065</x:v>
+        <x:v>33.7374057330407</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -4357,10 +4357,10 @@
         <x:v>42095</x:v>
       </x:c>
       <x:c r="B401" s="11" t="n">
-        <x:v>89.52931983760519</x:v>
+        <x:v>89.53762727932772</x:v>
       </x:c>
       <x:c r="C401" s="11" t="n">
-        <x:v>76.32746505622868</x:v>
+        <x:v>76.3274650562287</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -4368,10 +4368,10 @@
         <x:v>42125</x:v>
       </x:c>
       <x:c r="B402" s="11" t="n">
-        <x:v>94.74243273779345</x:v>
+        <x:v>94.7512239052015</x:v>
       </x:c>
       <x:c r="C402" s="11" t="n">
-        <x:v>66.9242704227742</x:v>
+        <x:v>66.92427042277419</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -4379,7 +4379,7 @@
         <x:v>42156</x:v>
       </x:c>
       <x:c r="B403" s="11" t="n">
-        <x:v>106.7284796566562</x:v>
+        <x:v>106.7383830115179</x:v>
       </x:c>
       <x:c r="C403" s="11" t="n">
         <x:v>84.38928848198981</x:v>
@@ -4390,7 +4390,7 @@
         <x:v>42186</x:v>
       </x:c>
       <x:c r="B404" s="11" t="n">
-        <x:v>144.1380600626259</x:v>
+        <x:v>144.1514346591954</x:v>
       </x:c>
       <x:c r="C404" s="11" t="n">
         <x:v>140.8245750776364</x:v>
@@ -4401,10 +4401,10 @@
         <x:v>42217</x:v>
       </x:c>
       <x:c r="B405" s="11" t="n">
-        <x:v>90.18456046074257</x:v>
+        <x:v>90.19292870236062</x:v>
       </x:c>
       <x:c r="C405" s="11" t="n">
-        <x:v>58.56801747442766</x:v>
+        <x:v>58.56801747442772</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -4412,10 +4412,10 @@
         <x:v>42248</x:v>
       </x:c>
       <x:c r="B406" s="11" t="n">
-        <x:v>97.05987353857401</x:v>
+        <x:v>97.0688797417316</x:v>
       </x:c>
       <x:c r="C406" s="11" t="n">
-        <x:v>25.63245196461487</x:v>
+        <x:v>25.63245196461482</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -4423,10 +4423,10 @@
         <x:v>42278</x:v>
       </x:c>
       <x:c r="B407" s="11" t="n">
-        <x:v>91.02717088012501</x:v>
+        <x:v>91.03561730771574</x:v>
       </x:c>
       <x:c r="C407" s="11" t="n">
-        <x:v>64.30234777928463</x:v>
+        <x:v>64.30234777928464</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -4434,7 +4434,7 @@
         <x:v>42309</x:v>
       </x:c>
       <x:c r="B408" s="11" t="n">
-        <x:v>94.39539085963304</x:v>
+        <x:v>94.40414982496266</x:v>
       </x:c>
       <x:c r="C408" s="11" t="n">
         <x:v>101.9678962001895</x:v>
@@ -4445,10 +4445,10 @@
         <x:v>42339</x:v>
       </x:c>
       <x:c r="B409" s="11" t="n">
-        <x:v>77.21228239478111</x:v>
+        <x:v>77.21944693637958</x:v>
       </x:c>
       <x:c r="C409" s="11" t="n">
-        <x:v>48.0975049838645</x:v>
+        <x:v>48.09750498386453</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -4456,10 +4456,10 @@
         <x:v>42370</x:v>
       </x:c>
       <x:c r="B410" s="11" t="n">
-        <x:v>141.9174806363538</x:v>
+        <x:v>141.9306491849582</x:v>
       </x:c>
       <x:c r="C410" s="11" t="n">
-        <x:v>124.9555518308437</x:v>
+        <x:v>124.9555518308438</x:v>
       </x:c>
     </x:row>
     <x:row r="411">
@@ -4467,7 +4467,7 @@
         <x:v>42401</x:v>
       </x:c>
       <x:c r="B411" s="11" t="n">
-        <x:v>213.6393099265526</x:v>
+        <x:v>213.6591335566224</x:v>
       </x:c>
       <x:c r="C411" s="11" t="n">
         <x:v>211.4139785639329</x:v>
@@ -4478,7 +4478,7 @@
         <x:v>42430</x:v>
       </x:c>
       <x:c r="B412" s="11" t="n">
-        <x:v>210.6289917943018</x:v>
+        <x:v>210.6485360964095</x:v>
       </x:c>
       <x:c r="C412" s="11" t="n">
         <x:v>201.3874100058047</x:v>
@@ -4489,7 +4489,7 @@
         <x:v>42461</x:v>
       </x:c>
       <x:c r="B413" s="11" t="n">
-        <x:v>176.3242288144745</x:v>
+        <x:v>176.340589971443</x:v>
       </x:c>
       <x:c r="C413" s="11" t="n">
         <x:v>161.0026180581175</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>42491</x:v>
       </x:c>
       <x:c r="B414" s="11" t="n">
-        <x:v>136.0369265019145</x:v>
+        <x:v>136.049549392841</x:v>
       </x:c>
       <x:c r="C414" s="11" t="n">
         <x:v>109.6518336191547</x:v>
@@ -4511,7 +4511,7 @@
         <x:v>42522</x:v>
       </x:c>
       <x:c r="B415" s="11" t="n">
-        <x:v>342.230635885273</x:v>
+        <x:v>342.2623915276531</x:v>
       </x:c>
       <x:c r="C415" s="11" t="n">
         <x:v>292.1174349149136</x:v>
@@ -4522,10 +4522,10 @@
         <x:v>42552</x:v>
       </x:c>
       <x:c r="B416" s="11" t="n">
-        <x:v>405.8712740224991</x:v>
+        <x:v>405.908934891161</x:v>
       </x:c>
       <x:c r="C416" s="11" t="n">
-        <x:v>375.1291857472544</x:v>
+        <x:v>375.1291857472543</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -4533,10 +4533,10 @@
         <x:v>42583</x:v>
       </x:c>
       <x:c r="B417" s="11" t="n">
-        <x:v>228.6124149353944</x:v>
+        <x:v>228.6336279225763</x:v>
       </x:c>
       <x:c r="C417" s="11" t="n">
-        <x:v>248.269825150525</x:v>
+        <x:v>248.2698251505251</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -4544,10 +4544,10 @@
         <x:v>42614</x:v>
       </x:c>
       <x:c r="B418" s="11" t="n">
-        <x:v>163.6571315254246</x:v>
+        <x:v>163.6723173001528</x:v>
       </x:c>
       <x:c r="C418" s="11" t="n">
-        <x:v>147.6829411675586</x:v>
+        <x:v>147.6829411675587</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -4555,10 +4555,10 @@
         <x:v>42644</x:v>
       </x:c>
       <x:c r="B419" s="11" t="n">
-        <x:v>178.0310801900833</x:v>
+        <x:v>178.0475997260985</x:v>
       </x:c>
       <x:c r="C419" s="11" t="n">
-        <x:v>180.0547756339651</x:v>
+        <x:v>180.0547756339652</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -4566,10 +4566,10 @@
         <x:v>42675</x:v>
       </x:c>
       <x:c r="B420" s="11" t="n">
-        <x:v>253.3434532471069</x:v>
+        <x:v>253.3669610317908</x:v>
       </x:c>
       <x:c r="C420" s="11" t="n">
-        <x:v>181.1453536304456</x:v>
+        <x:v>181.1453536304455</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -4577,10 +4577,10 @@
         <x:v>42705</x:v>
       </x:c>
       <x:c r="B421" s="11" t="n">
-        <x:v>247.0938172502158</x:v>
+        <x:v>247.1167451300493</x:v>
       </x:c>
       <x:c r="C421" s="11" t="n">
-        <x:v>184.4447517821101</x:v>
+        <x:v>184.44475178211</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -4588,10 +4588,10 @@
         <x:v>42736</x:v>
       </x:c>
       <x:c r="B422" s="11" t="n">
-        <x:v>249.2402632866255</x:v>
+        <x:v>249.2633903355735</x:v>
       </x:c>
       <x:c r="C422" s="11" t="n">
-        <x:v>194.4205757141498</x:v>
+        <x:v>194.4205757141497</x:v>
       </x:c>
     </x:row>
     <x:row r="423">
@@ -4599,10 +4599,10 @@
         <x:v>42767</x:v>
       </x:c>
       <x:c r="B423" s="11" t="n">
-        <x:v>206.6834413269144</x:v>
+        <x:v>206.7026195206832</x:v>
       </x:c>
       <x:c r="C423" s="11" t="n">
-        <x:v>157.7411779290857</x:v>
+        <x:v>157.7411779290858</x:v>
       </x:c>
     </x:row>
     <x:row r="424">
@@ -4610,10 +4610,10 @@
         <x:v>42795</x:v>
       </x:c>
       <x:c r="B424" s="11" t="n">
-        <x:v>139.5727282703685</x:v>
+        <x:v>139.5856792489783</x:v>
       </x:c>
       <x:c r="C424" s="11" t="n">
-        <x:v>37.09857789160881</x:v>
+        <x:v>37.09857789160879</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -4621,7 +4621,7 @@
         <x:v>42826</x:v>
       </x:c>
       <x:c r="B425" s="11" t="n">
-        <x:v>178.4300936945466</x:v>
+        <x:v>178.4466502550969</x:v>
       </x:c>
       <x:c r="C425" s="11" t="n">
         <x:v>137.1834894159752</x:v>
@@ -4632,10 +4632,10 @@
         <x:v>42856</x:v>
       </x:c>
       <x:c r="B426" s="11" t="n">
-        <x:v>166.9718121517548</x:v>
+        <x:v>166.9873054962957</x:v>
       </x:c>
       <x:c r="C426" s="11" t="n">
-        <x:v>155.748707858531</x:v>
+        <x:v>155.7487078585311</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -4643,10 +4643,10 @@
         <x:v>42887</x:v>
       </x:c>
       <x:c r="B427" s="11" t="n">
-        <x:v>192.1840800835012</x:v>
+        <x:v>192.2019128789273</x:v>
       </x:c>
       <x:c r="C427" s="11" t="n">
-        <x:v>186.401735523647</x:v>
+        <x:v>186.4017355236471</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -4654,7 +4654,7 @@
         <x:v>42917</x:v>
       </x:c>
       <x:c r="B428" s="11" t="n">
-        <x:v>122.5258597934955</x:v>
+        <x:v>122.5372289901071</x:v>
       </x:c>
       <x:c r="C428" s="11" t="n">
         <x:v>107.5363510745885</x:v>
@@ -4665,10 +4665,10 @@
         <x:v>42948</x:v>
       </x:c>
       <x:c r="B429" s="11" t="n">
-        <x:v>151.8999457656161</x:v>
+        <x:v>151.9140405889588</x:v>
       </x:c>
       <x:c r="C429" s="11" t="n">
-        <x:v>179.3700170709378</x:v>
+        <x:v>179.3700170709379</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -4676,10 +4676,10 @@
         <x:v>42979</x:v>
       </x:c>
       <x:c r="B430" s="11" t="n">
-        <x:v>153.4225602356145</x:v>
+        <x:v>153.4367963426283</x:v>
       </x:c>
       <x:c r="C430" s="11" t="n">
-        <x:v>150.7567098675539</x:v>
+        <x:v>150.7567098675538</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -4687,7 +4687,7 @@
         <x:v>43009</x:v>
       </x:c>
       <x:c r="B431" s="11" t="n">
-        <x:v>166.6109592079258</x:v>
+        <x:v>166.626419068857</x:v>
       </x:c>
       <x:c r="C431" s="11" t="n">
         <x:v>154.5718603325681</x:v>
@@ -4698,10 +4698,10 @@
         <x:v>43040</x:v>
       </x:c>
       <x:c r="B432" s="11" t="n">
-        <x:v>127.0108406426343</x:v>
+        <x:v>127.0226260014272</x:v>
       </x:c>
       <x:c r="C432" s="11" t="n">
-        <x:v>105.5533307855701</x:v>
+        <x:v>105.55333078557</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -4709,10 +4709,10 @@
         <x:v>43070</x:v>
       </x:c>
       <x:c r="B433" s="11" t="n">
-        <x:v>135.298410509763</x:v>
+        <x:v>135.3109648736575</x:v>
       </x:c>
       <x:c r="C433" s="11" t="n">
-        <x:v>129.986439303196</x:v>
+        <x:v>129.9864393031961</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -4720,7 +4720,7 @@
         <x:v>43101</x:v>
       </x:c>
       <x:c r="B434" s="11" t="n">
-        <x:v>118.1325022710195</x:v>
+        <x:v>118.1434638071949</x:v>
       </x:c>
       <x:c r="C434" s="11" t="n">
         <x:v>114.4784784104427</x:v>
@@ -4731,10 +4731,10 @@
         <x:v>43132</x:v>
       </x:c>
       <x:c r="B435" s="11" t="n">
-        <x:v>92.61665860294612</x:v>
+        <x:v>92.6252525193891</x:v>
       </x:c>
       <x:c r="C435" s="11" t="n">
-        <x:v>94.4712466455848</x:v>
+        <x:v>94.47124664558478</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -4742,10 +4742,10 @@
         <x:v>43160</x:v>
       </x:c>
       <x:c r="B436" s="11" t="n">
-        <x:v>94.01930406155755</x:v>
+        <x:v>94.02802812972541</x:v>
       </x:c>
       <x:c r="C436" s="11" t="n">
-        <x:v>81.00650623409149</x:v>
+        <x:v>81.00650623409152</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -4753,7 +4753,7 @@
         <x:v>43191</x:v>
       </x:c>
       <x:c r="B437" s="11" t="n">
-        <x:v>116.7595919214665</x:v>
+        <x:v>116.7704260650431</x:v>
       </x:c>
       <x:c r="C437" s="11" t="n">
         <x:v>116.0637715060473</x:v>
@@ -4764,10 +4764,10 @@
         <x:v>43221</x:v>
       </x:c>
       <x:c r="B438" s="11" t="n">
-        <x:v>76.98595722351338</x:v>
+        <x:v>76.99310076435842</x:v>
       </x:c>
       <x:c r="C438" s="11" t="n">
-        <x:v>25.03918518217242</x:v>
+        <x:v>25.03918518217237</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -4775,10 +4775,10 @@
         <x:v>43252</x:v>
       </x:c>
       <x:c r="B439" s="11" t="n">
-        <x:v>106.2863753595496</x:v>
+        <x:v>106.2962376914739</x:v>
       </x:c>
       <x:c r="C439" s="11" t="n">
-        <x:v>64.0002326749782</x:v>
+        <x:v>64.00023267497818</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -4786,7 +4786,7 @@
         <x:v>43282</x:v>
       </x:c>
       <x:c r="B440" s="11" t="n">
-        <x:v>129.290293580226</x:v>
+        <x:v>129.3022904498678</x:v>
       </x:c>
       <x:c r="C440" s="11" t="n">
         <x:v>105.5594452062976</x:v>
@@ -4797,10 +4797,10 @@
         <x:v>43313</x:v>
       </x:c>
       <x:c r="B441" s="11" t="n">
-        <x:v>117.8427074877302</x:v>
+        <x:v>117.8536421337953</x:v>
       </x:c>
       <x:c r="C441" s="11" t="n">
-        <x:v>98.40216773834625</x:v>
+        <x:v>98.40216773834631</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -4808,7 +4808,7 @@
         <x:v>43344</x:v>
       </x:c>
       <x:c r="B442" s="11" t="n">
-        <x:v>134.5560390966522</x:v>
+        <x:v>134.5685245757694</x:v>
       </x:c>
       <x:c r="C442" s="11" t="n">
         <x:v>106.8933912337233</x:v>
@@ -4819,10 +4819,10 @@
         <x:v>43374</x:v>
       </x:c>
       <x:c r="B443" s="11" t="n">
-        <x:v>149.8691680635756</x:v>
+        <x:v>149.8830744506894</x:v>
       </x:c>
       <x:c r="C443" s="11" t="n">
-        <x:v>94.46179666506626</x:v>
+        <x:v>94.46179666506622</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -4830,10 +4830,10 @@
         <x:v>43405</x:v>
       </x:c>
       <x:c r="B444" s="11" t="n">
-        <x:v>149.0970632632683</x:v>
+        <x:v>149.1108980066385</x:v>
       </x:c>
       <x:c r="C444" s="11" t="n">
-        <x:v>89.49566303337696</x:v>
+        <x:v>89.49566303337686</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -4841,7 +4841,7 @@
         <x:v>43435</x:v>
       </x:c>
       <x:c r="B445" s="11" t="n">
-        <x:v>202.1266526988985</x:v>
+        <x:v>202.1454080674293</x:v>
       </x:c>
       <x:c r="C445" s="11" t="n">
         <x:v>142.1696325418972</x:v>
@@ -4852,7 +4852,7 @@
         <x:v>43466</x:v>
       </x:c>
       <x:c r="B446" s="11" t="n">
-        <x:v>215.4400960809923</x:v>
+        <x:v>215.4600868063339</x:v>
       </x:c>
       <x:c r="C446" s="11" t="n">
         <x:v>159.9691602983856</x:v>
@@ -4863,7 +4863,7 @@
         <x:v>43497</x:v>
       </x:c>
       <x:c r="B447" s="11" t="n">
-        <x:v>177.0979577561274</x:v>
+        <x:v>177.1143907075439</x:v>
       </x:c>
       <x:c r="C447" s="11" t="n">
         <x:v>138.7280691873053</x:v>
@@ -4874,7 +4874,7 @@
         <x:v>43525</x:v>
       </x:c>
       <x:c r="B448" s="11" t="n">
-        <x:v>194.6624210927844</x:v>
+        <x:v>194.6804838539193</x:v>
       </x:c>
       <x:c r="C448" s="11" t="n">
         <x:v>177.2397482669232</x:v>
@@ -4885,7 +4885,7 @@
         <x:v>43556</x:v>
       </x:c>
       <x:c r="B449" s="11" t="n">
-        <x:v>155.0911707878135</x:v>
+        <x:v>155.1055617255012</x:v>
       </x:c>
       <x:c r="C449" s="11" t="n">
         <x:v>121.8631321270109</x:v>
@@ -4896,10 +4896,10 @@
         <x:v>43586</x:v>
       </x:c>
       <x:c r="B450" s="11" t="n">
-        <x:v>157.6776173746705</x:v>
+        <x:v>157.6922483092031</x:v>
       </x:c>
       <x:c r="C450" s="11" t="n">
-        <x:v>99.41492615211101</x:v>
+        <x:v>99.41492615211105</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -4907,10 +4907,10 @@
         <x:v>43617</x:v>
       </x:c>
       <x:c r="B451" s="11" t="n">
-        <x:v>184.3829002750531</x:v>
+        <x:v>184.4000091975988</x:v>
       </x:c>
       <x:c r="C451" s="11" t="n">
-        <x:v>133.7688627811186</x:v>
+        <x:v>133.7688627811187</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
@@ -4918,10 +4918,10 @@
         <x:v>43647</x:v>
       </x:c>
       <x:c r="B452" s="11" t="n">
-        <x:v>183.6583962725508</x:v>
+        <x:v>183.6754379682395</x:v>
       </x:c>
       <x:c r="C452" s="11" t="n">
-        <x:v>141.0878443703234</x:v>
+        <x:v>141.0878443703235</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -4929,7 +4929,7 @@
         <x:v>43678</x:v>
       </x:c>
       <x:c r="B453" s="11" t="n">
-        <x:v>255.0607063573223</x:v>
+        <x:v>255.0843734862317</x:v>
       </x:c>
       <x:c r="C453" s="11" t="n">
         <x:v>207.8579839108186</x:v>
@@ -4940,10 +4940,10 @@
         <x:v>43709</x:v>
       </x:c>
       <x:c r="B454" s="11" t="n">
-        <x:v>291.1371375937438</x:v>
+        <x:v>291.1641522612093</x:v>
       </x:c>
       <x:c r="C454" s="11" t="n">
-        <x:v>277.65340204527</x:v>
+        <x:v>277.6534020452701</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -4951,7 +4951,7 @@
         <x:v>43739</x:v>
       </x:c>
       <x:c r="B455" s="11" t="n">
-        <x:v>271.2402582790621</x:v>
+        <x:v>271.2654267115101</x:v>
       </x:c>
       <x:c r="C455" s="11" t="n">
         <x:v>257.0059504855193</x:v>
@@ -4962,10 +4962,10 @@
         <x:v>43770</x:v>
       </x:c>
       <x:c r="B456" s="11" t="n">
-        <x:v>142.4202716978492</x:v>
+        <x:v>142.4334869005268</x:v>
       </x:c>
       <x:c r="C456" s="11" t="n">
-        <x:v>71.33336473271503</x:v>
+        <x:v>71.3333647327151</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -4973,7 +4973,7 @@
         <x:v>43800</x:v>
       </x:c>
       <x:c r="B457" s="11" t="n">
-        <x:v>157.1041912298316</x:v>
+        <x:v>157.1187689560488</x:v>
       </x:c>
       <x:c r="C457" s="11" t="n">
         <x:v>85.20324429611617</x:v>
@@ -4984,10 +4984,10 @@
         <x:v>43831</x:v>
       </x:c>
       <x:c r="B458" s="11" t="n">
-        <x:v>189.5514214522204</x:v>
+        <x:v>189.5690099627776</x:v>
       </x:c>
       <x:c r="C458" s="11" t="n">
-        <x:v>161.1583019901425</x:v>
+        <x:v>161.1583019901426</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
@@ -4995,10 +4995,10 @@
         <x:v>43862</x:v>
       </x:c>
       <x:c r="B459" s="11" t="n">
-        <x:v>135.5353313896966</x:v>
+        <x:v>135.5479077375222</x:v>
       </x:c>
       <x:c r="C459" s="11" t="n">
-        <x:v>70.51887951296177</x:v>
+        <x:v>70.51887951296186</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -5006,10 +5006,10 @@
         <x:v>43891</x:v>
       </x:c>
       <x:c r="B460" s="11" t="n">
-        <x:v>275.8655041475972</x:v>
+        <x:v>275.891101757443</x:v>
       </x:c>
       <x:c r="C460" s="11" t="n">
-        <x:v>108.7249163570367</x:v>
+        <x:v>108.7249163570365</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
@@ -5017,10 +5017,10 @@
         <x:v>43922</x:v>
       </x:c>
       <x:c r="B461" s="11" t="n">
-        <x:v>329.4050694095187</x:v>
+        <x:v>329.4356349652739</x:v>
       </x:c>
       <x:c r="C461" s="11" t="n">
-        <x:v>197.1352061720078</x:v>
+        <x:v>197.1352061720077</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
@@ -5028,10 +5028,10 @@
         <x:v>43952</x:v>
       </x:c>
       <x:c r="B462" s="11" t="n">
-        <x:v>366.8050870945731</x:v>
+        <x:v>366.8391230047095</x:v>
       </x:c>
       <x:c r="C462" s="11" t="n">
-        <x:v>237.2876204714396</x:v>
+        <x:v>237.2876204714393</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -5039,10 +5039,10 @@
         <x:v>43983</x:v>
       </x:c>
       <x:c r="B463" s="11" t="n">
-        <x:v>285.9932873716467</x:v>
+        <x:v>286.0198247403231</x:v>
       </x:c>
       <x:c r="C463" s="11" t="n">
-        <x:v>195.7381423365738</x:v>
+        <x:v>195.7381423365739</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -5050,7 +5050,7 @@
         <x:v>44013</x:v>
       </x:c>
       <x:c r="B464" s="11" t="n">
-        <x:v>202.9747695596763</x:v>
+        <x:v>202.9936036251235</x:v>
       </x:c>
       <x:c r="C464" s="11" t="n">
         <x:v>76.9390127722789</x:v>
@@ -5061,10 +5061,10 @@
         <x:v>44044</x:v>
       </x:c>
       <x:c r="B465" s="11" t="n">
-        <x:v>185.3575534580187</x:v>
+        <x:v>185.3747528188088</x:v>
       </x:c>
       <x:c r="C465" s="11" t="n">
-        <x:v>80.6586070971405</x:v>
+        <x:v>80.65860709714055</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -5072,10 +5072,10 @@
         <x:v>44075</x:v>
       </x:c>
       <x:c r="B466" s="11" t="n">
-        <x:v>179.1903557825797</x:v>
+        <x:v>179.2069828879861</x:v>
       </x:c>
       <x:c r="C466" s="11" t="n">
-        <x:v>70.4348012861163</x:v>
+        <x:v>70.43480128611631</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -5083,7 +5083,7 @@
         <x:v>44105</x:v>
       </x:c>
       <x:c r="B467" s="11" t="n">
-        <x:v>242.8286765612018</x:v>
+        <x:v>242.8512086778621</x:v>
       </x:c>
       <x:c r="C467" s="11" t="n">
         <x:v>135.5895196518088</x:v>
@@ -5094,7 +5094,7 @@
         <x:v>44136</x:v>
       </x:c>
       <x:c r="B468" s="11" t="n">
-        <x:v>172.3875431195672</x:v>
+        <x:v>172.4035389907606</x:v>
       </x:c>
       <x:c r="C468" s="11" t="n">
         <x:v>12.13680897470802</x:v>
@@ -5105,10 +5105,10 @@
         <x:v>44166</x:v>
       </x:c>
       <x:c r="B469" s="11" t="n">
-        <x:v>177.8807994277603</x:v>
+        <x:v>177.8973050191966</x:v>
       </x:c>
       <x:c r="C469" s="11" t="n">
-        <x:v>89.16179552174978</x:v>
+        <x:v>89.16179552174988</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -5116,10 +5116,10 @@
         <x:v>44197</x:v>
       </x:c>
       <x:c r="B470" s="11" t="n">
-        <x:v>160.6989830366842</x:v>
+        <x:v>160.7138943242811</x:v>
       </x:c>
       <x:c r="C470" s="11" t="n">
-        <x:v>63.49294682884251</x:v>
+        <x:v>63.49294682884256</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -5127,10 +5127,10 @@
         <x:v>44228</x:v>
       </x:c>
       <x:c r="B471" s="11" t="n">
-        <x:v>175.3693084297252</x:v>
+        <x:v>175.3855809794591</x:v>
       </x:c>
       <x:c r="C471" s="11" t="n">
-        <x:v>133.7251917258528</x:v>
+        <x:v>133.7251917258529</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -5138,7 +5138,7 @@
         <x:v>44256</x:v>
       </x:c>
       <x:c r="B472" s="11" t="n">
-        <x:v>112.0425406154825</x:v>
+        <x:v>112.0529370630183</x:v>
       </x:c>
       <x:c r="C472" s="11" t="n">
         <x:v>48.96100329212265</x:v>
@@ -5149,10 +5149,10 @@
         <x:v>44287</x:v>
       </x:c>
       <x:c r="B473" s="11" t="n">
-        <x:v>110.3575805984075</x:v>
+        <x:v>110.3678206981997</x:v>
       </x:c>
       <x:c r="C473" s="11" t="n">
-        <x:v>59.80663801442098</x:v>
+        <x:v>59.80663801442104</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
@@ -5160,10 +5160,10 @@
         <x:v>44317</x:v>
       </x:c>
       <x:c r="B474" s="11" t="n">
-        <x:v>76.8659377453379</x:v>
+        <x:v>76.87307014955394</x:v>
       </x:c>
       <x:c r="C474" s="11" t="n">
-        <x:v>27.39508175339004</x:v>
+        <x:v>27.39508175339009</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -5171,10 +5171,10 @@
         <x:v>44348</x:v>
       </x:c>
       <x:c r="B475" s="11" t="n">
-        <x:v>130.5533732615526</x:v>
+        <x:v>130.5654873325857</x:v>
       </x:c>
       <x:c r="C475" s="11" t="n">
-        <x:v>100.8558295630176</x:v>
+        <x:v>100.8558295630177</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -5182,7 +5182,7 @@
         <x:v>44378</x:v>
       </x:c>
       <x:c r="B476" s="11" t="n">
-        <x:v>143.0088992334425</x:v>
+        <x:v>143.0221690549752</x:v>
       </x:c>
       <x:c r="C476" s="11" t="n">
         <x:v>125.0435894346694</x:v>
@@ -5193,10 +5193,10 @@
         <x:v>44409</x:v>
       </x:c>
       <x:c r="B477" s="11" t="n">
-        <x:v>111.0652860071604</x:v>
+        <x:v>111.075591775065</x:v>
       </x:c>
       <x:c r="C477" s="11" t="n">
-        <x:v>92.70581476312488</x:v>
+        <x:v>92.7058147631249</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -5204,10 +5204,10 @@
         <x:v>44440</x:v>
       </x:c>
       <x:c r="B478" s="11" t="n">
-        <x:v>129.1903022025022</x:v>
+        <x:v>129.202289793926</x:v>
       </x:c>
       <x:c r="C478" s="11" t="n">
-        <x:v>80.51156566687449</x:v>
+        <x:v>80.51156566687453</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -5215,10 +5215,10 @@
         <x:v>44470</x:v>
       </x:c>
       <x:c r="B479" s="11" t="n">
-        <x:v>92.77062268631467</x:v>
+        <x:v>92.77923088911268</x:v>
       </x:c>
       <x:c r="C479" s="11" t="n">
-        <x:v>27.69515582357776</x:v>
+        <x:v>27.69515582357782</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -5226,10 +5226,10 @@
         <x:v>44501</x:v>
       </x:c>
       <x:c r="B480" s="11" t="n">
-        <x:v>91.73634164947886</x:v>
+        <x:v>91.74485388115308</x:v>
       </x:c>
       <x:c r="C480" s="11" t="n">
-        <x:v>9.875998703844587</x:v>
+        <x:v>9.875998703844559</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -5237,10 +5237,10 @@
         <x:v>44531</x:v>
       </x:c>
       <x:c r="B481" s="11" t="n">
-        <x:v>150.9175598201728</x:v>
+        <x:v>150.9315634877466</x:v>
       </x:c>
       <x:c r="C481" s="11" t="n">
-        <x:v>75.8283506546836</x:v>
+        <x:v>75.82835065468358</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -5248,10 +5248,10 @@
         <x:v>44562</x:v>
       </x:c>
       <x:c r="B482" s="11" t="n">
-        <x:v>122.5956456433937</x:v>
+        <x:v>122.6070213154469</x:v>
       </x:c>
       <x:c r="C482" s="11" t="n">
-        <x:v>71.20629020440646</x:v>
+        <x:v>71.20629020440649</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -5259,10 +5259,10 @@
         <x:v>44593</x:v>
       </x:c>
       <x:c r="B483" s="11" t="n">
-        <x:v>113.4565823258226</x:v>
+        <x:v>113.4671099825435</x:v>
       </x:c>
       <x:c r="C483" s="11" t="n">
-        <x:v>55.36932562314295</x:v>
+        <x:v>55.36932562314293</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
@@ -5270,10 +5270,10 @@
         <x:v>44621</x:v>
       </x:c>
       <x:c r="B484" s="11" t="n">
-        <x:v>169.5775267121277</x:v>
+        <x:v>169.5932618413923</x:v>
       </x:c>
       <x:c r="C484" s="11" t="n">
-        <x:v>33.02052983748557</x:v>
+        <x:v>33.02052983748547</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -5281,10 +5281,10 @@
         <x:v>44652</x:v>
       </x:c>
       <x:c r="B485" s="11" t="n">
-        <x:v>126.0861434586502</x:v>
+        <x:v>126.0978430146247</x:v>
       </x:c>
       <x:c r="C485" s="11" t="n">
-        <x:v>-15.49043042813075</x:v>
+        <x:v>-15.49043042813082</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -5292,10 +5292,10 @@
         <x:v>44682</x:v>
       </x:c>
       <x:c r="B486" s="11" t="n">
-        <x:v>149.322882367037</x:v>
+        <x:v>149.3367380642025</x:v>
       </x:c>
       <x:c r="C486" s="11" t="n">
-        <x:v>36.90379864014539</x:v>
+        <x:v>36.90379864014536</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -5303,10 +5303,10 @@
         <x:v>44713</x:v>
       </x:c>
       <x:c r="B487" s="11" t="n">
-        <x:v>179.813210014663</x:v>
+        <x:v>179.8298949148259</x:v>
       </x:c>
       <x:c r="C487" s="11" t="n">
-        <x:v>79.25537897319008</x:v>
+        <x:v>79.25537897319022</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -5314,7 +5314,7 @@
         <x:v>44743</x:v>
       </x:c>
       <x:c r="B488" s="11" t="n">
-        <x:v>190.8221166736009</x:v>
+        <x:v>190.8398230921967</x:v>
       </x:c>
       <x:c r="C488" s="11" t="n">
         <x:v>64.37245805517469</x:v>
@@ -5325,10 +5325,10 @@
         <x:v>44774</x:v>
       </x:c>
       <x:c r="B489" s="11" t="n">
-        <x:v>119.0431572170769</x:v>
+        <x:v>119.0542032530888</x:v>
       </x:c>
       <x:c r="C489" s="11" t="n">
-        <x:v>5.799024927160133</x:v>
+        <x:v>5.799024927160204</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -5336,7 +5336,7 @@
         <x:v>44805</x:v>
       </x:c>
       <x:c r="B490" s="11" t="n">
-        <x:v>188.6724987836558</x:v>
+        <x:v>188.6900057388202</x:v>
       </x:c>
       <x:c r="C490" s="11" t="n">
         <x:v>86.13111051502318</x:v>
@@ -5347,10 +5347,10 @@
         <x:v>44835</x:v>
       </x:c>
       <x:c r="B491" s="11" t="n">
-        <x:v>172.0675174510932</x:v>
+        <x:v>172.0834836270472</x:v>
       </x:c>
       <x:c r="C491" s="11" t="n">
-        <x:v>32.87466546043905</x:v>
+        <x:v>32.87466546043908</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -5358,10 +5358,10 @@
         <x:v>44866</x:v>
       </x:c>
       <x:c r="B492" s="11" t="n">
-        <x:v>168.6672716446716</x:v>
+        <x:v>168.6829223112044</x:v>
       </x:c>
       <x:c r="C492" s="11" t="n">
-        <x:v>65.75017755699062</x:v>
+        <x:v>65.75017755699068</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -5369,7 +5369,7 @@
         <x:v>44896</x:v>
       </x:c>
       <x:c r="B493" s="11" t="n">
-        <x:v>199.2633851309265</x:v>
+        <x:v>199.2818748163436</x:v>
       </x:c>
       <x:c r="C493" s="11" t="n">
         <x:v>133.5334721706034</x:v>
@@ -5380,10 +5380,10 @@
         <x:v>44927</x:v>
       </x:c>
       <x:c r="B494" s="11" t="n">
-        <x:v>144.1809710659194</x:v>
+        <x:v>144.1943496442086</x:v>
       </x:c>
       <x:c r="C494" s="11" t="n">
-        <x:v>60.93267460317625</x:v>
+        <x:v>60.93267460317638</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -5391,10 +5391,10 @@
         <x:v>44958</x:v>
       </x:c>
       <x:c r="B495" s="11" t="n">
-        <x:v>104.7285053245948</x:v>
+        <x:v>104.7382231014779</x:v>
       </x:c>
       <x:c r="C495" s="11" t="n">
-        <x:v>1.298659345123554</x:v>
+        <x:v>1.298659345123639</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
@@ -5402,10 +5402,10 @@
         <x:v>44986</x:v>
       </x:c>
       <x:c r="B496" s="11" t="n">
-        <x:v>134.235238989807</x:v>
+        <x:v>134.2476947018245</x:v>
       </x:c>
       <x:c r="C496" s="11" t="n">
-        <x:v>15.62445501876894</x:v>
+        <x:v>15.62445501876896</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -5413,10 +5413,10 @@
         <x:v>45017</x:v>
       </x:c>
       <x:c r="B497" s="11" t="n">
-        <x:v>100.5330243342957</x:v>
+        <x:v>100.5423528117416</x:v>
       </x:c>
       <x:c r="C497" s="11" t="n">
-        <x:v>-23.33505036004</x:v>
+        <x:v>-23.33505036003993</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -5424,10 +5424,10 @@
         <x:v>45047</x:v>
       </x:c>
       <x:c r="B498" s="11" t="n">
-        <x:v>82.25580177946419</x:v>
+        <x:v>82.26343431013531</x:v>
       </x:c>
       <x:c r="C498" s="11" t="n">
-        <x:v>-27.70150422202948</x:v>
+        <x:v>-27.70150422202937</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -5435,10 +5435,10 @@
         <x:v>45078</x:v>
       </x:c>
       <x:c r="B499" s="11" t="n">
-        <x:v>96.12106210156391</x:v>
+        <x:v>96.12998119223907</x:v>
       </x:c>
       <x:c r="C499" s="11" t="n">
-        <x:v>12.26405768947872</x:v>
+        <x:v>12.26405768947879</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -5446,10 +5446,10 @@
         <x:v>45108</x:v>
       </x:c>
       <x:c r="B500" s="11" t="n">
-        <x:v>88.51121811948033</x:v>
+        <x:v>88.51943109136097</x:v>
       </x:c>
       <x:c r="C500" s="11" t="n">
-        <x:v>6.424020990626104</x:v>
+        <x:v>6.42402099062619</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -5457,10 +5457,10 @@
         <x:v>45139</x:v>
       </x:c>
       <x:c r="B501" s="11" t="n">
-        <x:v>118.1742493023512</x:v>
+        <x:v>118.1852147122411</x:v>
       </x:c>
       <x:c r="C501" s="11" t="n">
-        <x:v>60.77329424011787</x:v>
+        <x:v>60.7732942401179</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -5468,10 +5468,10 @@
         <x:v>45170</x:v>
       </x:c>
       <x:c r="B502" s="11" t="n">
-        <x:v>95.87503892484254</x:v>
+        <x:v>95.88393518698281</x:v>
       </x:c>
       <x:c r="C502" s="11" t="n">
-        <x:v>25.88405597291781</x:v>
+        <x:v>25.88405597291776</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -5479,10 +5479,10 @@
         <x:v>45200</x:v>
       </x:c>
       <x:c r="B503" s="11" t="n">
-        <x:v>125.7537948023662</x:v>
+        <x:v>125.7654635196491</x:v>
       </x:c>
       <x:c r="C503" s="11" t="n">
-        <x:v>16.9163427326928</x:v>
+        <x:v>16.91634273269275</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -5490,10 +5490,10 @@
         <x:v>45231</x:v>
       </x:c>
       <x:c r="B504" s="11" t="n">
-        <x:v>114.9542862657304</x:v>
+        <x:v>114.9649528946699</x:v>
       </x:c>
       <x:c r="C504" s="11" t="n">
-        <x:v>-4.175556651759365</x:v>
+        <x:v>-4.175556651759379</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -5501,7 +5501,7 @@
         <x:v>45261</x:v>
       </x:c>
       <x:c r="B505" s="11" t="n">
-        <x:v>114.2436339739843</x:v>
+        <x:v>114.2542346613696</x:v>
       </x:c>
       <x:c r="C505" s="11" t="n">
         <x:v>22.54057176843281</x:v>
@@ -5512,10 +5512,10 @@
         <x:v>45292</x:v>
       </x:c>
       <x:c r="B506" s="11" t="n">
-        <x:v>100.7770858944842</x:v>
+        <x:v>100.7864370184462</x:v>
       </x:c>
       <x:c r="C506" s="11" t="n">
-        <x:v>20.58679883400552</x:v>
+        <x:v>20.58679883400555</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -5523,10 +5523,10 @@
         <x:v>45323</x:v>
       </x:c>
       <x:c r="B507" s="11" t="n">
-        <x:v>127.9253044623614</x:v>
+        <x:v>127.9371746744169</x:v>
       </x:c>
       <x:c r="C507" s="11" t="n">
-        <x:v>69.86626347342066</x:v>
+        <x:v>69.86626347342067</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -5534,10 +5534,10 @@
         <x:v>45352</x:v>
       </x:c>
       <x:c r="B508" s="11" t="n">
-        <x:v>128.6451581573461</x:v>
+        <x:v>128.6570951647557</x:v>
       </x:c>
       <x:c r="C508" s="11" t="n">
-        <x:v>100.439427724117</x:v>
+        <x:v>100.4394277241171</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -5545,10 +5545,10 @@
         <x:v>45383</x:v>
       </x:c>
       <x:c r="B509" s="11" t="n">
-        <x:v>86.43781634156433</x:v>
+        <x:v>86.44583692212034</x:v>
       </x:c>
       <x:c r="C509" s="11" t="n">
-        <x:v>27.94600357280568</x:v>
+        <x:v>27.94600357280574</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -5556,10 +5556,10 @@
         <x:v>45413</x:v>
       </x:c>
       <x:c r="B510" s="11" t="n">
-        <x:v>101.0838343296338</x:v>
+        <x:v>101.0932139168384</x:v>
       </x:c>
       <x:c r="C510" s="11" t="n">
-        <x:v>36.72145133245465</x:v>
+        <x:v>36.72145133245466</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -5567,7 +5567,7 @@
         <x:v>45444</x:v>
       </x:c>
       <x:c r="B511" s="11" t="n">
-        <x:v>142.3585778396306</x:v>
+        <x:v>142.3717873177239</x:v>
       </x:c>
       <x:c r="C511" s="11" t="n">
         <x:v>77.50952405642816</x:v>
@@ -5578,7 +5578,7 @@
         <x:v>45474</x:v>
       </x:c>
       <x:c r="B512" s="11" t="n">
-        <x:v>102.6276924739936</x:v>
+        <x:v>102.6372153160737</x:v>
       </x:c>
       <x:c r="C512" s="11" t="n">
         <x:v>15.58240766491157</x:v>
@@ -5589,10 +5589,10 @@
         <x:v>45505</x:v>
       </x:c>
       <x:c r="B513" s="11" t="n">
-        <x:v>80.18153271430978</x:v>
+        <x:v>80.18897277318052</x:v>
       </x:c>
       <x:c r="C513" s="11" t="n">
-        <x:v>-12.23212121897102</x:v>
+        <x:v>-12.23212121897109</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -5600,10 +5600,10 @@
         <x:v>45536</x:v>
       </x:c>
       <x:c r="B514" s="11" t="n">
-        <x:v>101.3580715361711</x:v>
+        <x:v>101.3674765698955</x:v>
       </x:c>
       <x:c r="C514" s="11" t="n">
-        <x:v>6.087564235834137</x:v>
+        <x:v>6.08756423583425</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -5611,10 +5611,10 @@
         <x:v>45566</x:v>
       </x:c>
       <x:c r="B515" s="11" t="n">
-        <x:v>99.83895102894816</x:v>
+        <x:v>99.84821510320693</x:v>
       </x:c>
       <x:c r="C515" s="11" t="n">
-        <x:v>3.966705089061477</x:v>
+        <x:v>3.96670508906152</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
@@ -5622,10 +5622,10 @@
         <x:v>45597</x:v>
       </x:c>
       <x:c r="B516" s="11" t="n">
-        <x:v>194.8096004183577</x:v>
+        <x:v>194.8276768362888</x:v>
       </x:c>
       <x:c r="C516" s="11" t="n">
-        <x:v>27.47645152944769</x:v>
+        <x:v>27.47645152944759</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -5633,10 +5633,10 @@
         <x:v>45627</x:v>
       </x:c>
       <x:c r="B517" s="11" t="n">
-        <x:v>254.7358940723874</x:v>
+        <x:v>254.7595310619064</x:v>
       </x:c>
       <x:c r="C517" s="11" t="n">
-        <x:v>83.15839485715847</x:v>
+        <x:v>83.15839485715834</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -5644,10 +5644,10 @@
         <x:v>45658</x:v>
       </x:c>
       <x:c r="B518" s="11" t="n">
-        <x:v>222.2356170316463</x:v>
+        <x:v>222.2562383146016</x:v>
       </x:c>
       <x:c r="C518" s="11" t="n">
-        <x:v>40.78309561066067</x:v>
+        <x:v>40.78309561066057</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -5655,10 +5655,10 @@
         <x:v>45689</x:v>
       </x:c>
       <x:c r="B519" s="11" t="n">
-        <x:v>248.1381698167848</x:v>
+        <x:v>248.1611946022811</x:v>
       </x:c>
       <x:c r="C519" s="11" t="n">
-        <x:v>56.36655941184218</x:v>
+        <x:v>56.36655941184215</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -5666,10 +5666,10 @@
         <x:v>45717</x:v>
       </x:c>
       <x:c r="B520" s="11" t="n">
-        <x:v>346.5275205297081</x:v>
+        <x:v>346.5596748807886</x:v>
       </x:c>
       <x:c r="C520" s="11" t="n">
-        <x:v>41.72731147633394</x:v>
+        <x:v>41.72731147633383</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -5677,10 +5677,10 @@
         <x:v>45748</x:v>
       </x:c>
       <x:c r="B521" s="11" t="n">
-        <x:v>571.1301188688376</x:v>
+        <x:v>571.1831141354954</x:v>
       </x:c>
       <x:c r="C521" s="11" t="n">
-        <x:v>259.5692369442045</x:v>
+        <x:v>259.5692369442042</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -5688,10 +5688,10 @@
         <x:v>45778</x:v>
       </x:c>
       <x:c r="B522" s="11" t="n">
-        <x:v>337.896906593523</x:v>
+        <x:v>337.9282601083809</x:v>
       </x:c>
       <x:c r="C522" s="11" t="n">
-        <x:v>50.08144026201209</x:v>
+        <x:v>50.08144026201203</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -5699,10 +5699,10 @@
         <x:v>45809</x:v>
       </x:c>
       <x:c r="B523" s="11" t="n">
-        <x:v>388.5656283747545</x:v>
+        <x:v>388.6016834494379</x:v>
       </x:c>
       <x:c r="C523" s="11" t="n">
-        <x:v>234.0307591737168</x:v>
+        <x:v>234.0307591737169</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
@@ -5710,10 +5710,10 @@
         <x:v>45839</x:v>
       </x:c>
       <x:c r="B524" s="11" t="n">
-        <x:v>463.9381850709005</x:v>
+        <x:v>463.9812339787034</x:v>
       </x:c>
       <x:c r="C524" s="11" t="n">
-        <x:v>289.7451774586029</x:v>
+        <x:v>289.7451774586032</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -5721,10 +5721,10 @@
         <x:v>45870</x:v>
       </x:c>
       <x:c r="B525" s="11" t="n">
-        <x:v>240.415605973183</x:v>
+        <x:v>240.4379141805885</x:v>
       </x:c>
       <x:c r="C525" s="11" t="n">
-        <x:v>73.69525247655801</x:v>
+        <x:v>73.69525247655815</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -5732,10 +5732,10 @@
         <x:v>45901</x:v>
       </x:c>
       <x:c r="B526" s="11" t="n">
-        <x:v>242.8305582903328</x:v>
+        <x:v>242.853090581599</x:v>
       </x:c>
       <x:c r="C526" s="11" t="n">
-        <x:v>88.32914428838541</x:v>
+        <x:v>88.32914428838544</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -5743,7 +5743,7 @@
         <x:v>45931</x:v>
       </x:c>
       <x:c r="B527" s="11" t="n">
-        <x:v>294.3342036337785</x:v>
+        <x:v>294.3615149575781</x:v>
       </x:c>
       <x:c r="C527" s="11" t="n">
         <x:v>115.7487507898298</x:v>
@@ -5754,10 +5754,10 @@
         <x:v>45962</x:v>
       </x:c>
       <x:c r="B528" s="11" t="n">
-        <x:v>208.5401720055013</x:v>
+        <x:v>208.5595224856445</x:v>
       </x:c>
       <x:c r="C528" s="11" t="n">
-        <x:v>25.68388422758531</x:v>
+        <x:v>25.68388422758527</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -5765,10 +5765,10 @@
         <x:v>45992</x:v>
       </x:c>
       <x:c r="B529" s="11" t="n">
-        <x:v>263.8459404536204</x:v>
+        <x:v>263.8704227659849</x:v>
       </x:c>
       <x:c r="C529" s="11" t="n">
-        <x:v>147.6353739934368</x:v>
+        <x:v>147.6353739934369</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -5776,10 +5776,10 @@
         <x:v>46023</x:v>
       </x:c>
       <x:c r="B530" s="11" t="n">
-        <x:v>253.2761649979227</x:v>
+        <x:v>253.2996665389179</x:v>
       </x:c>
       <x:c r="C530" s="11" t="n">
-        <x:v>61.83750548698296</x:v>
+        <x:v>61.83750548698301</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -5787,10 +5787,10 @@
         <x:v>46054</x:v>
       </x:c>
       <x:c r="B531" s="11" t="n">
-        <x:v>202.0970790765369</x:v>
+        <x:v>202.115831700926</x:v>
       </x:c>
       <x:c r="C531" s="11" t="n">
-        <x:v>21.87961834992562</x:v>
+        <x:v>21.87961834992564</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -5798,10 +5798,10 @@
         <x:v>46082</x:v>
       </x:c>
       <x:c r="B532" s="11" t="n">
-        <x:v>279.6761416542947</x:v>
+        <x:v>279.7020928538815</x:v>
       </x:c>
       <x:c r="C532" s="11" t="n">
-        <x:v>60.98282630318935</x:v>
+        <x:v>60.98282630318916</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -5809,10 +5809,10 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="B533" s="11" t="n">
-        <x:v>294.0531316115304</x:v>
+        <x:v>294.0804168546064</x:v>
       </x:c>
       <x:c r="C533" s="11" t="n">
-        <x:v>108.9328884087401</x:v>
+        <x:v>108.93288840874</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
@@ -5820,10 +5820,10 @@
         <x:v>46143</x:v>
       </x:c>
       <x:c r="B534" s="11" t="n">
-        <x:v>209.6603251169854</x:v>
+        <x:v>209.6797795363376</x:v>
       </x:c>
       <x:c r="C534" s="11" t="n">
-        <x:v>19.29625447194417</x:v>
+        <x:v>19.29625447194425</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -5831,10 +5831,10 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B535" s="11" t="n">
-        <x:v>189.6884500859727</x:v>
+        <x:v>189.7060513114415</x:v>
       </x:c>
       <x:c r="C535" s="11" t="n">
-        <x:v>27.54781087730773</x:v>
+        <x:v>27.54781087730788</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -5842,10 +5842,10 @@
         <x:v>46204</x:v>
       </x:c>
       <x:c r="B536" s="11" t="n">
-        <x:v>151.5161281248731</x:v>
+        <x:v>151.5301873337048</x:v>
       </x:c>
       <x:c r="C536" s="11" t="n">
-        <x:v>24.61251930021614</x:v>
+        <x:v>24.61251930021194</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -5853,7 +5853,7 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B537" s="13" t="n">
-        <x:v>95.67053277111685</x:v>
+        <x:v>90.70585639739723</x:v>
       </x:c>
       <x:c r="C537" s="13"/>
     </x:row>

--- a/files/ireland-epu-index.xlsx
+++ b/files/ireland-epu-index.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" r:id="Rfd3d6a445aac410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" r:id="R7d484ea7e5f54b0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,7 +334,7 @@
         <x:v>29952</x:v>
       </x:c>
       <x:c r="B2" s="9" t="n">
-        <x:v>79.4231462894064</x:v>
+        <x:v>79.40484963206504</x:v>
       </x:c>
       <x:c r="C2" s="9"/>
     </x:row>
@@ -343,7 +343,7 @@
         <x:v>29983</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>46.68609860202226</x:v>
+        <x:v>46.67534355656468</x:v>
       </x:c>
       <x:c r="C3" s="11"/>
     </x:row>
@@ -352,7 +352,7 @@
         <x:v>30011</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>46.4727013229645</x:v>
+        <x:v>46.46199543769606</x:v>
       </x:c>
       <x:c r="C4" s="11"/>
     </x:row>
@@ -361,7 +361,7 @@
         <x:v>30042</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>80.52349467246826</x:v>
+        <x:v>80.50494452860238</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
     </x:row>
@@ -370,7 +370,7 @@
         <x:v>30072</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>34.14112926138839</x:v>
+        <x:v>34.13326419216705</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
     </x:row>
@@ -379,7 +379,7 @@
         <x:v>30103</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>25.78609514400516</x:v>
+        <x:v>25.78015481843178</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
     </x:row>
@@ -388,7 +388,7 @@
         <x:v>30133</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>47.12922788050386</x:v>
+        <x:v>47.11837075164938</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
     </x:row>
@@ -397,7 +397,7 @@
         <x:v>30164</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>45.94976555821614</x:v>
+        <x:v>45.93918014131172</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
     </x:row>
@@ -406,7 +406,7 @@
         <x:v>30195</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>44.40172532817998</x:v>
+        <x:v>44.39149653227287</x:v>
       </x:c>
       <x:c r="C10" s="11"/>
     </x:row>
@@ -415,7 +415,7 @@
         <x:v>30225</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>38.46709583678322</x:v>
+        <x:v>38.45823419752156</x:v>
       </x:c>
       <x:c r="C11" s="11"/>
     </x:row>
@@ -424,7 +424,7 @@
         <x:v>30256</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>73.0908682779019</x:v>
+        <x:v>73.07403038323088</x:v>
       </x:c>
       <x:c r="C12" s="11"/>
     </x:row>
@@ -433,7 +433,7 @@
         <x:v>30286</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>56.67308823533521</x:v>
+        <x:v>56.66003249372382</x:v>
       </x:c>
       <x:c r="C13" s="11"/>
     </x:row>
@@ -442,7 +442,7 @@
         <x:v>30317</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>45.75563539513038</x:v>
+        <x:v>45.74509469986239</x:v>
       </x:c>
       <x:c r="C14" s="11"/>
     </x:row>
@@ -451,7 +451,7 @@
         <x:v>30348</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>50.30975906670903</x:v>
+        <x:v>50.29816924100237</x:v>
       </x:c>
       <x:c r="C15" s="11"/>
     </x:row>
@@ -460,7 +460,7 @@
         <x:v>30376</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>54.31610970150233</x:v>
+        <x:v>54.30359693546681</x:v>
       </x:c>
       <x:c r="C16" s="11"/>
     </x:row>
@@ -469,7 +469,7 @@
         <x:v>30407</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>48.65110919747846</x:v>
+        <x:v>48.63990147383806</x:v>
       </x:c>
       <x:c r="C17" s="11"/>
     </x:row>
@@ -478,7 +478,7 @@
         <x:v>30437</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>36.51329215641891</x:v>
+        <x:v>36.50488061361051</x:v>
       </x:c>
       <x:c r="C18" s="11"/>
     </x:row>
@@ -487,7 +487,7 @@
         <x:v>30468</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>49.63607506198981</x:v>
+        <x:v>49.62464043241886</x:v>
       </x:c>
       <x:c r="C19" s="11"/>
     </x:row>
@@ -496,7 +496,7 @@
         <x:v>30498</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>33.79177817127186</x:v>
+        <x:v>33.7839935818286</x:v>
       </x:c>
       <x:c r="C20" s="11"/>
     </x:row>
@@ -505,7 +505,7 @@
         <x:v>30529</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>19.60132822561298</x:v>
+        <x:v>19.59681268067759</x:v>
       </x:c>
       <x:c r="C21" s="11"/>
     </x:row>
@@ -514,7 +514,7 @@
         <x:v>30560</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>31.61545825423608</x:v>
+        <x:v>31.60817502216341</x:v>
       </x:c>
       <x:c r="C22" s="11"/>
     </x:row>
@@ -523,7 +523,7 @@
         <x:v>30590</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>14.32560841333619</x:v>
+        <x:v>14.32230823246209</x:v>
       </x:c>
       <x:c r="C23" s="11"/>
     </x:row>
@@ -532,7 +532,7 @@
         <x:v>30621</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>24.41137584193353</x:v>
+        <x:v>24.40575220953067</x:v>
       </x:c>
       <x:c r="C24" s="11"/>
     </x:row>
@@ -541,7 +541,7 @@
         <x:v>30651</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>42.52777420799865</x:v>
+        <x:v>42.51797711296368</x:v>
       </x:c>
       <x:c r="C25" s="11"/>
     </x:row>
@@ -550,7 +550,7 @@
         <x:v>30682</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>11.59006509822677</x:v>
+        <x:v>11.58739510264521</x:v>
       </x:c>
       <x:c r="C26" s="11"/>
     </x:row>
@@ -559,7 +559,7 @@
         <x:v>30713</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>46.45103572794216</x:v>
+        <x:v>46.44033483376241</x:v>
       </x:c>
       <x:c r="C27" s="11"/>
     </x:row>
@@ -568,7 +568,7 @@
         <x:v>30742</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>40.40230521589906</x:v>
+        <x:v>40.39299776374094</x:v>
       </x:c>
       <x:c r="C28" s="11"/>
     </x:row>
@@ -577,7 +577,7 @@
         <x:v>30773</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>46.4727013229645</x:v>
+        <x:v>46.46199543769606</x:v>
       </x:c>
       <x:c r="C29" s="11"/>
     </x:row>
@@ -586,7 +586,7 @@
         <x:v>30803</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>46.58859334621381</x:v>
+        <x:v>46.57786076297711</x:v>
       </x:c>
       <x:c r="C30" s="11"/>
     </x:row>
@@ -595,7 +595,7 @@
         <x:v>30834</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>78.07600272413795</x:v>
+        <x:v>78.05801640736298</x:v>
       </x:c>
       <x:c r="C31" s="11"/>
     </x:row>
@@ -604,7 +604,7 @@
         <x:v>30864</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>11.37102524838353</x:v>
+        <x:v>11.36840571286638</x:v>
       </x:c>
       <x:c r="C32" s="11"/>
     </x:row>
@@ -613,7 +613,7 @@
         <x:v>30895</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>22.55670371195235</x:v>
+        <x:v>22.55150733913347</x:v>
       </x:c>
       <x:c r="C33" s="11"/>
     </x:row>
@@ -622,7 +622,7 @@
         <x:v>30926</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>64.83130962525995</x:v>
+        <x:v>64.81637447961761</x:v>
       </x:c>
       <x:c r="C34" s="11"/>
     </x:row>
@@ -631,7 +631,7 @@
         <x:v>30956</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>50.00676124048216</x:v>
+        <x:v>49.99524121618302</x:v>
       </x:c>
       <x:c r="C35" s="11"/>
     </x:row>
@@ -640,7 +640,7 @@
         <x:v>30987</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>20.0898200734809</x:v>
+        <x:v>20.0851919950037</x:v>
       </x:c>
       <x:c r="C36" s="11"/>
     </x:row>
@@ -649,7 +649,7 @@
         <x:v>31017</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>70.07699355508514</x:v>
+        <x:v>70.06084996472775</x:v>
       </x:c>
       <x:c r="C37" s="11"/>
     </x:row>
@@ -658,7 +658,7 @@
         <x:v>31048</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>29.56952505829651</x:v>
+        <x:v>29.56271314649227</x:v>
       </x:c>
       <x:c r="C38" s="11"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>31079</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>15.61128597963711</x:v>
+        <x:v>15.60768961807789</x:v>
       </x:c>
       <x:c r="C39" s="11"/>
     </x:row>
@@ -676,7 +676,7 @@
         <x:v>31107</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>41.58839286936969</x:v>
+        <x:v>41.57881217898838</x:v>
       </x:c>
       <x:c r="C40" s="11"/>
     </x:row>
@@ -685,7 +685,7 @@
         <x:v>31138</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>41.86917510495682</x:v>
+        <x:v>41.8595297309588</x:v>
       </x:c>
       <x:c r="C41" s="11"/>
     </x:row>
@@ -694,7 +694,7 @@
         <x:v>31168</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>30.06510369055846</x:v>
+        <x:v>30.0581776126346</x:v>
       </x:c>
       <x:c r="C42" s="11"/>
     </x:row>
@@ -703,7 +703,7 @@
         <x:v>31199</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>23.71236759301365</x:v>
+        <x:v>23.70690499067577</x:v>
       </x:c>
       <x:c r="C43" s="11"/>
     </x:row>
@@ -712,7 +712,7 @@
         <x:v>31229</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>22.34424821412717</x:v>
+        <x:v>22.3391007845399</x:v>
       </x:c>
       <x:c r="C44" s="11"/>
     </x:row>
@@ -721,7 +721,7 @@
         <x:v>31260</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>38.00056126484969</x:v>
+        <x:v>37.99180710084682</x:v>
       </x:c>
       <x:c r="C45" s="11"/>
     </x:row>
@@ -730,7 +730,7 @@
         <x:v>31291</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>20.82548943157677</x:v>
+        <x:v>20.82069187743924</x:v>
       </x:c>
       <x:c r="C46" s="11"/>
     </x:row>
@@ -739,7 +739,7 @@
         <x:v>31321</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>24.42669638847274</x:v>
+        <x:v>24.42106922668577</x:v>
       </x:c>
       <x:c r="C47" s="11"/>
     </x:row>
@@ -748,7 +748,7 @@
         <x:v>31352</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>22.47488803694689</x:v>
+        <x:v>22.4697105119506</x:v>
       </x:c>
       <x:c r="C48" s="11"/>
     </x:row>
@@ -757,7 +757,7 @@
         <x:v>31382</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>20.76299734025921</x:v>
+        <x:v>20.75821418238317</x:v>
       </x:c>
       <x:c r="C49" s="11"/>
     </x:row>
@@ -766,7 +766,7 @@
         <x:v>31413</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>59.93591893433342</x:v>
+        <x:v>59.92211153658585</x:v>
       </x:c>
       <x:c r="C50" s="11"/>
     </x:row>
@@ -775,7 +775,7 @@
         <x:v>31444</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>37.66320532308683</x:v>
+        <x:v>37.65452887554769</x:v>
       </x:c>
       <x:c r="C51" s="11"/>
     </x:row>
@@ -784,7 +784,7 @@
         <x:v>31472</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>42.4929510561395</x:v>
+        <x:v>42.48316198329084</x:v>
       </x:c>
       <x:c r="C52" s="11"/>
     </x:row>
@@ -793,7 +793,7 @@
         <x:v>31503</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>41.56757264765785</x:v>
+        <x:v>41.55799675361716</x:v>
       </x:c>
       <x:c r="C53" s="11"/>
     </x:row>
@@ -802,7 +802,7 @@
         <x:v>31533</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>30.24449721844217</x:v>
+        <x:v>30.23752981375071</x:v>
       </x:c>
       <x:c r="C54" s="11"/>
     </x:row>
@@ -811,7 +811,7 @@
         <x:v>31564</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>26.22259549131397</x:v>
+        <x:v>26.21655460944615</x:v>
       </x:c>
       <x:c r="C55" s="11"/>
     </x:row>
@@ -820,7 +820,7 @@
         <x:v>31594</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>31.82085834071152</x:v>
+        <x:v>31.81352779075765</x:v>
       </x:c>
       <x:c r="C56" s="11"/>
     </x:row>
@@ -829,7 +829,7 @@
         <x:v>31625</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>103.8983996911377</x:v>
+        <x:v>103.8744646859625</x:v>
       </x:c>
       <x:c r="C57" s="11"/>
     </x:row>
@@ -838,7 +838,7 @@
         <x:v>31656</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>89.23824185255185</x:v>
+        <x:v>89.2176840981792</x:v>
       </x:c>
       <x:c r="C58" s="11"/>
     </x:row>
@@ -847,7 +847,7 @@
         <x:v>31686</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>45.43183758136167</x:v>
+        <x:v>45.42137147918051</x:v>
       </x:c>
       <x:c r="C59" s="11"/>
     </x:row>
@@ -856,7 +856,7 @@
         <x:v>31717</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>59.00972789897525</x:v>
+        <x:v>58.99613386723998</x:v>
       </x:c>
       <x:c r="C60" s="11"/>
     </x:row>
@@ -865,7 +865,7 @@
         <x:v>31747</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>63.94584968768101</x:v>
+        <x:v>63.93111852485508</x:v>
       </x:c>
       <x:c r="C61" s="11"/>
     </x:row>
@@ -874,7 +874,7 @@
         <x:v>31778</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>48.41157276971166</x:v>
+        <x:v>48.40042022791867</x:v>
       </x:c>
       <x:c r="C62" s="11"/>
     </x:row>
@@ -883,7 +883,7 @@
         <x:v>31809</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>70.88607828431694</x:v>
+        <x:v>70.86974830564908</x:v>
       </x:c>
       <x:c r="C63" s="11"/>
     </x:row>
@@ -892,7 +892,7 @@
         <x:v>31837</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>53.14338604947297</x:v>
+        <x:v>53.13114344300453</x:v>
       </x:c>
       <x:c r="C64" s="11"/>
     </x:row>
@@ -901,7 +901,7 @@
         <x:v>31868</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
-        <x:v>70.00038539092448</x:v>
+        <x:v>69.98425944873888</x:v>
       </x:c>
       <x:c r="C65" s="11"/>
     </x:row>
@@ -910,7 +910,7 @@
         <x:v>31898</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
-        <x:v>61.2653266702886</x:v>
+        <x:v>61.25121301776585</x:v>
       </x:c>
       <x:c r="C66" s="11"/>
     </x:row>
@@ -919,7 +919,7 @@
         <x:v>31929</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>68.43232942062906</x:v>
+        <x:v>68.41656471045354</x:v>
       </x:c>
       <x:c r="C67" s="11"/>
     </x:row>
@@ -928,7 +928,7 @@
         <x:v>31959</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>26.60575056514245</x:v>
+        <x:v>26.59962141609532</x:v>
       </x:c>
       <x:c r="C68" s="11"/>
     </x:row>
@@ -937,7 +937,7 @@
         <x:v>31990</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>27.98302317460791</x:v>
+        <x:v>27.97657674418654</x:v>
       </x:c>
       <x:c r="C69" s="11"/>
     </x:row>
@@ -946,7 +946,7 @@
         <x:v>32021</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>18.67128994011616</x:v>
+        <x:v>18.66698864748151</x:v>
       </x:c>
       <x:c r="C70" s="11"/>
     </x:row>
@@ -955,7 +955,7 @@
         <x:v>32051</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>37.68151865836015</x:v>
+        <x:v>37.67283799199015</x:v>
       </x:c>
       <x:c r="C71" s="11"/>
     </x:row>
@@ -964,7 +964,7 @@
         <x:v>32082</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>34.66236787606609</x:v>
+        <x:v>34.65438272945205</x:v>
       </x:c>
       <x:c r="C72" s="11"/>
     </x:row>
@@ -973,7 +973,7 @@
         <x:v>32112</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>35.26241210236264</x:v>
+        <x:v>35.25428872395963</x:v>
       </x:c>
       <x:c r="C73" s="11"/>
     </x:row>
@@ -982,7 +982,7 @@
         <x:v>32143</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>67.98408272136729</x:v>
+        <x:v>67.9684212734855</x:v>
       </x:c>
       <x:c r="C74" s="11"/>
     </x:row>
@@ -991,7 +991,7 @@
         <x:v>32174</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>27.88528558694808</x:v>
+        <x:v>27.87886167226972</x:v>
       </x:c>
       <x:c r="C75" s="11"/>
     </x:row>
@@ -1000,7 +1000,7 @@
         <x:v>32203</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>35.67655100130187</x:v>
+        <x:v>35.66833221799639</x:v>
       </x:c>
       <x:c r="C76" s="11"/>
     </x:row>
@@ -1009,7 +1009,7 @@
         <x:v>32234</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>42.92604021756839</x:v>
+        <x:v>42.91615137425791</x:v>
       </x:c>
       <x:c r="C77" s="11"/>
     </x:row>
@@ -1018,7 +1018,7 @@
         <x:v>32264</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>33.22134957203117</x:v>
+        <x:v>33.2136963918446</x:v>
       </x:c>
       <x:c r="C78" s="11"/>
     </x:row>
@@ -1027,7 +1027,7 @@
         <x:v>32295</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>11.81434638071949</x:v>
+        <x:v>11.81162471760818</x:v>
       </x:c>
       <x:c r="C79" s="11"/>
     </x:row>
@@ -1036,7 +1036,7 @@
         <x:v>32325</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>50.68373828494771</x:v>
+        <x:v>50.67206230589748</x:v>
       </x:c>
       <x:c r="C80" s="11"/>
     </x:row>
@@ -1045,7 +1045,7 @@
         <x:v>32356</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
-        <x:v>11.89900062535061</x:v>
+        <x:v>11.89625946049732</x:v>
       </x:c>
       <x:c r="C81" s="11"/>
     </x:row>
@@ -1054,7 +1054,7 @@
         <x:v>32387</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
-        <x:v>11.31832420442974</x:v>
+        <x:v>11.315716809617</x:v>
       </x:c>
       <x:c r="C82" s="11"/>
     </x:row>
@@ -1063,7 +1063,7 @@
         <x:v>32417</x:v>
       </x:c>
       <x:c r="B83" s="11" t="n">
-        <x:v>49.21243857497426</x:v>
+        <x:v>49.20110153825883</x:v>
       </x:c>
       <x:c r="C83" s="11"/>
     </x:row>
@@ -1072,7 +1072,7 @@
         <x:v>32448</x:v>
       </x:c>
       <x:c r="B84" s="11" t="n">
-        <x:v>49.39982529967669</x:v>
+        <x:v>49.38844509480621</x:v>
       </x:c>
       <x:c r="C84" s="11"/>
     </x:row>
@@ -1081,7 +1081,7 @@
         <x:v>32478</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>45.90178361629417</x:v>
+        <x:v>45.89120925295777</x:v>
       </x:c>
       <x:c r="C85" s="11"/>
     </x:row>
@@ -1090,7 +1090,7 @@
         <x:v>32509</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>60.90580754872382</x:v>
+        <x:v>60.89177671838178</x:v>
       </x:c>
       <x:c r="C86" s="11"/>
     </x:row>
@@ -1099,7 +1099,7 @@
         <x:v>32540</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
-        <x:v>38.48492531341673</x:v>
+        <x:v>38.4760595667904</x:v>
       </x:c>
       <x:c r="C87" s="11"/>
     </x:row>
@@ -1108,7 +1108,7 @@
         <x:v>32568</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>33.51637232119077</x:v>
+        <x:v>33.50865117680986</x:v>
       </x:c>
       <x:c r="C88" s="11"/>
     </x:row>
@@ -1117,7 +1117,7 @@
         <x:v>32599</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>67.43196510316453</x:v>
+        <x:v>67.41643084625092</x:v>
       </x:c>
       <x:c r="C89" s="11"/>
     </x:row>
@@ -1126,7 +1126,7 @@
         <x:v>32629</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>47.8780777340639</x:v>
+        <x:v>47.86704809316714</x:v>
       </x:c>
       <x:c r="C90" s="11"/>
     </x:row>
@@ -1135,7 +1135,7 @@
         <x:v>32660</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
-        <x:v>65.34461676051671</x:v>
+        <x:v>65.32956336465132</x:v>
       </x:c>
       <x:c r="C91" s="11"/>
     </x:row>
@@ -1144,7 +1144,7 @@
         <x:v>32690</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
-        <x:v>44.42548227057067</x:v>
+        <x:v>44.41524800179255</x:v>
       </x:c>
       <x:c r="C92" s="11"/>
     </x:row>
@@ -1153,7 +1153,7 @@
         <x:v>32721</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
-        <x:v>28.49781245321821</x:v>
+        <x:v>28.4912474311334</x:v>
       </x:c>
       <x:c r="C93" s="11"/>
     </x:row>
@@ -1162,7 +1162,7 @@
         <x:v>32752</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
-        <x:v>18.02414465203254</x:v>
+        <x:v>18.01999244182713</x:v>
       </x:c>
       <x:c r="C94" s="11"/>
     </x:row>
@@ -1171,7 +1171,7 @@
         <x:v>32782</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
-        <x:v>72.32685223318516</x:v>
+        <x:v>72.31019034438178</x:v>
       </x:c>
       <x:c r="C95" s="11"/>
     </x:row>
@@ -1180,7 +1180,7 @@
         <x:v>32813</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
-        <x:v>83.07276274506911</x:v>
+        <x:v>83.05362532801429</x:v>
       </x:c>
       <x:c r="C96" s="11"/>
     </x:row>
@@ -1189,7 +1189,7 @@
         <x:v>32843</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
-        <x:v>45.83562040502158</x:v>
+        <x:v>45.82506128366012</x:v>
       </x:c>
       <x:c r="C97" s="11"/>
     </x:row>
@@ -1198,7 +1198,7 @@
         <x:v>32874</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
-        <x:v>26.61939803914355</x:v>
+        <x:v>26.61326574613692</x:v>
       </x:c>
       <x:c r="C98" s="11"/>
     </x:row>
@@ -1207,7 +1207,7 @@
         <x:v>32905</x:v>
       </x:c>
       <x:c r="B99" s="11" t="n">
-        <x:v>46.9397636478184</x:v>
+        <x:v>46.92895016571309</x:v>
       </x:c>
       <x:c r="C99" s="11"/>
     </x:row>
@@ -1216,7 +1216,7 @@
         <x:v>32933</x:v>
       </x:c>
       <x:c r="B100" s="11" t="n">
-        <x:v>71.543400362614</x:v>
+        <x:v>71.52691895709651</x:v>
       </x:c>
       <x:c r="C100" s="11"/>
     </x:row>
@@ -1225,7 +1225,7 @@
         <x:v>32964</x:v>
       </x:c>
       <x:c r="B101" s="11" t="n">
-        <x:v>81.60889982390846</x:v>
+        <x:v>81.59009963598035</x:v>
       </x:c>
       <x:c r="C101" s="11"/>
     </x:row>
@@ -1234,7 +1234,7 @@
         <x:v>32994</x:v>
       </x:c>
       <x:c r="B102" s="11" t="n">
-        <x:v>62.13361912973053</x:v>
+        <x:v>62.1193054492519</x:v>
       </x:c>
       <x:c r="C102" s="11"/>
     </x:row>
@@ -1243,7 +1243,7 @@
         <x:v>33025</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>43.7415732424063</x:v>
+        <x:v>43.73149652529575</x:v>
       </x:c>
       <x:c r="C103" s="11"/>
     </x:row>
@@ -1252,7 +1252,7 @@
         <x:v>33055</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>63.26992102897885</x:v>
+        <x:v>63.25534557938808</x:v>
       </x:c>
       <x:c r="C104" s="11"/>
     </x:row>
@@ -1261,7 +1261,7 @@
         <x:v>33086</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>100.7403129572309</x:v>
+        <x:v>100.7171054783943</x:v>
       </x:c>
       <x:c r="C105" s="11"/>
     </x:row>
@@ -1270,7 +1270,7 @@
         <x:v>33117</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>111.0340015561602</x:v>
+        <x:v>111.0084227271333</x:v>
       </x:c>
       <x:c r="C106" s="11"/>
     </x:row>
@@ -1279,7 +1279,7 @@
         <x:v>33147</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>135.3996415865599</x:v>
+        <x:v>135.3684496612586</x:v>
       </x:c>
       <x:c r="C107" s="11"/>
     </x:row>
@@ -1288,7 +1288,7 @@
         <x:v>33178</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
-        <x:v>94.96709011017546</x:v>
+        <x:v>94.9452126048432</x:v>
       </x:c>
       <x:c r="C108" s="11"/>
     </x:row>
@@ -1297,7 +1297,7 @@
         <x:v>33208</x:v>
       </x:c>
       <x:c r="B109" s="11" t="n">
-        <x:v>88.68488797190555</x:v>
+        <x:v>88.66445769329803</x:v>
       </x:c>
       <x:c r="C109" s="11"/>
     </x:row>
@@ -1306,7 +1306,7 @@
         <x:v>33239</x:v>
       </x:c>
       <x:c r="B110" s="11" t="n">
-        <x:v>121.8657921189284</x:v>
+        <x:v>121.83771797752</x:v>
       </x:c>
       <x:c r="C110" s="11"/>
     </x:row>
@@ -1315,7 +1315,7 @@
         <x:v>33270</x:v>
       </x:c>
       <x:c r="B111" s="11" t="n">
-        <x:v>129.6012898496825</x:v>
+        <x:v>129.571433686811</x:v>
       </x:c>
       <x:c r="C111" s="11"/>
     </x:row>
@@ -1324,7 +1324,7 @@
         <x:v>33298</x:v>
       </x:c>
       <x:c r="B112" s="11" t="n">
-        <x:v>84.76899067248247</x:v>
+        <x:v>84.74946249652913</x:v>
       </x:c>
       <x:c r="C112" s="11"/>
     </x:row>
@@ -1333,7 +1333,7 @@
         <x:v>33329</x:v>
       </x:c>
       <x:c r="B113" s="11" t="n">
-        <x:v>65.63733309383127</x:v>
+        <x:v>65.62221226509904</x:v>
       </x:c>
       <x:c r="C113" s="11"/>
     </x:row>
@@ -1342,7 +1342,7 @@
         <x:v>33359</x:v>
       </x:c>
       <x:c r="B114" s="11" t="n">
-        <x:v>59.04729053534151</x:v>
+        <x:v>59.03368785032669</x:v>
       </x:c>
       <x:c r="C114" s="11"/>
     </x:row>
@@ -1351,7 +1351,7 @@
         <x:v>33390</x:v>
       </x:c>
       <x:c r="B115" s="11" t="n">
-        <x:v>54.88579214945569</x:v>
+        <x:v>54.87314814605385</x:v>
       </x:c>
       <x:c r="C115" s="11"/>
     </x:row>
@@ -1360,7 +1360,7 @@
         <x:v>33420</x:v>
       </x:c>
       <x:c r="B116" s="11" t="n">
-        <x:v>60.66309046231817</x:v>
+        <x:v>60.64911554654976</x:v>
       </x:c>
       <x:c r="C116" s="11"/>
     </x:row>
@@ -1369,7 +1369,7 @@
         <x:v>33451</x:v>
       </x:c>
       <x:c r="B117" s="11" t="n">
-        <x:v>96.85765688386887</x:v>
+        <x:v>96.83534384992744</x:v>
       </x:c>
       <x:c r="C117" s="11"/>
     </x:row>
@@ -1378,7 +1378,7 @@
         <x:v>33482</x:v>
       </x:c>
       <x:c r="B118" s="11" t="n">
-        <x:v>56.20344744835057</x:v>
+        <x:v>56.19049989757465</x:v>
       </x:c>
       <x:c r="C118" s="11"/>
     </x:row>
@@ -1387,7 +1387,7 @@
         <x:v>33512</x:v>
       </x:c>
       <x:c r="B119" s="11" t="n">
-        <x:v>94.30008672765085</x:v>
+        <x:v>94.27836287944382</x:v>
       </x:c>
       <x:c r="C119" s="11"/>
     </x:row>
@@ -1396,7 +1396,7 @@
         <x:v>33543</x:v>
       </x:c>
       <x:c r="B120" s="11" t="n">
-        <x:v>132.2490226231151</x:v>
+        <x:v>132.2185565038072</x:v>
       </x:c>
       <x:c r="C120" s="11"/>
     </x:row>
@@ -1405,7 +1405,7 @@
         <x:v>33573</x:v>
       </x:c>
       <x:c r="B121" s="11" t="n">
-        <x:v>133.1404504374143</x:v>
+        <x:v>133.1097789604742</x:v>
       </x:c>
       <x:c r="C121" s="11"/>
     </x:row>
@@ -1414,7 +1414,7 @@
         <x:v>33604</x:v>
       </x:c>
       <x:c r="B122" s="11" t="n">
-        <x:v>105.850328831873</x:v>
+        <x:v>105.825944162081</x:v>
       </x:c>
       <x:c r="C122" s="11"/>
     </x:row>
@@ -1423,7 +1423,7 @@
         <x:v>33635</x:v>
       </x:c>
       <x:c r="B123" s="11" t="n">
-        <x:v>58.41286070610528</x:v>
+        <x:v>58.39940417426791</x:v>
       </x:c>
       <x:c r="C123" s="11"/>
     </x:row>
@@ -1432,7 +1432,7 @@
         <x:v>33664</x:v>
       </x:c>
       <x:c r="B124" s="11" t="n">
-        <x:v>62.96604628187303</x:v>
+        <x:v>62.95154083570548</x:v>
       </x:c>
       <x:c r="C124" s="11"/>
     </x:row>
@@ -1441,7 +1441,7 @@
         <x:v>33695</x:v>
       </x:c>
       <x:c r="B125" s="11" t="n">
-        <x:v>95.37146456077812</x:v>
+        <x:v>95.34949389997286</x:v>
       </x:c>
       <x:c r="C125" s="11"/>
     </x:row>
@@ -1450,7 +1450,7 @@
         <x:v>33725</x:v>
       </x:c>
       <x:c r="B126" s="11" t="n">
-        <x:v>81.08518199579744</x:v>
+        <x:v>81.06650245639676</x:v>
       </x:c>
       <x:c r="C126" s="11"/>
     </x:row>
@@ -1459,7 +1459,7 @@
         <x:v>33756</x:v>
       </x:c>
       <x:c r="B127" s="11" t="n">
-        <x:v>177.2705246056883</x:v>
+        <x:v>177.229686912938</x:v>
       </x:c>
       <x:c r="C127" s="11"/>
     </x:row>
@@ -1468,7 +1468,7 @@
         <x:v>33786</x:v>
       </x:c>
       <x:c r="B128" s="11" t="n">
-        <x:v>53.10260064191389</x:v>
+        <x:v>53.09036743115264</x:v>
       </x:c>
       <x:c r="C128" s="11"/>
     </x:row>
@@ -1477,7 +1477,7 @@
         <x:v>33817</x:v>
       </x:c>
       <x:c r="B129" s="11" t="n">
-        <x:v>69.14330056458198</x:v>
+        <x:v>69.1273720684573</x:v>
       </x:c>
       <x:c r="C129" s="11"/>
     </x:row>
@@ -1486,7 +1486,7 @@
         <x:v>33848</x:v>
       </x:c>
       <x:c r="B130" s="11" t="n">
-        <x:v>165.4832613127984</x:v>
+        <x:v>165.4451390440464</x:v>
       </x:c>
       <x:c r="C130" s="11"/>
     </x:row>
@@ -1495,7 +1495,7 @@
         <x:v>33878</x:v>
       </x:c>
       <x:c r="B131" s="11" t="n">
-        <x:v>149.1982388867722</x:v>
+        <x:v>149.1638681877961</x:v>
       </x:c>
       <x:c r="C131" s="11"/>
     </x:row>
@@ -1504,7 +1504,7 @@
         <x:v>33909</x:v>
       </x:c>
       <x:c r="B132" s="11" t="n">
-        <x:v>124.1552729155804</x:v>
+        <x:v>124.1266713480048</x:v>
       </x:c>
       <x:c r="C132" s="11"/>
     </x:row>
@@ -1513,7 +1513,7 @@
         <x:v>33939</x:v>
       </x:c>
       <x:c r="B133" s="11" t="n">
-        <x:v>184.9490105061375</x:v>
+        <x:v>184.9064039257016</x:v>
       </x:c>
       <x:c r="C133" s="11"/>
     </x:row>
@@ -1522,7 +1522,7 @@
         <x:v>33970</x:v>
       </x:c>
       <x:c r="B134" s="11" t="n">
-        <x:v>150.8712759741354</x:v>
+        <x:v>150.8365198587192</x:v>
       </x:c>
       <x:c r="C134" s="11"/>
     </x:row>
@@ -1531,7 +1531,7 @@
         <x:v>34001</x:v>
       </x:c>
       <x:c r="B135" s="11" t="n">
-        <x:v>139.6746820300279</x:v>
+        <x:v>139.6425052665054</x:v>
       </x:c>
       <x:c r="C135" s="11"/>
     </x:row>
@@ -1540,7 +1540,7 @@
         <x:v>34029</x:v>
       </x:c>
       <x:c r="B136" s="11" t="n">
-        <x:v>53.4421109399463</x:v>
+        <x:v>53.42979951642369</x:v>
       </x:c>
       <x:c r="C136" s="11"/>
     </x:row>
@@ -1549,7 +1549,7 @@
         <x:v>34060</x:v>
       </x:c>
       <x:c r="B137" s="11" t="n">
-        <x:v>42.56920090422793</x:v>
+        <x:v>42.55939426575252</x:v>
       </x:c>
       <x:c r="C137" s="11"/>
     </x:row>
@@ -1558,7 +1558,7 @@
         <x:v>34090</x:v>
       </x:c>
       <x:c r="B138" s="11" t="n">
-        <x:v>60.45543837589723</x:v>
+        <x:v>60.44151129680173</x:v>
       </x:c>
       <x:c r="C138" s="11"/>
     </x:row>
@@ -1567,7 +1567,7 @@
         <x:v>34121</x:v>
       </x:c>
       <x:c r="B139" s="11" t="n">
-        <x:v>59.99366066741082</x:v>
+        <x:v>59.97983996773865</x:v>
       </x:c>
       <x:c r="C139" s="11"/>
     </x:row>
@@ -1576,7 +1576,7 @@
         <x:v>34151</x:v>
       </x:c>
       <x:c r="B140" s="11" t="n">
-        <x:v>77.37750965801743</x:v>
+        <x:v>77.35968425262514</x:v>
       </x:c>
       <x:c r="C140" s="11"/>
     </x:row>
@@ -1585,7 +1585,7 @@
         <x:v>34182</x:v>
       </x:c>
       <x:c r="B141" s="11" t="n">
-        <x:v>86.51206473295183</x:v>
+        <x:v>86.49213500618748</x:v>
       </x:c>
       <x:c r="C141" s="11"/>
     </x:row>
@@ -1594,7 +1594,7 @@
         <x:v>34213</x:v>
       </x:c>
       <x:c r="B142" s="11" t="n">
-        <x:v>62.76658580409028</x:v>
+        <x:v>62.75212630750022</x:v>
       </x:c>
       <x:c r="C142" s="11"/>
     </x:row>
@@ -1603,7 +1603,7 @@
         <x:v>34243</x:v>
       </x:c>
       <x:c r="B143" s="11" t="n">
-        <x:v>55.07092898861816</x:v>
+        <x:v>55.05824233536594</x:v>
       </x:c>
       <x:c r="C143" s="11"/>
     </x:row>
@@ -1612,7 +1612,7 @@
         <x:v>34274</x:v>
       </x:c>
       <x:c r="B144" s="11" t="n">
-        <x:v>25.60584694604129</x:v>
+        <x:v>25.59994814412529</x:v>
       </x:c>
       <x:c r="C144" s="11"/>
     </x:row>
@@ -1621,7 +1621,7 @@
         <x:v>34304</x:v>
       </x:c>
       <x:c r="B145" s="11" t="n">
-        <x:v>60.30739857909397</x:v>
+        <x:v>60.29350560382792</x:v>
       </x:c>
       <x:c r="C145" s="11"/>
     </x:row>
@@ -1630,7 +1630,7 @@
         <x:v>34335</x:v>
       </x:c>
       <x:c r="B146" s="11" t="n">
-        <x:v>46.39087210486908</x:v>
+        <x:v>46.38018507054314</x:v>
       </x:c>
       <x:c r="C146" s="11"/>
     </x:row>
@@ -1639,7 +1639,7 @@
         <x:v>34366</x:v>
       </x:c>
       <x:c r="B147" s="11" t="n">
-        <x:v>42.44161198887835</x:v>
+        <x:v>42.43183474297643</x:v>
       </x:c>
       <x:c r="C147" s="11"/>
     </x:row>
@@ -1648,7 +1648,7 @@
         <x:v>34394</x:v>
       </x:c>
       <x:c r="B148" s="11" t="n">
-        <x:v>28.84531053107403</x:v>
+        <x:v>28.83866545608834</x:v>
       </x:c>
       <x:c r="C148" s="11"/>
     </x:row>
@@ -1657,7 +1657,7 @@
         <x:v>34425</x:v>
       </x:c>
       <x:c r="B149" s="11" t="n">
-        <x:v>40.34915576959985</x:v>
+        <x:v>40.33986056144429</x:v>
       </x:c>
       <x:c r="C149" s="11"/>
     </x:row>
@@ -1666,7 +1666,7 @@
         <x:v>34455</x:v>
       </x:c>
       <x:c r="B150" s="11" t="n">
-        <x:v>53.59158328121553</x:v>
+        <x:v>53.57923742384917</x:v>
       </x:c>
       <x:c r="C150" s="11"/>
     </x:row>
@@ -1675,7 +1675,7 @@
         <x:v>34486</x:v>
       </x:c>
       <x:c r="B151" s="11" t="n">
-        <x:v>42.14783064147034</x:v>
+        <x:v>42.13812107378187</x:v>
       </x:c>
       <x:c r="C151" s="11"/>
     </x:row>
@@ -1684,7 +1684,7 @@
         <x:v>34516</x:v>
       </x:c>
       <x:c r="B152" s="11" t="n">
-        <x:v>42.21640551337023</x:v>
+        <x:v>42.20668014813417</x:v>
       </x:c>
       <x:c r="C152" s="11"/>
     </x:row>
@@ -1693,7 +1693,7 @@
         <x:v>34547</x:v>
       </x:c>
       <x:c r="B153" s="11" t="n">
-        <x:v>44.51599097345945</x:v>
+        <x:v>44.5057358542517</x:v>
       </x:c>
       <x:c r="C153" s="11"/>
     </x:row>
@@ -1702,7 +1702,7 @@
         <x:v>34578</x:v>
       </x:c>
       <x:c r="B154" s="11" t="n">
-        <x:v>52.03544580971165</x:v>
+        <x:v>52.02345843869873</x:v>
       </x:c>
       <x:c r="C154" s="11"/>
     </x:row>
@@ -1711,7 +1711,7 @@
         <x:v>34608</x:v>
       </x:c>
       <x:c r="B155" s="11" t="n">
-        <x:v>23.42867561052386</x:v>
+        <x:v>23.42327836211916</x:v>
       </x:c>
       <x:c r="C155" s="11"/>
     </x:row>
@@ -1720,7 +1720,7 @@
         <x:v>34639</x:v>
       </x:c>
       <x:c r="B156" s="11" t="n">
-        <x:v>18.54037744812803</x:v>
+        <x:v>18.53610631371702</x:v>
       </x:c>
       <x:c r="C156" s="11"/>
     </x:row>
@@ -1729,7 +1729,7 @@
         <x:v>34669</x:v>
       </x:c>
       <x:c r="B157" s="11" t="n">
-        <x:v>99.19583452966035</x:v>
+        <x:v>99.1729828512911</x:v>
       </x:c>
       <x:c r="C157" s="11"/>
     </x:row>
@@ -1738,7 +1738,7 @@
         <x:v>34700</x:v>
       </x:c>
       <x:c r="B158" s="11" t="n">
-        <x:v>38.22800477149934</x:v>
+        <x:v>38.21919821148725</x:v>
       </x:c>
       <x:c r="C158" s="11"/>
     </x:row>
@@ -1747,7 +1747,7 @@
         <x:v>34731</x:v>
       </x:c>
       <x:c r="B159" s="11" t="n">
-        <x:v>65.5233793905434</x:v>
+        <x:v>65.50828481324992</x:v>
       </x:c>
       <x:c r="C159" s="11"/>
     </x:row>
@@ -1756,7 +1756,7 @@
         <x:v>34759</x:v>
       </x:c>
       <x:c r="B160" s="11" t="n">
-        <x:v>62.12255072102138</x:v>
+        <x:v>62.10823959036469</x:v>
       </x:c>
       <x:c r="C160" s="11"/>
     </x:row>
@@ -1765,7 +1765,7 @@
         <x:v>34790</x:v>
       </x:c>
       <x:c r="B161" s="11" t="n">
-        <x:v>16.41257686572378</x:v>
+        <x:v>16.40879591131652</x:v>
       </x:c>
       <x:c r="C161" s="11"/>
     </x:row>
@@ -1774,7 +1774,7 @@
         <x:v>34820</x:v>
       </x:c>
       <x:c r="B162" s="11" t="n">
-        <x:v>21.00283972100251</x:v>
+        <x:v>20.99800131079687</x:v>
       </x:c>
       <x:c r="C162" s="11"/>
     </x:row>
@@ -1783,7 +1783,7 @@
         <x:v>34851</x:v>
       </x:c>
       <x:c r="B163" s="11" t="n">
-        <x:v>21.82275713932312</x:v>
+        <x:v>21.81772984528761</x:v>
       </x:c>
       <x:c r="C163" s="11"/>
     </x:row>
@@ -1792,7 +1792,7 @@
         <x:v>34881</x:v>
       </x:c>
       <x:c r="B164" s="11" t="n">
-        <x:v>12.88237893520323</x:v>
+        <x:v>12.8794112301433</x:v>
       </x:c>
       <x:c r="C164" s="11"/>
     </x:row>
@@ -1801,7 +1801,7 @@
         <x:v>34912</x:v>
       </x:c>
       <x:c r="B165" s="11" t="n">
-        <x:v>11.54708321393889</x:v>
+        <x:v>11.5444231200654</x:v>
       </x:c>
       <x:c r="C165" s="11"/>
     </x:row>
@@ -1810,7 +1810,7 @@
         <x:v>34943</x:v>
       </x:c>
       <x:c r="B166" s="11" t="n">
-        <x:v>32.02267043509038</x:v>
+        <x:v>32.01529339381867</x:v>
       </x:c>
       <x:c r="C166" s="11"/>
     </x:row>
@@ -1819,7 +1819,7 @@
         <x:v>34973</x:v>
       </x:c>
       <x:c r="B167" s="11" t="n">
-        <x:v>29.55899834948259</x:v>
+        <x:v>29.55218886270925</x:v>
       </x:c>
       <x:c r="C167" s="11"/>
     </x:row>
@@ -1828,7 +1828,7 @@
         <x:v>35004</x:v>
       </x:c>
       <x:c r="B168" s="11" t="n">
-        <x:v>28.76536510088225</x:v>
+        <x:v>28.7587384428721</x:v>
       </x:c>
       <x:c r="C168" s="11"/>
     </x:row>
@@ -1837,7 +1837,7 @@
         <x:v>35034</x:v>
       </x:c>
       <x:c r="B169" s="11" t="n">
-        <x:v>54.85901314942343</x:v>
+        <x:v>54.84637531508201</x:v>
       </x:c>
       <x:c r="C169" s="11"/>
     </x:row>
@@ -1846,7 +1846,7 @@
         <x:v>35065</x:v>
       </x:c>
       <x:c r="B170" s="11" t="n">
-        <x:v>51.0856601909536</x:v>
+        <x:v>51.07389162142143</x:v>
       </x:c>
       <x:c r="C170" s="11"/>
     </x:row>
@@ -1855,7 +1855,7 @@
         <x:v>35096</x:v>
       </x:c>
       <x:c r="B171" s="11" t="n">
-        <x:v>28.63145736679192</x:v>
+        <x:v>28.62486155701734</x:v>
       </x:c>
       <x:c r="C171" s="11"/>
     </x:row>
@@ -1864,7 +1864,7 @@
         <x:v>35125</x:v>
       </x:c>
       <x:c r="B172" s="11" t="n">
-        <x:v>32.9082718545565</x:v>
+        <x:v>32.90069079787531</x:v>
       </x:c>
       <x:c r="C172" s="11"/>
     </x:row>
@@ -1873,7 +1873,7 @@
         <x:v>35156</x:v>
       </x:c>
       <x:c r="B173" s="11" t="n">
-        <x:v>33.82816311415628</x:v>
+        <x:v>33.82037014273796</x:v>
       </x:c>
       <x:c r="C173" s="11"/>
     </x:row>
@@ -1882,7 +1882,7 @@
         <x:v>35186</x:v>
       </x:c>
       <x:c r="B174" s="11" t="n">
-        <x:v>12.26337529987641</x:v>
+        <x:v>12.2605501942719</x:v>
       </x:c>
       <x:c r="C174" s="11"/>
     </x:row>
@@ -1891,7 +1891,7 @@
         <x:v>35217</x:v>
       </x:c>
       <x:c r="B175" s="11" t="n">
-        <x:v>14.21118662089741</x:v>
+        <x:v>14.20791279929546</x:v>
       </x:c>
       <x:c r="C175" s="11"/>
     </x:row>
@@ -1900,7 +1900,7 @@
         <x:v>35247</x:v>
       </x:c>
       <x:c r="B176" s="11" t="n">
-        <x:v>28.60890847341386</x:v>
+        <x:v>28.60231785821284</x:v>
       </x:c>
       <x:c r="C176" s="11"/>
     </x:row>
@@ -1909,7 +1909,7 @@
         <x:v>35278</x:v>
       </x:c>
       <x:c r="B177" s="11" t="n">
-        <x:v>33.9804486857772</x:v>
+        <x:v>33.97262063243311</x:v>
       </x:c>
       <x:c r="C177" s="11"/>
     </x:row>
@@ -1918,7 +1918,7 @@
         <x:v>35309</x:v>
       </x:c>
       <x:c r="B178" s="11" t="n">
-        <x:v>43.20542537426394</x:v>
+        <x:v>43.19547216918087</x:v>
       </x:c>
       <x:c r="C178" s="11"/>
     </x:row>
@@ -1927,7 +1927,7 @@
         <x:v>35339</x:v>
       </x:c>
       <x:c r="B179" s="11" t="n">
-        <x:v>57.11660618571894</x:v>
+        <x:v>57.10344827117256</x:v>
       </x:c>
       <x:c r="C179" s="11"/>
     </x:row>
@@ -1936,7 +1936,7 @@
         <x:v>35370</x:v>
       </x:c>
       <x:c r="B180" s="11" t="n">
-        <x:v>24.58970178589237</x:v>
+        <x:v>24.58403707266049</x:v>
       </x:c>
       <x:c r="C180" s="11"/>
     </x:row>
@@ -1945,7 +1945,7 @@
         <x:v>35400</x:v>
       </x:c>
       <x:c r="B181" s="11" t="n">
-        <x:v>69.17621810829279</x:v>
+        <x:v>69.16028202897547</x:v>
       </x:c>
       <x:c r="C181" s="11"/>
     </x:row>
@@ -1954,7 +1954,7 @@
         <x:v>35431</x:v>
       </x:c>
       <x:c r="B182" s="11" t="n">
-        <x:v>47.74903230869209</x:v>
+        <x:v>47.73803239590408</x:v>
       </x:c>
       <x:c r="C182" s="11"/>
     </x:row>
@@ -1963,7 +1963,7 @@
         <x:v>35462</x:v>
       </x:c>
       <x:c r="B183" s="11" t="n">
-        <x:v>93.7247771252219</x:v>
+        <x:v>93.70318581070502</x:v>
       </x:c>
       <x:c r="C183" s="11"/>
     </x:row>
@@ -1972,7 +1972,7 @@
         <x:v>35490</x:v>
       </x:c>
       <x:c r="B184" s="11" t="n">
-        <x:v>33.8143866274472</x:v>
+        <x:v>33.80659682970894</x:v>
       </x:c>
       <x:c r="C184" s="11"/>
     </x:row>
@@ -1981,10 +1981,10 @@
         <x:v>35521</x:v>
       </x:c>
       <x:c r="B185" s="11" t="n">
-        <x:v>44.7103725279353</x:v>
+        <x:v>44.70007262917824</x:v>
       </x:c>
       <x:c r="C185" s="11" t="n">
-        <x:v>67.64241648750661</x:v>
+        <x:v>67.64241648750665</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -1992,7 +1992,7 @@
         <x:v>35551</x:v>
       </x:c>
       <x:c r="B186" s="11" t="n">
-        <x:v>85.70522952487259</x:v>
+        <x:v>85.68548566819806</x:v>
       </x:c>
       <x:c r="C186" s="11" t="n">
         <x:v>111.6840002379332</x:v>
@@ -2003,10 +2003,10 @@
         <x:v>35582</x:v>
       </x:c>
       <x:c r="B187" s="11" t="n">
-        <x:v>115.0016985646767</x:v>
+        <x:v>114.9752056999311</x:v>
       </x:c>
       <x:c r="C187" s="11" t="n">
-        <x:v>154.9586363503532</x:v>
+        <x:v>154.9586363503533</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -2014,10 +2014,10 @@
         <x:v>35612</x:v>
       </x:c>
       <x:c r="B188" s="11" t="n">
-        <x:v>54.14355651725801</x:v>
+        <x:v>54.13108350218469</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>97.53964153146063</x:v>
+        <x:v>97.53964153146065</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -2025,10 +2025,10 @@
         <x:v>35643</x:v>
       </x:c>
       <x:c r="B189" s="11" t="n">
-        <x:v>36.99319508295682</x:v>
+        <x:v>36.9846729852307</x:v>
       </x:c>
       <x:c r="C189" s="11" t="n">
-        <x:v>68.94368050985187</x:v>
+        <x:v>68.9436805098519</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -2036,10 +2036,10 @@
         <x:v>35674</x:v>
       </x:c>
       <x:c r="B190" s="11" t="n">
-        <x:v>63.43795945709191</x:v>
+        <x:v>63.42334529660031</x:v>
       </x:c>
       <x:c r="C190" s="11" t="n">
-        <x:v>98.77268933870593</x:v>
+        <x:v>98.77268933870596</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -2047,10 +2047,10 @@
         <x:v>35704</x:v>
       </x:c>
       <x:c r="B191" s="11" t="n">
-        <x:v>61.24451197164874</x:v>
+        <x:v>61.23040311419425</x:v>
       </x:c>
       <x:c r="C191" s="11" t="n">
-        <x:v>86.718418120693</x:v>
+        <x:v>86.71841812069304</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -2058,10 +2058,10 @@
         <x:v>35735</x:v>
       </x:c>
       <x:c r="B192" s="11" t="n">
-        <x:v>55.65095600783953</x:v>
+        <x:v>55.63813573414899</x:v>
       </x:c>
       <x:c r="C192" s="11" t="n">
-        <x:v>50.32583083226664</x:v>
+        <x:v>50.32583083226666</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -2069,7 +2069,7 @@
         <x:v>35765</x:v>
       </x:c>
       <x:c r="B193" s="11" t="n">
-        <x:v>51.11711042296115</x:v>
+        <x:v>51.10533460825998</x:v>
       </x:c>
       <x:c r="C193" s="11" t="n">
         <x:v>21.00644001839197</x:v>
@@ -2080,7 +2080,7 @@
         <x:v>35796</x:v>
       </x:c>
       <x:c r="B194" s="11" t="n">
-        <x:v>97.07167317117539</x:v>
+        <x:v>97.04931083444433</x:v>
       </x:c>
       <x:c r="C194" s="11" t="n">
         <x:v>108.2427097862725</x:v>
@@ -2091,7 +2091,7 @@
         <x:v>35827</x:v>
       </x:c>
       <x:c r="B195" s="11" t="n">
-        <x:v>40.74152422163718</x:v>
+        <x:v>40.73213862382251</x:v>
       </x:c>
       <x:c r="C195" s="11" t="n">
         <x:v>42.25739112113391</x:v>
@@ -2102,10 +2102,10 @@
         <x:v>35855</x:v>
       </x:c>
       <x:c r="B196" s="11" t="n">
-        <x:v>57.54335591644099</x:v>
+        <x:v>57.5300996918432</x:v>
       </x:c>
       <x:c r="C196" s="11" t="n">
-        <x:v>63.86038406948393</x:v>
+        <x:v>63.86038406948396</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -2113,7 +2113,7 @@
         <x:v>35886</x:v>
       </x:c>
       <x:c r="B197" s="11" t="n">
-        <x:v>53.0696297065263</x:v>
+        <x:v>53.05740409125749</x:v>
       </x:c>
       <x:c r="C197" s="11" t="n">
         <x:v>67.41472768454105</x:v>
@@ -2124,10 +2124,10 @@
         <x:v>35916</x:v>
       </x:c>
       <x:c r="B198" s="11" t="n">
-        <x:v>65.07149401543619</x:v>
+        <x:v>65.05650353867577</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>81.90926711854149</x:v>
+        <x:v>81.9092671185415</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -2135,10 +2135,10 @@
         <x:v>35947</x:v>
       </x:c>
       <x:c r="B199" s="11" t="n">
-        <x:v>49.48225647419342</x:v>
+        <x:v>49.47085727970815</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
-        <x:v>56.13231300732826</x:v>
+        <x:v>56.13231300732829</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -2146,10 +2146,10 @@
         <x:v>35977</x:v>
       </x:c>
       <x:c r="B200" s="11" t="n">
-        <x:v>71.04544232851025</x:v>
+        <x:v>71.02907563725361</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>70.18937552207203</x:v>
+        <x:v>70.18937552207208</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -2157,10 +2157,10 @@
         <x:v>36008</x:v>
       </x:c>
       <x:c r="B201" s="11" t="n">
-        <x:v>109.2056323175723</x:v>
+        <x:v>109.1804746887499</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>87.64460054585946</x:v>
+        <x:v>87.64460054585949</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -2168,10 +2168,10 @@
         <x:v>36039</x:v>
       </x:c>
       <x:c r="B202" s="11" t="n">
-        <x:v>148.0699525475599</x:v>
+        <x:v>148.0358417711568</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>102.9950327889626</x:v>
+        <x:v>102.9950327889627</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -2179,7 +2179,7 @@
         <x:v>36069</x:v>
       </x:c>
       <x:c r="B203" s="11" t="n">
-        <x:v>64.79667867163246</x:v>
+        <x:v>64.78175150389987</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
         <x:v>29.58817673052359</x:v>
@@ -2190,10 +2190,10 @@
         <x:v>36100</x:v>
       </x:c>
       <x:c r="B204" s="11" t="n">
-        <x:v>85.02545987717949</x:v>
+        <x:v>85.0058726185862</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
-        <x:v>99.89411913667232</x:v>
+        <x:v>99.89411913667233</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -2201,7 +2201,7 @@
         <x:v>36130</x:v>
       </x:c>
       <x:c r="B205" s="11" t="n">
-        <x:v>123.0532279511039</x:v>
+        <x:v>123.0248802608932</x:v>
       </x:c>
       <x:c r="C205" s="11" t="n">
         <x:v>162.8123634567349</x:v>
@@ -2212,7 +2212,7 @@
         <x:v>36161</x:v>
       </x:c>
       <x:c r="B206" s="11" t="n">
-        <x:v>87.25258975368435</x:v>
+        <x:v>87.23248943266393</x:v>
       </x:c>
       <x:c r="C206" s="11" t="n">
         <x:v>114.4487146096298</x:v>
@@ -2223,10 +2223,10 @@
         <x:v>36192</x:v>
       </x:c>
       <x:c r="B207" s="11" t="n">
-        <x:v>58.6615446655103</x:v>
+        <x:v>58.64803084451473</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
-        <x:v>90.38987602970603</x:v>
+        <x:v>90.38987602970606</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -2234,10 +2234,10 @@
         <x:v>36220</x:v>
       </x:c>
       <x:c r="B208" s="11" t="n">
-        <x:v>40.55843413623319</x:v>
+        <x:v>40.54909071675962</x:v>
       </x:c>
       <x:c r="C208" s="11" t="n">
-        <x:v>77.22453414937107</x:v>
+        <x:v>77.2245341493711</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -2245,10 +2245,10 @@
         <x:v>36251</x:v>
       </x:c>
       <x:c r="B209" s="11" t="n">
-        <x:v>61.37957964420371</x:v>
+        <x:v>61.36543967129941</x:v>
       </x:c>
       <x:c r="C209" s="11" t="n">
-        <x:v>112.0057602351625</x:v>
+        <x:v>112.0057602351626</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -2256,10 +2256,10 @@
         <x:v>36281</x:v>
       </x:c>
       <x:c r="B210" s="11" t="n">
-        <x:v>48.36048130502042</x:v>
+        <x:v>48.34934053313414</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>72.39083723189822</x:v>
+        <x:v>72.39083723189825</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -2267,10 +2267,10 @@
         <x:v>36312</x:v>
       </x:c>
       <x:c r="B211" s="11" t="n">
-        <x:v>55.24083637298134</x:v>
+        <x:v>55.22811057827808</x:v>
       </x:c>
       <x:c r="C211" s="11" t="n">
-        <x:v>87.44471232375349</x:v>
+        <x:v>87.44471232375352</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -2278,10 +2278,10 @@
         <x:v>36342</x:v>
       </x:c>
       <x:c r="B212" s="11" t="n">
-        <x:v>52.61801417217781</x:v>
+        <x:v>52.60589259527902</x:v>
       </x:c>
       <x:c r="C212" s="11" t="n">
-        <x:v>91.78464576259181</x:v>
+        <x:v>91.78464576259184</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -2289,10 +2289,10 @@
         <x:v>36373</x:v>
       </x:c>
       <x:c r="B213" s="11" t="n">
-        <x:v>63.96858733720845</x:v>
+        <x:v>63.95385093632533</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
-        <x:v>125.6451274187022</x:v>
+        <x:v>125.6451274187023</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -2300,10 +2300,10 @@
         <x:v>36404</x:v>
       </x:c>
       <x:c r="B214" s="11" t="n">
-        <x:v>37.68664958410339</x:v>
+        <x:v>37.67796773572545</x:v>
       </x:c>
       <x:c r="C214" s="11" t="n">
-        <x:v>79.9898273148568</x:v>
+        <x:v>79.98982731485683</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -2311,10 +2311,10 @@
         <x:v>36434</x:v>
       </x:c>
       <x:c r="B215" s="11" t="n">
-        <x:v>53.95642262772707</x:v>
+        <x:v>53.94399272256332</x:v>
       </x:c>
       <x:c r="C215" s="11" t="n">
-        <x:v>99.7133081045013</x:v>
+        <x:v>99.71330810450134</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -2322,10 +2322,10 @@
         <x:v>36465</x:v>
       </x:c>
       <x:c r="B216" s="11" t="n">
-        <x:v>51.82475238755788</x:v>
+        <x:v>51.81281355384837</x:v>
       </x:c>
       <x:c r="C216" s="11" t="n">
-        <x:v>102.3349936539656</x:v>
+        <x:v>102.3349936539657</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -2333,10 +2333,10 @@
         <x:v>36495</x:v>
       </x:c>
       <x:c r="B217" s="11" t="n">
-        <x:v>63.36326798206395</x:v>
+        <x:v>63.34867102819772</x:v>
       </x:c>
       <x:c r="C217" s="11" t="n">
-        <x:v>127.65943984786</x:v>
+        <x:v>127.6594398478601</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -2344,10 +2344,10 @@
         <x:v>36526</x:v>
       </x:c>
       <x:c r="B218" s="11" t="n">
-        <x:v>43.03622651884757</x:v>
+        <x:v>43.02631229199221</x:v>
       </x:c>
       <x:c r="C218" s="11" t="n">
-        <x:v>93.86154676790949</x:v>
+        <x:v>93.86154676790953</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -2355,10 +2355,10 @@
         <x:v>36557</x:v>
       </x:c>
       <x:c r="B219" s="11" t="n">
-        <x:v>34.99817521886799</x:v>
+        <x:v>34.99011271253994</x:v>
       </x:c>
       <x:c r="C219" s="11" t="n">
-        <x:v>85.1365005297786</x:v>
+        <x:v>85.13650052977863</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -2366,7 +2366,7 @@
         <x:v>36586</x:v>
       </x:c>
       <x:c r="B220" s="11" t="n">
-        <x:v>52.74215830724827</x:v>
+        <x:v>52.73000813134773</x:v>
       </x:c>
       <x:c r="C220" s="11" t="n">
         <x:v>112.2833949098791</x:v>
@@ -2377,7 +2377,7 @@
         <x:v>36617</x:v>
       </x:c>
       <x:c r="B221" s="11" t="n">
-        <x:v>70.69830059349756</x:v>
+        <x:v>70.68201387305135</x:v>
       </x:c>
       <x:c r="C221" s="11" t="n">
         <x:v>123.8260605053116</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>36647</x:v>
       </x:c>
       <x:c r="B222" s="11" t="n">
-        <x:v>64.99957856800708</x:v>
+        <x:v>64.98460465836041</x:v>
       </x:c>
       <x:c r="C222" s="11" t="n">
         <x:v>103.9682769537645</x:v>
@@ -2399,10 +2399,10 @@
         <x:v>36678</x:v>
       </x:c>
       <x:c r="B223" s="11" t="n">
-        <x:v>50.46782975163902</x:v>
+        <x:v>50.45620351129389</x:v>
       </x:c>
       <x:c r="C223" s="11" t="n">
-        <x:v>69.45724140682046</x:v>
+        <x:v>69.4572414068205</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -2410,7 +2410,7 @@
         <x:v>36708</x:v>
       </x:c>
       <x:c r="B224" s="11" t="n">
-        <x:v>33.50735527187108</x:v>
+        <x:v>33.49963620474183</x:v>
       </x:c>
       <x:c r="C224" s="11" t="n">
         <x:v>80.18186071203425</x:v>
@@ -2421,10 +2421,10 @@
         <x:v>36739</x:v>
       </x:c>
       <x:c r="B225" s="11" t="n">
-        <x:v>37.84851282786008</x:v>
+        <x:v>37.83979369115442</x:v>
       </x:c>
       <x:c r="C225" s="11" t="n">
-        <x:v>93.24971145704696</x:v>
+        <x:v>93.24971145704698</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -2432,10 +2432,10 @@
         <x:v>36770</x:v>
       </x:c>
       <x:c r="B226" s="11" t="n">
-        <x:v>30.67845053157088</x:v>
+        <x:v>30.67138315734354</x:v>
       </x:c>
       <x:c r="C226" s="11" t="n">
-        <x:v>65.6019211692969</x:v>
+        <x:v>65.60192116929694</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -2443,10 +2443,10 @@
         <x:v>36800</x:v>
       </x:c>
       <x:c r="B227" s="11" t="n">
-        <x:v>65.22785804911469</x:v>
+        <x:v>65.21283155087592</x:v>
       </x:c>
       <x:c r="C227" s="11" t="n">
-        <x:v>117.3340756224134</x:v>
+        <x:v>117.3340756224135</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -2454,7 +2454,7 @@
         <x:v>36831</x:v>
       </x:c>
       <x:c r="B228" s="11" t="n">
-        <x:v>81.44671749604623</x:v>
+        <x:v>81.42795466995304</x:v>
       </x:c>
       <x:c r="C228" s="11" t="n">
         <x:v>101.8535166145087</x:v>
@@ -2465,10 +2465,10 @@
         <x:v>36861</x:v>
       </x:c>
       <x:c r="B229" s="11" t="n">
-        <x:v>65.15903414191435</x:v>
+        <x:v>65.14402349859327</x:v>
       </x:c>
       <x:c r="C229" s="11" t="n">
-        <x:v>82.8741955195845</x:v>
+        <x:v>82.87419551958453</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -2476,10 +2476,10 @@
         <x:v>36892</x:v>
       </x:c>
       <x:c r="B230" s="11" t="n">
-        <x:v>58.5551666880794</x:v>
+        <x:v>58.54167737330769</x:v>
       </x:c>
       <x:c r="C230" s="11" t="n">
-        <x:v>71.9155097798053</x:v>
+        <x:v>71.91550977980535</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -2487,10 +2487,10 @@
         <x:v>36923</x:v>
       </x:c>
       <x:c r="B231" s="11" t="n">
-        <x:v>70.66133601235693</x:v>
+        <x:v>70.64505780741665</x:v>
       </x:c>
       <x:c r="C231" s="11" t="n">
-        <x:v>82.60445933479423</x:v>
+        <x:v>82.60445933479426</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -2498,10 +2498,10 @@
         <x:v>36951</x:v>
       </x:c>
       <x:c r="B232" s="11" t="n">
-        <x:v>85.88898721089548</x:v>
+        <x:v>85.86920102208512</x:v>
       </x:c>
       <x:c r="C232" s="11" t="n">
-        <x:v>91.02835883535984</x:v>
+        <x:v>91.02835883535982</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -2509,10 +2509,10 @@
         <x:v>36982</x:v>
       </x:c>
       <x:c r="B233" s="11" t="n">
-        <x:v>108.5172861362726</x:v>
+        <x:v>108.4922870813017</x:v>
       </x:c>
       <x:c r="C233" s="11" t="n">
-        <x:v>128.0730694602136</x:v>
+        <x:v>128.0730694602137</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -2520,10 +2520,10 @@
         <x:v>37012</x:v>
       </x:c>
       <x:c r="B234" s="11" t="n">
-        <x:v>65.58999197571855</x:v>
+        <x:v>65.57488205292817</x:v>
       </x:c>
       <x:c r="C234" s="11" t="n">
-        <x:v>95.19467746879157</x:v>
+        <x:v>95.19467746879155</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -2531,7 +2531,7 @@
         <x:v>37043</x:v>
       </x:c>
       <x:c r="B235" s="11" t="n">
-        <x:v>104.8695066595984</x:v>
+        <x:v>104.8453479411574</x:v>
       </x:c>
       <x:c r="C235" s="11" t="n">
         <x:v>159.4871670180582</x:v>
@@ -2542,10 +2542,10 @@
         <x:v>37073</x:v>
       </x:c>
       <x:c r="B236" s="11" t="n">
-        <x:v>78.31849599594082</x:v>
+        <x:v>78.30045381615226</x:v>
       </x:c>
       <x:c r="C236" s="11" t="n">
-        <x:v>90.82060119591488</x:v>
+        <x:v>90.82060119591493</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -2553,7 +2553,7 @@
         <x:v>37104</x:v>
       </x:c>
       <x:c r="B237" s="11" t="n">
-        <x:v>86.02215036085875</x:v>
+        <x:v>86.00233349534219</x:v>
       </x:c>
       <x:c r="C237" s="11" t="n">
         <x:v>121.8605293632929</x:v>
@@ -2564,7 +2564,7 @@
         <x:v>37135</x:v>
       </x:c>
       <x:c r="B238" s="11" t="n">
-        <x:v>142.7821612870642</x:v>
+        <x:v>142.7492686556138</x:v>
       </x:c>
       <x:c r="C238" s="11" t="n">
         <x:v>102.4546777707315</x:v>
@@ -2575,10 +2575,10 @@
         <x:v>37165</x:v>
       </x:c>
       <x:c r="B239" s="11" t="n">
-        <x:v>183.4617261065284</x:v>
+        <x:v>183.4194621508096</x:v>
       </x:c>
       <x:c r="C239" s="11" t="n">
-        <x:v>159.8702972006244</x:v>
+        <x:v>159.8702972006245</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -2586,7 +2586,7 @@
         <x:v>37196</x:v>
       </x:c>
       <x:c r="B240" s="11" t="n">
-        <x:v>164.8656502294314</x:v>
+        <x:v>164.8276702393335</x:v>
       </x:c>
       <x:c r="C240" s="11" t="n">
         <x:v>182.1632607298961</x:v>
@@ -2597,7 +2597,7 @@
         <x:v>37226</x:v>
       </x:c>
       <x:c r="B241" s="11" t="n">
-        <x:v>162.6728054327936</x:v>
+        <x:v>162.6353306068919</x:v>
       </x:c>
       <x:c r="C241" s="11" t="n">
         <x:v>205.398662201525</x:v>
@@ -2608,10 +2608,10 @@
         <x:v>37257</x:v>
       </x:c>
       <x:c r="B242" s="11" t="n">
-        <x:v>80.92081159724054</x:v>
+        <x:v>80.90216992373918</x:v>
       </x:c>
       <x:c r="C242" s="11" t="n">
-        <x:v>91.41612634405304</x:v>
+        <x:v>91.41612634405307</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -2619,10 +2619,10 @@
         <x:v>37288</x:v>
       </x:c>
       <x:c r="B243" s="11" t="n">
-        <x:v>72.8692747726713</x:v>
+        <x:v>72.85248792634857</x:v>
       </x:c>
       <x:c r="C243" s="11" t="n">
-        <x:v>87.33552436054313</x:v>
+        <x:v>87.33552436054318</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -2630,10 +2630,10 @@
         <x:v>37316</x:v>
       </x:c>
       <x:c r="B244" s="11" t="n">
-        <x:v>90.5889315065268</x:v>
+        <x:v>90.56806259467768</x:v>
       </x:c>
       <x:c r="C244" s="11" t="n">
-        <x:v>138.8637262829773</x:v>
+        <x:v>138.8637262829774</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -2641,7 +2641,7 @@
         <x:v>37347</x:v>
       </x:c>
       <x:c r="B245" s="11" t="n">
-        <x:v>75.24500419089918</x:v>
+        <x:v>75.22767004937181</x:v>
       </x:c>
       <x:c r="C245" s="11" t="n">
         <x:v>106.6280924218638</x:v>
@@ -2652,7 +2652,7 @@
         <x:v>37377</x:v>
       </x:c>
       <x:c r="B246" s="11" t="n">
-        <x:v>78.6638115466278</x:v>
+        <x:v>78.64568981672566</x:v>
       </x:c>
       <x:c r="C246" s="11" t="n">
         <x:v>112.9434618550594</x:v>
@@ -2663,10 +2663,10 @@
         <x:v>37408</x:v>
       </x:c>
       <x:c r="B247" s="11" t="n">
-        <x:v>96.10095643946363</x:v>
+        <x:v>96.07881772609986</x:v>
       </x:c>
       <x:c r="C247" s="11" t="n">
-        <x:v>111.7177992894964</x:v>
+        <x:v>111.7177992894965</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -2674,7 +2674,7 @@
         <x:v>37438</x:v>
       </x:c>
       <x:c r="B248" s="11" t="n">
-        <x:v>79.32041063154266</x:v>
+        <x:v>79.30213764134642</x:v>
       </x:c>
       <x:c r="C248" s="11" t="n">
         <x:v>91.66624808502418</x:v>
@@ -2685,10 +2685,10 @@
         <x:v>37469</x:v>
       </x:c>
       <x:c r="B249" s="11" t="n">
-        <x:v>101.8371541664308</x:v>
+        <x:v>101.8136940090151</x:v>
       </x:c>
       <x:c r="C249" s="11" t="n">
-        <x:v>109.5315706592089</x:v>
+        <x:v>109.531570659209</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -2696,7 +2696,7 @@
         <x:v>37500</x:v>
       </x:c>
       <x:c r="B250" s="11" t="n">
-        <x:v>176.2122800587788</x:v>
+        <x:v>176.1716861531203</x:v>
       </x:c>
       <x:c r="C250" s="11" t="n">
         <x:v>184.2954009298287</x:v>
@@ -2707,7 +2707,7 @@
         <x:v>37530</x:v>
       </x:c>
       <x:c r="B251" s="11" t="n">
-        <x:v>91.14294880757032</x:v>
+        <x:v>91.12195226712434</x:v>
       </x:c>
       <x:c r="C251" s="11" t="n">
         <x:v>60.21429648214023</x:v>
@@ -2718,10 +2718,10 @@
         <x:v>37561</x:v>
       </x:c>
       <x:c r="B252" s="11" t="n">
-        <x:v>151.1490771183797</x:v>
+        <x:v>151.1142570060989</x:v>
       </x:c>
       <x:c r="C252" s="11" t="n">
-        <x:v>161.4865269602663</x:v>
+        <x:v>161.4865269602664</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -2729,7 +2729,7 @@
         <x:v>37591</x:v>
       </x:c>
       <x:c r="B253" s="11" t="n">
-        <x:v>187.8534533115307</x:v>
+        <x:v>187.8101776365391</x:v>
       </x:c>
       <x:c r="C253" s="11" t="n">
         <x:v>223.9262067641156</x:v>
@@ -2740,7 +2740,7 @@
         <x:v>37622</x:v>
       </x:c>
       <x:c r="B254" s="11" t="n">
-        <x:v>163.8504713639795</x:v>
+        <x:v>163.8127252399611</x:v>
       </x:c>
       <x:c r="C254" s="11" t="n">
         <x:v>188.8802872709832</x:v>
@@ -2751,10 +2751,10 @@
         <x:v>37653</x:v>
       </x:c>
       <x:c r="B255" s="11" t="n">
-        <x:v>171.4159032440933</x:v>
+        <x:v>171.3764142765688</x:v>
       </x:c>
       <x:c r="C255" s="11" t="n">
-        <x:v>170.9542400209728</x:v>
+        <x:v>170.9542400209729</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -2762,10 +2762,10 @@
         <x:v>37681</x:v>
       </x:c>
       <x:c r="B256" s="11" t="n">
-        <x:v>179.0237739622608</x:v>
+        <x:v>178.9825323746233</x:v>
       </x:c>
       <x:c r="C256" s="11" t="n">
-        <x:v>148.2718110014323</x:v>
+        <x:v>148.2718110014324</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -2773,10 +2773,10 @@
         <x:v>37712</x:v>
       </x:c>
       <x:c r="B257" s="11" t="n">
-        <x:v>147.6548186669175</x:v>
+        <x:v>147.62080352463</x:v>
       </x:c>
       <x:c r="C257" s="11" t="n">
-        <x:v>135.2465845812064</x:v>
+        <x:v>135.2465845812063</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -2784,7 +2784,7 @@
         <x:v>37742</x:v>
       </x:c>
       <x:c r="B258" s="11" t="n">
-        <x:v>110.0134798403232</x:v>
+        <x:v>109.9881361082047</x:v>
       </x:c>
       <x:c r="C258" s="11" t="n">
         <x:v>103.5274259225224</x:v>
@@ -2795,10 +2795,10 @@
         <x:v>37773</x:v>
       </x:c>
       <x:c r="B259" s="11" t="n">
-        <x:v>75.56307571396623</x:v>
+        <x:v>75.54566829851382</x:v>
       </x:c>
       <x:c r="C259" s="11" t="n">
-        <x:v>95.36196327257315</x:v>
+        <x:v>95.36196327257313</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -2806,7 +2806,7 @@
         <x:v>37803</x:v>
       </x:c>
       <x:c r="B260" s="11" t="n">
-        <x:v>79.43443514053322</x:v>
+        <x:v>79.41613588258674</x:v>
       </x:c>
       <x:c r="C260" s="11" t="n">
         <x:v>115.1292550705642</x:v>
@@ -2817,7 +2817,7 @@
         <x:v>37834</x:v>
       </x:c>
       <x:c r="B261" s="11" t="n">
-        <x:v>70.12772496933833</x:v>
+        <x:v>70.11156969201883</x:v>
       </x:c>
       <x:c r="C261" s="11" t="n">
         <x:v>118.5165213626801</x:v>
@@ -2828,7 +2828,7 @@
         <x:v>37865</x:v>
       </x:c>
       <x:c r="B262" s="11" t="n">
-        <x:v>72.3378108471599</x:v>
+        <x:v>72.3211464338279</x:v>
       </x:c>
       <x:c r="C262" s="11" t="n">
         <x:v>113.7244849436983</x:v>
@@ -2839,10 +2839,10 @@
         <x:v>37895</x:v>
       </x:c>
       <x:c r="B263" s="11" t="n">
-        <x:v>85.82334588309321</x:v>
+        <x:v>85.80357481603187</x:v>
       </x:c>
       <x:c r="C263" s="11" t="n">
-        <x:v>129.8231747314039</x:v>
+        <x:v>129.823174731404</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -2850,10 +2850,10 @@
         <x:v>37926</x:v>
       </x:c>
       <x:c r="B264" s="11" t="n">
-        <x:v>55.52690126863345</x:v>
+        <x:v>55.51410957335061</x:v>
       </x:c>
       <x:c r="C264" s="11" t="n">
-        <x:v>83.61554294099071</x:v>
+        <x:v>83.61554294099075</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -2861,7 +2861,7 @@
         <x:v>37956</x:v>
       </x:c>
       <x:c r="B265" s="11" t="n">
-        <x:v>62.92363062253867</x:v>
+        <x:v>62.90913494763832</x:v>
       </x:c>
       <x:c r="C265" s="11" t="n">
         <x:v>104.852407753693</x:v>
@@ -2872,10 +2872,10 @@
         <x:v>37987</x:v>
       </x:c>
       <x:c r="B266" s="11" t="n">
-        <x:v>67.86489717004339</x:v>
+        <x:v>67.84926317885774</x:v>
       </x:c>
       <x:c r="C266" s="11" t="n">
-        <x:v>105.6962454717874</x:v>
+        <x:v>105.6962454717875</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -2883,10 +2883,10 @@
         <x:v>38018</x:v>
       </x:c>
       <x:c r="B267" s="11" t="n">
-        <x:v>26.81887156450147</x:v>
+        <x:v>26.81269331891158</x:v>
       </x:c>
       <x:c r="C267" s="11" t="n">
-        <x:v>42.34656466217313</x:v>
+        <x:v>42.34656466217312</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -2894,7 +2894,7 @@
         <x:v>38047</x:v>
       </x:c>
       <x:c r="B268" s="11" t="n">
-        <x:v>49.70989730622117</x:v>
+        <x:v>49.69844567026895</x:v>
       </x:c>
       <x:c r="C268" s="11" t="n">
         <x:v>76.74845660557868</x:v>
@@ -2905,10 +2905,10 @@
         <x:v>38078</x:v>
       </x:c>
       <x:c r="B269" s="11" t="n">
-        <x:v>46.9821211617242</x:v>
+        <x:v>46.9712979217466</x:v>
       </x:c>
       <x:c r="C269" s="11" t="n">
-        <x:v>69.92274673958583</x:v>
+        <x:v>69.92274673958588</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -2916,10 +2916,10 @@
         <x:v>38108</x:v>
       </x:c>
       <x:c r="B270" s="11" t="n">
-        <x:v>55.88640236018038</x:v>
+        <x:v>55.87352784687039</x:v>
       </x:c>
       <x:c r="C270" s="11" t="n">
-        <x:v>50.50335911935551</x:v>
+        <x:v>50.50335911935552</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -2927,10 +2927,10 @@
         <x:v>38139</x:v>
       </x:c>
       <x:c r="B271" s="11" t="n">
-        <x:v>43.97258115381787</x:v>
+        <x:v>43.96245121956854</x:v>
       </x:c>
       <x:c r="C271" s="11" t="n">
-        <x:v>61.45686499911832</x:v>
+        <x:v>61.45686499911834</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -2938,10 +2938,10 @@
         <x:v>38169</x:v>
       </x:c>
       <x:c r="B272" s="11" t="n">
-        <x:v>53.18423415558324</x:v>
+        <x:v>53.17198213896379</x:v>
       </x:c>
       <x:c r="C272" s="11" t="n">
-        <x:v>80.23303849252633</x:v>
+        <x:v>80.23303849252635</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
@@ -2949,7 +2949,7 @@
         <x:v>38200</x:v>
       </x:c>
       <x:c r="B273" s="11" t="n">
-        <x:v>48.7763162593048</x:v>
+        <x:v>48.76507969179691</x:v>
       </x:c>
       <x:c r="C273" s="11" t="n">
         <x:v>82.83532570719049</x:v>
@@ -2960,10 +2960,10 @@
         <x:v>38231</x:v>
       </x:c>
       <x:c r="B274" s="11" t="n">
-        <x:v>49.54130451294546</x:v>
+        <x:v>49.52989171560279</x:v>
       </x:c>
       <x:c r="C274" s="11" t="n">
-        <x:v>78.01502701559811</x:v>
+        <x:v>78.01502701559812</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -2971,10 +2971,10 @@
         <x:v>38261</x:v>
       </x:c>
       <x:c r="B275" s="11" t="n">
-        <x:v>67.80431457604712</x:v>
+        <x:v>67.78869454123331</x:v>
       </x:c>
       <x:c r="C275" s="11" t="n">
-        <x:v>89.76321923156596</x:v>
+        <x:v>89.76321923156601</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -2982,7 +2982,7 @@
         <x:v>38292</x:v>
       </x:c>
       <x:c r="B276" s="11" t="n">
-        <x:v>74.9871502463598</x:v>
+        <x:v>74.96987550647398</x:v>
       </x:c>
       <x:c r="C276" s="11" t="n">
         <x:v>103.2827215546372</x:v>
@@ -2993,7 +2993,7 @@
         <x:v>38322</x:v>
       </x:c>
       <x:c r="B277" s="11" t="n">
-        <x:v>67.04477276810238</x:v>
+        <x:v>67.02932770842925</x:v>
       </x:c>
       <x:c r="C277" s="11" t="n">
         <x:v>109.1806546708208</x:v>
@@ -3004,10 +3004,10 @@
         <x:v>38353</x:v>
       </x:c>
       <x:c r="B278" s="11" t="n">
-        <x:v>31.88603162968379</x:v>
+        <x:v>31.87868606580273</x:v>
       </x:c>
       <x:c r="C278" s="11" t="n">
-        <x:v>70.66938711731551</x:v>
+        <x:v>70.66938711731552</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -3015,7 +3015,7 @@
         <x:v>38384</x:v>
       </x:c>
       <x:c r="B279" s="11" t="n">
-        <x:v>53.34368663077989</x:v>
+        <x:v>53.33139788119986</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
         <x:v>102.5887898729971</x:v>
@@ -3026,10 +3026,10 @@
         <x:v>38412</x:v>
       </x:c>
       <x:c r="B280" s="11" t="n">
-        <x:v>25.7780895261399</x:v>
+        <x:v>25.77215104481537</x:v>
       </x:c>
       <x:c r="C280" s="11" t="n">
-        <x:v>62.8839623130777</x:v>
+        <x:v>62.88396231307773</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -3037,10 +3037,10 @@
         <x:v>38443</x:v>
       </x:c>
       <x:c r="B281" s="11" t="n">
-        <x:v>46.39356517767209</x:v>
+        <x:v>46.38287752294477</x:v>
       </x:c>
       <x:c r="C281" s="11" t="n">
-        <x:v>76.66442776036969</x:v>
+        <x:v>76.66442776036973</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -3048,7 +3048,7 @@
         <x:v>38473</x:v>
       </x:c>
       <x:c r="B282" s="11" t="n">
-        <x:v>62.55326331920044</x:v>
+        <x:v>62.53885296556921</x:v>
       </x:c>
       <x:c r="C282" s="11" t="n">
         <x:v>102.7732232752676</x:v>
@@ -3059,10 +3059,10 @@
         <x:v>38504</x:v>
       </x:c>
       <x:c r="B283" s="11" t="n">
-        <x:v>73.13769138378142</x:v>
+        <x:v>73.12084270250266</x:v>
       </x:c>
       <x:c r="C283" s="11" t="n">
-        <x:v>122.0232220499722</x:v>
+        <x:v>122.0232220499723</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -3070,10 +3070,10 @@
         <x:v>38534</x:v>
       </x:c>
       <x:c r="B284" s="11" t="n">
-        <x:v>35.78315219948998</x:v>
+        <x:v>35.77490885853744</x:v>
       </x:c>
       <x:c r="C284" s="11" t="n">
-        <x:v>79.5919319422533</x:v>
+        <x:v>79.59193194225331</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -3081,10 +3081,10 @@
         <x:v>38565</x:v>
       </x:c>
       <x:c r="B285" s="11" t="n">
-        <x:v>42.14070023533915</x:v>
+        <x:v>42.13099231027759</x:v>
       </x:c>
       <x:c r="C285" s="11" t="n">
-        <x:v>87.07942155179452</x:v>
+        <x:v>87.07942155179455</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -3092,7 +3092,7 @@
         <x:v>38596</x:v>
       </x:c>
       <x:c r="B286" s="11" t="n">
-        <x:v>81.08518199579744</x:v>
+        <x:v>81.06650245639676</x:v>
       </x:c>
       <x:c r="C286" s="11" t="n">
         <x:v>117.910184121683</x:v>
@@ -3103,10 +3103,10 @@
         <x:v>38626</x:v>
       </x:c>
       <x:c r="B287" s="11" t="n">
-        <x:v>37.21249551827992</x:v>
+        <x:v>37.20392290045849</x:v>
       </x:c>
       <x:c r="C287" s="11" t="n">
-        <x:v>79.1268156712388</x:v>
+        <x:v>79.12681567123882</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -3114,10 +3114,10 @@
         <x:v>38657</x:v>
       </x:c>
       <x:c r="B288" s="11" t="n">
-        <x:v>66.58759500718533</x:v>
+        <x:v>66.57225526724866</x:v>
       </x:c>
       <x:c r="C288" s="11" t="n">
-        <x:v>115.8168297854517</x:v>
+        <x:v>115.8168297854518</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -3125,10 +3125,10 @@
         <x:v>38687</x:v>
       </x:c>
       <x:c r="B289" s="11" t="n">
-        <x:v>49.57771186515046</x:v>
+        <x:v>49.56629068067031</x:v>
       </x:c>
       <x:c r="C289" s="11" t="n">
-        <x:v>98.22237566205065</x:v>
+        <x:v>98.22237566205067</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -3136,7 +3136,7 @@
         <x:v>38718</x:v>
       </x:c>
       <x:c r="B290" s="11" t="n">
-        <x:v>58.90213854877489</x:v>
+        <x:v>58.8885693023266</x:v>
       </x:c>
       <x:c r="C290" s="11" t="n">
         <x:v>106.4000371970356</x:v>
@@ -3147,10 +3147,10 @@
         <x:v>38749</x:v>
       </x:c>
       <x:c r="B291" s="11" t="n">
-        <x:v>28.02268861413992</x:v>
+        <x:v>28.01623304601765</x:v>
       </x:c>
       <x:c r="C291" s="11" t="n">
-        <x:v>82.98404450562609</x:v>
+        <x:v>82.9840445056261</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -3158,10 +3158,10 @@
         <x:v>38777</x:v>
       </x:c>
       <x:c r="B292" s="11" t="n">
-        <x:v>41.64374779043424</x:v>
+        <x:v>41.63415434797662</x:v>
       </x:c>
       <x:c r="C292" s="11" t="n">
-        <x:v>95.6634388470679</x:v>
+        <x:v>95.66343884706794</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -3169,10 +3169,10 @@
         <x:v>38808</x:v>
       </x:c>
       <x:c r="B293" s="11" t="n">
-        <x:v>66.76795754656487</x:v>
+        <x:v>66.75257625663006</x:v>
       </x:c>
       <x:c r="C293" s="11" t="n">
-        <x:v>114.830183471622</x:v>
+        <x:v>114.8301834716221</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -3180,10 +3180,10 @@
         <x:v>38838</x:v>
       </x:c>
       <x:c r="B294" s="11" t="n">
-        <x:v>46.38270502962345</x:v>
+        <x:v>46.37201987674119</x:v>
       </x:c>
       <x:c r="C294" s="11" t="n">
-        <x:v>90.04393028137397</x:v>
+        <x:v>90.043930281374</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -3191,10 +3191,10 @@
         <x:v>38869</x:v>
       </x:c>
       <x:c r="B295" s="11" t="n">
-        <x:v>48.68280373115761</x:v>
+        <x:v>48.67158870606858</x:v>
       </x:c>
       <x:c r="C295" s="11" t="n">
-        <x:v>87.301883517795</x:v>
+        <x:v>87.30188351779503</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -3202,10 +3202,10 @@
         <x:v>38899</x:v>
       </x:c>
       <x:c r="B296" s="11" t="n">
-        <x:v>45.3935164437579</x:v>
+        <x:v>45.3830591695917</x:v>
       </x:c>
       <x:c r="C296" s="11" t="n">
-        <x:v>85.93090657579111</x:v>
+        <x:v>85.93090657579114</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -3213,10 +3213,10 @@
         <x:v>38930</x:v>
       </x:c>
       <x:c r="B297" s="11" t="n">
-        <x:v>27.8858619078241</x:v>
+        <x:v>27.87943786037908</x:v>
       </x:c>
       <x:c r="C297" s="11" t="n">
-        <x:v>76.57169050003978</x:v>
+        <x:v>76.57169050003981</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -3224,10 +3224,10 @@
         <x:v>38961</x:v>
       </x:c>
       <x:c r="B298" s="11" t="n">
-        <x:v>33.34252639843252</x:v>
+        <x:v>33.33484530282112</x:v>
       </x:c>
       <x:c r="C298" s="11" t="n">
-        <x:v>81.19760625867836</x:v>
+        <x:v>81.1976062586784</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -3235,10 +3235,10 @@
         <x:v>38991</x:v>
       </x:c>
       <x:c r="B299" s="11" t="n">
-        <x:v>39.29052851440115</x:v>
+        <x:v>39.28147718150168</x:v>
       </x:c>
       <x:c r="C299" s="11" t="n">
-        <x:v>86.50854192984875</x:v>
+        <x:v>86.50854192984876</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -3246,10 +3246,10 @@
         <x:v>39022</x:v>
       </x:c>
       <x:c r="B300" s="11" t="n">
-        <x:v>24.06469704290307</x:v>
+        <x:v>24.05915327466436</x:v>
       </x:c>
       <x:c r="C300" s="11" t="n">
-        <x:v>67.73798001959366</x:v>
+        <x:v>67.73798001959369</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -3257,7 +3257,7 @@
         <x:v>39052</x:v>
       </x:c>
       <x:c r="B301" s="11" t="n">
-        <x:v>56.15276805479931</x:v>
+        <x:v>56.13983217900154</x:v>
       </x:c>
       <x:c r="C301" s="11" t="n">
         <x:v>119.0481308108179</x:v>
@@ -3268,10 +3268,10 @@
         <x:v>39083</x:v>
       </x:c>
       <x:c r="B302" s="11" t="n">
-        <x:v>45.74952364258979</x:v>
+        <x:v>45.73898435528218</x:v>
       </x:c>
       <x:c r="C302" s="11" t="n">
-        <x:v>104.3625368271335</x:v>
+        <x:v>104.3625368271336</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -3279,7 +3279,7 @@
         <x:v>39114</x:v>
       </x:c>
       <x:c r="B303" s="11" t="n">
-        <x:v>54.06241949922945</x:v>
+        <x:v>54.04996517563697</x:v>
       </x:c>
       <x:c r="C303" s="11" t="n">
         <x:v>114.1570651956294</x:v>
@@ -3290,7 +3290,7 @@
         <x:v>39142</x:v>
       </x:c>
       <x:c r="B304" s="11" t="n">
-        <x:v>64.6315479656921</x:v>
+        <x:v>64.61665883901031</x:v>
       </x:c>
       <x:c r="C304" s="11" t="n">
         <x:v>128.4091355192489</x:v>
@@ -3301,10 +3301,10 @@
         <x:v>39173</x:v>
       </x:c>
       <x:c r="B305" s="11" t="n">
-        <x:v>96.25265487109657</x:v>
+        <x:v>96.23048121106609</x:v>
       </x:c>
       <x:c r="C305" s="11" t="n">
-        <x:v>172.2137859749045</x:v>
+        <x:v>172.2137859749046</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -3312,10 +3312,10 @@
         <x:v>39203</x:v>
       </x:c>
       <x:c r="B306" s="11" t="n">
-        <x:v>79.5647823333879</x:v>
+        <x:v>79.54645304744538</x:v>
       </x:c>
       <x:c r="C306" s="11" t="n">
-        <x:v>158.5992203266933</x:v>
+        <x:v>158.5992203266934</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -3323,7 +3323,7 @@
         <x:v>39234</x:v>
       </x:c>
       <x:c r="B307" s="11" t="n">
-        <x:v>43.68684960733273</x:v>
+        <x:v>43.67678549686956</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
         <x:v>104.1623598688283</x:v>
@@ -3334,7 +3334,7 @@
         <x:v>39264</x:v>
       </x:c>
       <x:c r="B308" s="11" t="n">
-        <x:v>37.72129471359813</x:v>
+        <x:v>37.71260488404476</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
         <x:v>103.0468209815275</x:v>
@@ -3345,10 +3345,10 @@
         <x:v>39295</x:v>
       </x:c>
       <x:c r="B309" s="11" t="n">
-        <x:v>58.54337072379895</x:v>
+        <x:v>58.52988412645568</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
-        <x:v>95.502407817926</x:v>
+        <x:v>95.50240781792604</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -3356,10 +3356,10 @@
         <x:v>39326</x:v>
       </x:c>
       <x:c r="B310" s="11" t="n">
-        <x:v>64.04685510552189</x:v>
+        <x:v>64.03210067414507</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>71.86675119064739</x:v>
+        <x:v>71.86675119064742</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -3367,7 +3367,7 @@
         <x:v>39356</x:v>
       </x:c>
       <x:c r="B311" s="11" t="n">
-        <x:v>58.54662430818909</x:v>
+        <x:v>58.53313696131974</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
         <x:v>93.52565543242308</x:v>
@@ -3378,7 +3378,7 @@
         <x:v>39387</x:v>
       </x:c>
       <x:c r="B312" s="11" t="n">
-        <x:v>86.2235011021772</x:v>
+        <x:v>86.20363785162439</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
         <x:v>129.0717472629741</x:v>
@@ -3389,10 +3389,10 @@
         <x:v>39417</x:v>
       </x:c>
       <x:c r="B313" s="11" t="n">
-        <x:v>131.4093266013955</x:v>
+        <x:v>131.3790539223012</x:v>
       </x:c>
       <x:c r="C313" s="11" t="n">
-        <x:v>175.7741035366301</x:v>
+        <x:v>175.7741035366302</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
@@ -3400,10 +3400,10 @@
         <x:v>39448</x:v>
       </x:c>
       <x:c r="B314" s="11" t="n">
-        <x:v>126.9189102122708</x:v>
+        <x:v>126.8896719874108</x:v>
       </x:c>
       <x:c r="C314" s="11" t="n">
-        <x:v>121.4736915584611</x:v>
+        <x:v>121.4736915584612</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -3411,7 +3411,7 @@
         <x:v>39479</x:v>
       </x:c>
       <x:c r="B315" s="11" t="n">
-        <x:v>100.166007163597</x:v>
+        <x:v>100.1429319872039</x:v>
       </x:c>
       <x:c r="C315" s="11" t="n">
         <x:v>106.3455346191326</x:v>
@@ -3422,7 +3422,7 @@
         <x:v>39508</x:v>
       </x:c>
       <x:c r="B316" s="11" t="n">
-        <x:v>114.7875547856092</x:v>
+        <x:v>114.7611112530235</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
         <x:v>108.0255685478136</x:v>
@@ -3433,7 +3433,7 @@
         <x:v>39539</x:v>
       </x:c>
       <x:c r="B317" s="11" t="n">
-        <x:v>89.53946643854387</x:v>
+        <x:v>89.51883929126386</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
         <x:v>103.8910386673778</x:v>
@@ -3444,10 +3444,10 @@
         <x:v>39569</x:v>
       </x:c>
       <x:c r="B318" s="11" t="n">
-        <x:v>56.10801240919302</x:v>
+        <x:v>56.09508684372354</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>76.11918109013372</x:v>
+        <x:v>76.11918109013374</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -3455,7 +3455,7 @@
         <x:v>39600</x:v>
       </x:c>
       <x:c r="B319" s="11" t="n">
-        <x:v>206.155303952387</x:v>
+        <x:v>206.1078120922461</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
         <x:v>284.3356968661188</x:v>
@@ -3466,7 +3466,7 @@
         <x:v>39630</x:v>
       </x:c>
       <x:c r="B320" s="11" t="n">
-        <x:v>162.0830347702747</x:v>
+        <x:v>162.0456958094479</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
         <x:v>217.4701837276596</x:v>
@@ -3477,7 +3477,7 @@
         <x:v>39661</x:v>
       </x:c>
       <x:c r="B321" s="11" t="n">
-        <x:v>138.9115574145494</x:v>
+        <x:v>138.8795564515366</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
         <x:v>188.9880807786956</x:v>
@@ -3488,10 +3488,10 @@
         <x:v>39692</x:v>
       </x:c>
       <x:c r="B322" s="11" t="n">
-        <x:v>220.3958229827096</x:v>
+        <x:v>220.3450505436792</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
-        <x:v>229.0676363751273</x:v>
+        <x:v>229.0676363751274</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
@@ -3499,10 +3499,10 @@
         <x:v>39722</x:v>
       </x:c>
       <x:c r="B323" s="11" t="n">
-        <x:v>270.0690412986154</x:v>
+        <x:v>270.0068256733475</x:v>
       </x:c>
       <x:c r="C323" s="11" t="n">
-        <x:v>203.8271888172035</x:v>
+        <x:v>203.8271888172036</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -3510,7 +3510,7 @@
         <x:v>39753</x:v>
       </x:c>
       <x:c r="B324" s="11" t="n">
-        <x:v>172.026021471747</x:v>
+        <x:v>171.9863919516926</x:v>
       </x:c>
       <x:c r="C324" s="11" t="n">
         <x:v>153.3537457706473</x:v>
@@ -3521,7 +3521,7 @@
         <x:v>39783</x:v>
       </x:c>
       <x:c r="B325" s="11" t="n">
-        <x:v>215.519823799952</x:v>
+        <x:v>215.4701746416075</x:v>
       </x:c>
       <x:c r="C325" s="11" t="n">
         <x:v>218.6680261218019</x:v>
@@ -3532,10 +3532,10 @@
         <x:v>39814</x:v>
       </x:c>
       <x:c r="B326" s="11" t="n">
-        <x:v>145.0843328902283</x:v>
+        <x:v>145.0509099090382</x:v>
       </x:c>
       <x:c r="C326" s="11" t="n">
-        <x:v>125.4927104547351</x:v>
+        <x:v>125.4927104547352</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -3543,7 +3543,7 @@
         <x:v>39845</x:v>
       </x:c>
       <x:c r="B327" s="11" t="n">
-        <x:v>166.5429701494637</x:v>
+        <x:v>166.5046037562925</x:v>
       </x:c>
       <x:c r="C327" s="11" t="n">
         <x:v>143.7934012783274</x:v>
@@ -3554,10 +3554,10 @@
         <x:v>39873</x:v>
       </x:c>
       <x:c r="B328" s="11" t="n">
-        <x:v>155.3203003424206</x:v>
+        <x:v>155.2845193082223</x:v>
       </x:c>
       <x:c r="C328" s="11" t="n">
-        <x:v>148.1829959454552</x:v>
+        <x:v>148.1829959454553</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -3565,7 +3565,7 @@
         <x:v>39904</x:v>
       </x:c>
       <x:c r="B329" s="11" t="n">
-        <x:v>161.3987514903003</x:v>
+        <x:v>161.3615701673572</x:v>
       </x:c>
       <x:c r="C329" s="11" t="n">
         <x:v>196.1832366518395</x:v>
@@ -3576,7 +3576,7 @@
         <x:v>39934</x:v>
       </x:c>
       <x:c r="B330" s="11" t="n">
-        <x:v>129.2223387097711</x:v>
+        <x:v>129.1925698456216</x:v>
       </x:c>
       <x:c r="C330" s="11" t="n">
         <x:v>142.1082413841262</x:v>
@@ -3587,7 +3587,7 @@
         <x:v>39965</x:v>
       </x:c>
       <x:c r="B331" s="11" t="n">
-        <x:v>128.674122727366</x:v>
+        <x:v>128.6444801553674</x:v>
       </x:c>
       <x:c r="C331" s="11" t="n">
         <x:v>156.9574315453123</x:v>
@@ -3598,7 +3598,7 @@
         <x:v>39995</x:v>
       </x:c>
       <x:c r="B332" s="11" t="n">
-        <x:v>101.9761240820509</x:v>
+        <x:v>101.9526319102282</x:v>
       </x:c>
       <x:c r="C332" s="11" t="n">
         <x:v>120.4606054476244</x:v>
@@ -3609,7 +3609,7 @@
         <x:v>40026</x:v>
       </x:c>
       <x:c r="B333" s="11" t="n">
-        <x:v>86.07786095758945</x:v>
+        <x:v>86.0580312580598</x:v>
       </x:c>
       <x:c r="C333" s="11" t="n">
         <x:v>107.9161117690122</x:v>
@@ -3620,10 +3620,10 @@
         <x:v>40057</x:v>
       </x:c>
       <x:c r="B334" s="11" t="n">
-        <x:v>181.9796019075758</x:v>
+        <x:v>181.9376793878221</x:v>
       </x:c>
       <x:c r="C334" s="11" t="n">
-        <x:v>247.0546293016912</x:v>
+        <x:v>247.0546293016913</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -3631,7 +3631,7 @@
         <x:v>40087</x:v>
       </x:c>
       <x:c r="B335" s="11" t="n">
-        <x:v>141.0836993923535</x:v>
+        <x:v>141.0511980344392</x:v>
       </x:c>
       <x:c r="C335" s="11" t="n">
         <x:v>196.0238151419967</x:v>
@@ -3642,7 +3642,7 @@
         <x:v>40118</x:v>
       </x:c>
       <x:c r="B336" s="11" t="n">
-        <x:v>95.42040549934072</x:v>
+        <x:v>95.39842356404401</x:v>
       </x:c>
       <x:c r="C336" s="11" t="n">
         <x:v>109.4810976171643</x:v>
@@ -3653,7 +3653,7 @@
         <x:v>40148</x:v>
       </x:c>
       <x:c r="B337" s="11" t="n">
-        <x:v>121.5170152974615</x:v>
+        <x:v>121.4890215035372</x:v>
       </x:c>
       <x:c r="C337" s="11" t="n">
         <x:v>143.9781361573145</x:v>
@@ -3664,10 +3664,10 @@
         <x:v>40179</x:v>
       </x:c>
       <x:c r="B338" s="11" t="n">
-        <x:v>114.6251038152996</x:v>
+        <x:v>114.5986977064358</x:v>
       </x:c>
       <x:c r="C338" s="11" t="n">
-        <x:v>123.3033784709782</x:v>
+        <x:v>123.3033784709783</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -3675,10 +3675,10 @@
         <x:v>40210</x:v>
       </x:c>
       <x:c r="B339" s="11" t="n">
-        <x:v>91.62347195601632</x:v>
+        <x:v>91.6023647177725</x:v>
       </x:c>
       <x:c r="C339" s="11" t="n">
-        <x:v>74.86724012042981</x:v>
+        <x:v>74.86724012042983</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -3686,10 +3686,10 @@
         <x:v>40238</x:v>
       </x:c>
       <x:c r="B340" s="11" t="n">
-        <x:v>87.08287154505602</x:v>
+        <x:v>87.06281032190635</x:v>
       </x:c>
       <x:c r="C340" s="11" t="n">
-        <x:v>89.11805832579445</x:v>
+        <x:v>89.11805832579446</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -3697,7 +3697,7 @@
         <x:v>40269</x:v>
       </x:c>
       <x:c r="B341" s="11" t="n">
-        <x:v>132.29193076487</x:v>
+        <x:v>132.261454760842</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
         <x:v>152.754943250921</x:v>
@@ -3708,10 +3708,10 @@
         <x:v>40299</x:v>
       </x:c>
       <x:c r="B342" s="11" t="n">
-        <x:v>146.9451319538555</x:v>
+        <x:v>146.9112803016237</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
-        <x:v>94.60686588844389</x:v>
+        <x:v>94.60686588844398</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -3719,7 +3719,7 @@
         <x:v>40330</x:v>
       </x:c>
       <x:c r="B343" s="11" t="n">
-        <x:v>104.2009903583631</x:v>
+        <x:v>104.1769856455774</x:v>
       </x:c>
       <x:c r="C343" s="11" t="n">
         <x:v>40.06140055356867</x:v>
@@ -3730,10 +3730,10 @@
         <x:v>40360</x:v>
       </x:c>
       <x:c r="B344" s="11" t="n">
-        <x:v>141.7981462156448</x:v>
+        <x:v>141.7654802710914</x:v>
       </x:c>
       <x:c r="C344" s="11" t="n">
-        <x:v>123.6664366843627</x:v>
+        <x:v>123.6664366843628</x:v>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -3741,7 +3741,7 @@
         <x:v>40391</x:v>
       </x:c>
       <x:c r="B345" s="11" t="n">
-        <x:v>124.5089455186479</x:v>
+        <x:v>124.4802624757502</x:v>
       </x:c>
       <x:c r="C345" s="11" t="n">
         <x:v>104.0488771715709</x:v>
@@ -3752,10 +3752,10 @@
         <x:v>40422</x:v>
       </x:c>
       <x:c r="B346" s="11" t="n">
-        <x:v>192.0381376640578</x:v>
+        <x:v>191.9938979661175</x:v>
       </x:c>
       <x:c r="C346" s="11" t="n">
-        <x:v>212.6908475691023</x:v>
+        <x:v>212.6908475691024</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -3763,7 +3763,7 @@
         <x:v>40452</x:v>
       </x:c>
       <x:c r="B347" s="11" t="n">
-        <x:v>133.3636592397268</x:v>
+        <x:v>133.3329363423235</x:v>
       </x:c>
       <x:c r="C347" s="11" t="n">
         <x:v>132.957822669873</x:v>
@@ -3774,7 +3774,7 @@
         <x:v>40483</x:v>
       </x:c>
       <x:c r="B348" s="11" t="n">
-        <x:v>238.5954780565994</x:v>
+        <x:v>238.5405129751446</x:v>
       </x:c>
       <x:c r="C348" s="11" t="n">
         <x:v>277.7565902279658</x:v>
@@ -3785,10 +3785,10 @@
         <x:v>40513</x:v>
       </x:c>
       <x:c r="B349" s="11" t="n">
-        <x:v>184.9836360744354</x:v>
+        <x:v>184.9410215173304</x:v>
       </x:c>
       <x:c r="C349" s="11" t="n">
-        <x:v>198.5996052923425</x:v>
+        <x:v>198.5996052923426</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -3796,7 +3796,7 @@
         <x:v>40544</x:v>
       </x:c>
       <x:c r="B350" s="11" t="n">
-        <x:v>121.7542630442325</x:v>
+        <x:v>121.7262145957027</x:v>
       </x:c>
       <x:c r="C350" s="11" t="n">
         <x:v>136.2676983185303</x:v>
@@ -3807,10 +3807,10 @@
         <x:v>40575</x:v>
       </x:c>
       <x:c r="B351" s="11" t="n">
-        <x:v>92.5507300232287</x:v>
+        <x:v>92.52940917316116</x:v>
       </x:c>
       <x:c r="C351" s="11" t="n">
-        <x:v>92.65478460363732</x:v>
+        <x:v>92.65478460363728</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -3818,10 +3818,10 @@
         <x:v>40603</x:v>
       </x:c>
       <x:c r="B352" s="11" t="n">
-        <x:v>132.8651467701168</x:v>
+        <x:v>132.8345387146993</x:v>
       </x:c>
       <x:c r="C352" s="11" t="n">
-        <x:v>130.8132552491234</x:v>
+        <x:v>130.8132552491235</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -3829,10 +3829,10 @@
         <x:v>40634</x:v>
       </x:c>
       <x:c r="B353" s="11" t="n">
-        <x:v>96.94101988337223</x:v>
+        <x:v>96.91868764515212</x:v>
       </x:c>
       <x:c r="C353" s="11" t="n">
-        <x:v>87.84814355339792</x:v>
+        <x:v>87.84814355339796</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
@@ -3840,10 +3840,10 @@
         <x:v>40664</x:v>
       </x:c>
       <x:c r="B354" s="11" t="n">
-        <x:v>68.62895082605691</x:v>
+        <x:v>68.61314082033911</x:v>
       </x:c>
       <x:c r="C354" s="11" t="n">
-        <x:v>58.19762822453863</x:v>
+        <x:v>58.1976282245386</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -3851,10 +3851,10 @@
         <x:v>40695</x:v>
       </x:c>
       <x:c r="B355" s="11" t="n">
-        <x:v>117.473438864953</x:v>
+        <x:v>117.4463765870399</x:v>
       </x:c>
       <x:c r="C355" s="11" t="n">
-        <x:v>104.4786056642876</x:v>
+        <x:v>104.4786056642877</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -3862,10 +3862,10 @@
         <x:v>40725</x:v>
       </x:c>
       <x:c r="B356" s="11" t="n">
-        <x:v>121.5647810392354</x:v>
+        <x:v>121.5367762415491</x:v>
       </x:c>
       <x:c r="C356" s="11" t="n">
-        <x:v>66.66887332220713</x:v>
+        <x:v>66.6688733222072</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -3873,10 +3873,10 @@
         <x:v>40756</x:v>
       </x:c>
       <x:c r="B357" s="11" t="n">
-        <x:v>134.8246243727274</x:v>
+        <x:v>134.7935649137589</x:v>
       </x:c>
       <x:c r="C357" s="11" t="n">
-        <x:v>-2.002580165095821</x:v>
+        <x:v>-2.002580165095779</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -3884,7 +3884,7 @@
         <x:v>40787</x:v>
       </x:c>
       <x:c r="B358" s="11" t="n">
-        <x:v>181.6875850409115</x:v>
+        <x:v>181.645729792889</x:v>
       </x:c>
       <x:c r="C358" s="11" t="n">
         <x:v>103.1138862580066</x:v>
@@ -3895,10 +3895,10 @@
         <x:v>40817</x:v>
       </x:c>
       <x:c r="B359" s="11" t="n">
-        <x:v>146.4128398727472</x:v>
+        <x:v>146.3791108442879</x:v>
       </x:c>
       <x:c r="C359" s="11" t="n">
-        <x:v>61.89670727974707</x:v>
+        <x:v>61.89670727974702</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -3906,7 +3906,7 @@
         <x:v>40848</x:v>
       </x:c>
       <x:c r="B360" s="11" t="n">
-        <x:v>224.9963203741625</x:v>
+        <x:v>224.9444881216104</x:v>
       </x:c>
       <x:c r="C360" s="11" t="n">
         <x:v>120.4994582437209</x:v>
@@ -3917,7 +3917,7 @@
         <x:v>40878</x:v>
       </x:c>
       <x:c r="B361" s="11" t="n">
-        <x:v>230.1368269716999</x:v>
+        <x:v>230.0838105040648</x:v>
       </x:c>
       <x:c r="C361" s="11" t="n">
         <x:v>173.8516673876594</x:v>
@@ -3928,10 +3928,10 @@
         <x:v>40909</x:v>
       </x:c>
       <x:c r="B362" s="11" t="n">
-        <x:v>199.3702267058949</x:v>
+        <x:v>199.3242979194827</x:v>
       </x:c>
       <x:c r="C362" s="11" t="n">
-        <x:v>163.1251089412563</x:v>
+        <x:v>163.1251089412562</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -3939,10 +3939,10 @@
         <x:v>40940</x:v>
       </x:c>
       <x:c r="B363" s="11" t="n">
-        <x:v>124.0043206427329</x:v>
+        <x:v>123.975753849932</x:v>
       </x:c>
       <x:c r="C363" s="11" t="n">
-        <x:v>54.94662044928008</x:v>
+        <x:v>54.94662044928003</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -3950,10 +3950,10 @@
         <x:v>40969</x:v>
       </x:c>
       <x:c r="B364" s="11" t="n">
-        <x:v>115.4782610076388</x:v>
+        <x:v>115.4516583575205</x:v>
       </x:c>
       <x:c r="C364" s="11" t="n">
-        <x:v>58.42606392976859</x:v>
+        <x:v>58.4260639297686</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -3961,7 +3961,7 @@
         <x:v>41000</x:v>
       </x:c>
       <x:c r="B365" s="11" t="n">
-        <x:v>140.613455210462</x:v>
+        <x:v>140.5810621823869</x:v>
       </x:c>
       <x:c r="C365" s="11" t="n">
         <x:v>86.81993270188899</x:v>
@@ -3972,7 +3972,7 @@
         <x:v>41030</x:v>
       </x:c>
       <x:c r="B366" s="11" t="n">
-        <x:v>196.4680580261687</x:v>
+        <x:v>196.4227978104234</x:v>
       </x:c>
       <x:c r="C366" s="11" t="n">
         <x:v>117.7793283990475</x:v>
@@ -3983,10 +3983,10 @@
         <x:v>41061</x:v>
       </x:c>
       <x:c r="B367" s="11" t="n">
-        <x:v>143.5361391381984</x:v>
+        <x:v>143.5030728133723</x:v>
       </x:c>
       <x:c r="C367" s="11" t="n">
-        <x:v>18.30350919008424</x:v>
+        <x:v>18.30350919008423</x:v>
       </x:c>
     </x:row>
     <x:row r="368">
@@ -3994,10 +3994,10 @@
         <x:v>41091</x:v>
       </x:c>
       <x:c r="B368" s="11" t="n">
-        <x:v>112.0637394284924</x:v>
+        <x:v>112.0379233794374</x:v>
       </x:c>
       <x:c r="C368" s="11" t="n">
-        <x:v>29.29510648515864</x:v>
+        <x:v>29.29510648515861</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -4005,10 +4005,10 @@
         <x:v>41122</x:v>
       </x:c>
       <x:c r="B369" s="11" t="n">
-        <x:v>149.7499635475307</x:v>
+        <x:v>149.7154657481117</x:v>
       </x:c>
       <x:c r="C369" s="11" t="n">
-        <x:v>141.8368795565375</x:v>
+        <x:v>141.8368795565374</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -4016,10 +4016,10 @@
         <x:v>41153</x:v>
       </x:c>
       <x:c r="B370" s="11" t="n">
-        <x:v>120.4398409685184</x:v>
+        <x:v>120.4120953225273</x:v>
       </x:c>
       <x:c r="C370" s="11" t="n">
-        <x:v>75.44459932537</x:v>
+        <x:v>75.44459932537005</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -4027,10 +4027,10 @@
         <x:v>41183</x:v>
       </x:c>
       <x:c r="B371" s="11" t="n">
-        <x:v>137.141956863928</x:v>
+        <x:v>137.1103635626161</x:v>
       </x:c>
       <x:c r="C371" s="11" t="n">
-        <x:v>86.11681032931766</x:v>
+        <x:v>86.11681032931759</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -4038,10 +4038,10 @@
         <x:v>41214</x:v>
       </x:c>
       <x:c r="B372" s="11" t="n">
-        <x:v>91.03451616809132</x:v>
+        <x:v>91.01354460720032</x:v>
       </x:c>
       <x:c r="C372" s="11" t="n">
-        <x:v>16.94171244112289</x:v>
+        <x:v>16.9417124411229</x:v>
       </x:c>
     </x:row>
     <x:row r="373">
@@ -4049,10 +4049,10 @@
         <x:v>41244</x:v>
       </x:c>
       <x:c r="B373" s="11" t="n">
-        <x:v>103.086172686305</x:v>
+        <x:v>103.0624247933243</x:v>
       </x:c>
       <x:c r="C373" s="11" t="n">
-        <x:v>25.49122584246318</x:v>
+        <x:v>25.49122584246322</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -4060,10 +4060,10 @@
         <x:v>41275</x:v>
       </x:c>
       <x:c r="B374" s="11" t="n">
-        <x:v>132.5964119697577</x:v>
+        <x:v>132.5658658225973</x:v>
       </x:c>
       <x:c r="C374" s="11" t="n">
-        <x:v>78.61602837596264</x:v>
+        <x:v>78.61602837596267</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -4071,10 +4071,10 @@
         <x:v>41306</x:v>
       </x:c>
       <x:c r="B375" s="11" t="n">
-        <x:v>77.51234724019473</x:v>
+        <x:v>77.49449077235838</x:v>
       </x:c>
       <x:c r="C375" s="11" t="n">
-        <x:v>25.97196094656925</x:v>
+        <x:v>25.97196094656923</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -4082,10 +4082,10 @@
         <x:v>41334</x:v>
       </x:c>
       <x:c r="B376" s="11" t="n">
-        <x:v>99.4920074600116</x:v>
+        <x:v>99.46908755248155</x:v>
       </x:c>
       <x:c r="C376" s="11" t="n">
-        <x:v>23.77395220684014</x:v>
+        <x:v>23.77395220684015</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -4093,10 +4093,10 @@
         <x:v>41365</x:v>
       </x:c>
       <x:c r="B377" s="11" t="n">
-        <x:v>102.8448832071453</x:v>
+        <x:v>102.8211908998613</x:v>
       </x:c>
       <x:c r="C377" s="11" t="n">
-        <x:v>46.49027454710356</x:v>
+        <x:v>46.49027454710355</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -4104,10 +4104,10 @@
         <x:v>41395</x:v>
       </x:c>
       <x:c r="B378" s="11" t="n">
-        <x:v>56.87515505576523</x:v>
+        <x:v>56.86205276415492</x:v>
       </x:c>
       <x:c r="C378" s="11" t="n">
-        <x:v>10.87620787881704</x:v>
+        <x:v>10.87620787881701</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -4115,10 +4115,10 @@
         <x:v>41426</x:v>
       </x:c>
       <x:c r="B379" s="11" t="n">
-        <x:v>70.85165419812603</x:v>
+        <x:v>70.83533214971199</x:v>
       </x:c>
       <x:c r="C379" s="11" t="n">
-        <x:v>14.40340281853733</x:v>
+        <x:v>14.40340281853737</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -4126,10 +4126,10 @@
         <x:v>41456</x:v>
       </x:c>
       <x:c r="B380" s="11" t="n">
-        <x:v>84.88565136269703</x:v>
+        <x:v>84.86609631169816</x:v>
       </x:c>
       <x:c r="C380" s="11" t="n">
-        <x:v>41.24902974289367</x:v>
+        <x:v>41.24902974289368</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -4137,10 +4137,10 @@
         <x:v>41487</x:v>
       </x:c>
       <x:c r="B381" s="11" t="n">
-        <x:v>56.93309542217263</x:v>
+        <x:v>56.91997978287868</x:v>
       </x:c>
       <x:c r="C381" s="11" t="n">
-        <x:v>5.63449134333635</x:v>
+        <x:v>5.634491343336322</x:v>
       </x:c>
     </x:row>
     <x:row r="382">
@@ -4148,10 +4148,10 @@
         <x:v>41518</x:v>
       </x:c>
       <x:c r="B382" s="11" t="n">
-        <x:v>72.17118185586209</x:v>
+        <x:v>72.1545558287399</x:v>
       </x:c>
       <x:c r="C382" s="11" t="n">
-        <x:v>20.42313854072104</x:v>
+        <x:v>20.42313854072103</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -4159,7 +4159,7 @@
         <x:v>41548</x:v>
       </x:c>
       <x:c r="B383" s="11" t="n">
-        <x:v>88.51943109136097</x:v>
+        <x:v>88.49903892894488</x:v>
       </x:c>
       <x:c r="C383" s="11" t="n">
         <x:v>35.66818435086707</x:v>
@@ -4170,10 +4170,10 @@
         <x:v>41579</x:v>
       </x:c>
       <x:c r="B384" s="11" t="n">
-        <x:v>80.79433230078084</x:v>
+        <x:v>80.77571976423079</x:v>
       </x:c>
       <x:c r="C384" s="11" t="n">
-        <x:v>65.18223638768256</x:v>
+        <x:v>65.18223638768254</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -4181,10 +4181,10 @@
         <x:v>41609</x:v>
       </x:c>
       <x:c r="B385" s="11" t="n">
-        <x:v>71.82632038382057</x:v>
+        <x:v>71.80977380220614</x:v>
       </x:c>
       <x:c r="C385" s="11" t="n">
-        <x:v>48.64548732412217</x:v>
+        <x:v>48.64548732412216</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -4192,7 +4192,7 @@
         <x:v>41640</x:v>
       </x:c>
       <x:c r="B386" s="11" t="n">
-        <x:v>47.61341383665271</x:v>
+        <x:v>47.60244516620182</x:v>
       </x:c>
       <x:c r="C386" s="11" t="n">
         <x:v>5.925072442912054</x:v>
@@ -4203,10 +4203,10 @@
         <x:v>41671</x:v>
       </x:c>
       <x:c r="B387" s="11" t="n">
-        <x:v>60.54864827755188</x:v>
+        <x:v>60.53469972575341</x:v>
       </x:c>
       <x:c r="C387" s="11" t="n">
-        <x:v>43.48058190710499</x:v>
+        <x:v>43.48058190710497</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -4214,10 +4214,10 @@
         <x:v>41699</x:v>
       </x:c>
       <x:c r="B388" s="11" t="n">
-        <x:v>62.38859872426337</x:v>
+        <x:v>62.37422630430528</x:v>
       </x:c>
       <x:c r="C388" s="11" t="n">
-        <x:v>32.11462428349323</x:v>
+        <x:v>32.11462428349324</x:v>
       </x:c>
     </x:row>
     <x:row r="389">
@@ -4225,7 +4225,7 @@
         <x:v>41730</x:v>
       </x:c>
       <x:c r="B389" s="11" t="n">
-        <x:v>57.93646177690152</x:v>
+        <x:v>57.92311499276835</x:v>
       </x:c>
       <x:c r="C389" s="11" t="n">
         <x:v>49.39347015856958</x:v>
@@ -4236,10 +4236,10 @@
         <x:v>41760</x:v>
       </x:c>
       <x:c r="B390" s="11" t="n">
-        <x:v>54.27665872118458</x:v>
+        <x:v>54.26415504344514</x:v>
       </x:c>
       <x:c r="C390" s="11" t="n">
-        <x:v>37.14025291399011</x:v>
+        <x:v>37.14025291399009</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -4247,10 +4247,10 @@
         <x:v>41791</x:v>
       </x:c>
       <x:c r="B391" s="11" t="n">
-        <x:v>54.97846473345246</x:v>
+        <x:v>54.96579938112914</x:v>
       </x:c>
       <x:c r="C391" s="11" t="n">
-        <x:v>57.04854881790286</x:v>
+        <x:v>57.04854881790287</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -4258,10 +4258,10 @@
         <x:v>41821</x:v>
       </x:c>
       <x:c r="B392" s="11" t="n">
-        <x:v>41.73933602293121</x:v>
+        <x:v>41.72972055987609</x:v>
       </x:c>
       <x:c r="C392" s="11" t="n">
-        <x:v>30.31308100222392</x:v>
+        <x:v>30.31308100222394</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -4269,10 +4269,10 @@
         <x:v>41852</x:v>
       </x:c>
       <x:c r="B393" s="11" t="n">
-        <x:v>74.17815037062562</x:v>
+        <x:v>74.16106199950265</x:v>
       </x:c>
       <x:c r="C393" s="11" t="n">
-        <x:v>56.75428836986614</x:v>
+        <x:v>56.75428836986617</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -4280,10 +4280,10 @@
         <x:v>41883</x:v>
       </x:c>
       <x:c r="B394" s="11" t="n">
-        <x:v>92.96731167460331</x:v>
+        <x:v>92.94589485689806</x:v>
       </x:c>
       <x:c r="C394" s="11" t="n">
-        <x:v>57.41749451847971</x:v>
+        <x:v>57.41749451847974</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -4291,10 +4291,10 @@
         <x:v>41913</x:v>
       </x:c>
       <x:c r="B395" s="11" t="n">
-        <x:v>66.90670939862737</x:v>
+        <x:v>66.89129614452078</x:v>
       </x:c>
       <x:c r="C395" s="11" t="n">
-        <x:v>33.68275509603231</x:v>
+        <x:v>33.68275509603232</x:v>
       </x:c>
     </x:row>
     <x:row r="396">
@@ -4302,7 +4302,7 @@
         <x:v>41944</x:v>
       </x:c>
       <x:c r="B396" s="11" t="n">
-        <x:v>73.39974732452693</x:v>
+        <x:v>73.38283827359554</x:v>
       </x:c>
       <x:c r="C396" s="11" t="n">
         <x:v>37.18878264097032</x:v>
@@ -4313,10 +4313,10 @@
         <x:v>41974</x:v>
       </x:c>
       <x:c r="B397" s="11" t="n">
-        <x:v>119.8372361642883</x:v>
+        <x:v>119.8096293399648</x:v>
       </x:c>
       <x:c r="C397" s="11" t="n">
-        <x:v>78.14799741273347</x:v>
+        <x:v>78.14799741273349</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -4324,10 +4324,10 @@
         <x:v>42005</x:v>
       </x:c>
       <x:c r="B398" s="11" t="n">
-        <x:v>89.38606998041759</x:v>
+        <x:v>89.36547817097752</x:v>
       </x:c>
       <x:c r="C398" s="11" t="n">
-        <x:v>39.69490057248868</x:v>
+        <x:v>39.69490057248871</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -4335,7 +4335,7 @@
         <x:v>42036</x:v>
       </x:c>
       <x:c r="B399" s="11" t="n">
-        <x:v>57.60057326652554</x:v>
+        <x:v>57.58730386080492</x:v>
       </x:c>
       <x:c r="C399" s="11" t="n">
         <x:v>1.890771340520914</x:v>
@@ -4346,10 +4346,10 @@
         <x:v>42064</x:v>
       </x:c>
       <x:c r="B400" s="11" t="n">
-        <x:v>65.22622877827546</x:v>
+        <x:v>65.21120265537073</x:v>
       </x:c>
       <x:c r="C400" s="11" t="n">
-        <x:v>33.7374057330407</x:v>
+        <x:v>33.73740573304067</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -4357,7 +4357,7 @@
         <x:v>42095</x:v>
       </x:c>
       <x:c r="B401" s="11" t="n">
-        <x:v>89.53762727932772</x:v>
+        <x:v>89.51700055573359</x:v>
       </x:c>
       <x:c r="C401" s="11" t="n">
         <x:v>76.3274650562287</x:v>
@@ -4368,10 +4368,10 @@
         <x:v>42125</x:v>
       </x:c>
       <x:c r="B402" s="11" t="n">
-        <x:v>94.7512239052015</x:v>
+        <x:v>94.72939612882318</x:v>
       </x:c>
       <x:c r="C402" s="11" t="n">
-        <x:v>66.92427042277419</x:v>
+        <x:v>66.92427042277421</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -4379,10 +4379,10 @@
         <x:v>42156</x:v>
       </x:c>
       <x:c r="B403" s="11" t="n">
-        <x:v>106.7383830115179</x:v>
+        <x:v>106.7137937612757</x:v>
       </x:c>
       <x:c r="C403" s="11" t="n">
-        <x:v>84.38928848198981</x:v>
+        <x:v>84.38928848198982</x:v>
       </x:c>
     </x:row>
     <x:row r="404">
@@ -4390,7 +4390,7 @@
         <x:v>42186</x:v>
       </x:c>
       <x:c r="B404" s="11" t="n">
-        <x:v>144.1514346591954</x:v>
+        <x:v>144.1182265891498</x:v>
       </x:c>
       <x:c r="C404" s="11" t="n">
         <x:v>140.8245750776364</x:v>
@@ -4401,10 +4401,10 @@
         <x:v>42217</x:v>
       </x:c>
       <x:c r="B405" s="11" t="n">
-        <x:v>90.19292870236062</x:v>
+        <x:v>90.17215101741387</x:v>
       </x:c>
       <x:c r="C405" s="11" t="n">
-        <x:v>58.56801747442772</x:v>
+        <x:v>58.56801747442769</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -4412,10 +4412,10 @@
         <x:v>42248</x:v>
       </x:c>
       <x:c r="B406" s="11" t="n">
-        <x:v>97.0688797417316</x:v>
+        <x:v>97.04651804852101</x:v>
       </x:c>
       <x:c r="C406" s="11" t="n">
-        <x:v>25.63245196461482</x:v>
+        <x:v>25.63245196461476</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -4423,10 +4423,10 @@
         <x:v>42278</x:v>
       </x:c>
       <x:c r="B407" s="11" t="n">
-        <x:v>91.03561730771574</x:v>
+        <x:v>91.01464549315594</x:v>
       </x:c>
       <x:c r="C407" s="11" t="n">
-        <x:v>64.30234777928464</x:v>
+        <x:v>64.30234777928463</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -4434,7 +4434,7 @@
         <x:v>42309</x:v>
       </x:c>
       <x:c r="B408" s="11" t="n">
-        <x:v>94.40414982496266</x:v>
+        <x:v>94.38240200380918</x:v>
       </x:c>
       <x:c r="C408" s="11" t="n">
         <x:v>101.9678962001895</x:v>
@@ -4445,10 +4445,10 @@
         <x:v>42339</x:v>
       </x:c>
       <x:c r="B409" s="11" t="n">
-        <x:v>77.21944693637958</x:v>
+        <x:v>77.20165794379126</x:v>
       </x:c>
       <x:c r="C409" s="11" t="n">
-        <x:v>48.09750498386453</x:v>
+        <x:v>48.09750498386455</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -4456,7 +4456,7 @@
         <x:v>42370</x:v>
       </x:c>
       <x:c r="B410" s="11" t="n">
-        <x:v>141.9306491849582</x:v>
+        <x:v>141.897952715784</x:v>
       </x:c>
       <x:c r="C410" s="11" t="n">
         <x:v>124.9555518308438</x:v>
@@ -4467,7 +4467,7 @@
         <x:v>42401</x:v>
       </x:c>
       <x:c r="B411" s="11" t="n">
-        <x:v>213.6591335566224</x:v>
+        <x:v>213.6099130442506</x:v>
       </x:c>
       <x:c r="C411" s="11" t="n">
         <x:v>211.4139785639329</x:v>
@@ -4478,10 +4478,10 @@
         <x:v>42430</x:v>
       </x:c>
       <x:c r="B412" s="11" t="n">
-        <x:v>210.6485360964095</x:v>
+        <x:v>210.6000091333707</x:v>
       </x:c>
       <x:c r="C412" s="11" t="n">
-        <x:v>201.3874100058047</x:v>
+        <x:v>201.3874100058048</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -4489,7 +4489,7 @@
         <x:v>42461</x:v>
       </x:c>
       <x:c r="B413" s="11" t="n">
-        <x:v>176.340589971443</x:v>
+        <x:v>176.2999665071153</x:v>
       </x:c>
       <x:c r="C413" s="11" t="n">
         <x:v>161.0026180581175</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>42491</x:v>
       </x:c>
       <x:c r="B414" s="11" t="n">
-        <x:v>136.049549392841</x:v>
+        <x:v>136.0182077487109</x:v>
       </x:c>
       <x:c r="C414" s="11" t="n">
         <x:v>109.6518336191547</x:v>
@@ -4511,10 +4511,10 @@
         <x:v>42522</x:v>
       </x:c>
       <x:c r="B415" s="11" t="n">
-        <x:v>342.2623915276531</x:v>
+        <x:v>342.1835447683495</x:v>
       </x:c>
       <x:c r="C415" s="11" t="n">
-        <x:v>292.1174349149136</x:v>
+        <x:v>292.1174349149138</x:v>
       </x:c>
     </x:row>
     <x:row r="416">
@@ -4522,7 +4522,7 @@
         <x:v>42552</x:v>
       </x:c>
       <x:c r="B416" s="11" t="n">
-        <x:v>405.908934891161</x:v>
+        <x:v>405.8154259200301</x:v>
       </x:c>
       <x:c r="C416" s="11" t="n">
         <x:v>375.1291857472543</x:v>
@@ -4533,10 +4533,10 @@
         <x:v>42583</x:v>
       </x:c>
       <x:c r="B417" s="11" t="n">
-        <x:v>228.6336279225763</x:v>
+        <x:v>228.5809577459056</x:v>
       </x:c>
       <x:c r="C417" s="11" t="n">
-        <x:v>248.2698251505251</x:v>
+        <x:v>248.269825150525</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -4544,7 +4544,7 @@
         <x:v>42614</x:v>
       </x:c>
       <x:c r="B418" s="11" t="n">
-        <x:v>163.6723173001528</x:v>
+        <x:v>163.6346122173676</x:v>
       </x:c>
       <x:c r="C418" s="11" t="n">
         <x:v>147.6829411675587</x:v>
@@ -4555,7 +4555,7 @@
         <x:v>42644</x:v>
       </x:c>
       <x:c r="B419" s="11" t="n">
-        <x:v>178.0475997260985</x:v>
+        <x:v>178.00658301907</x:v>
       </x:c>
       <x:c r="C419" s="11" t="n">
         <x:v>180.0547756339652</x:v>
@@ -4566,7 +4566,7 @@
         <x:v>42675</x:v>
       </x:c>
       <x:c r="B420" s="11" t="n">
-        <x:v>253.3669610317908</x:v>
+        <x:v>253.3085930536358</x:v>
       </x:c>
       <x:c r="C420" s="11" t="n">
         <x:v>181.1453536304455</x:v>
@@ -4577,7 +4577,7 @@
         <x:v>42705</x:v>
       </x:c>
       <x:c r="B421" s="11" t="n">
-        <x:v>247.1167451300493</x:v>
+        <x:v>247.059817009971</x:v>
       </x:c>
       <x:c r="C421" s="11" t="n">
         <x:v>184.44475178211</x:v>
@@ -4588,7 +4588,7 @@
         <x:v>42736</x:v>
       </x:c>
       <x:c r="B422" s="11" t="n">
-        <x:v>249.2633903355735</x:v>
+        <x:v>249.2059676942682</x:v>
       </x:c>
       <x:c r="C422" s="11" t="n">
         <x:v>194.4205757141497</x:v>
@@ -4599,7 +4599,7 @@
         <x:v>42767</x:v>
       </x:c>
       <x:c r="B423" s="11" t="n">
-        <x:v>206.7026195206832</x:v>
+        <x:v>206.6550015758193</x:v>
       </x:c>
       <x:c r="C423" s="11" t="n">
         <x:v>157.7411779290858</x:v>
@@ -4610,10 +4610,10 @@
         <x:v>42795</x:v>
       </x:c>
       <x:c r="B424" s="11" t="n">
-        <x:v>139.5856792489783</x:v>
+        <x:v>139.5535229889672</x:v>
       </x:c>
       <x:c r="C424" s="11" t="n">
-        <x:v>37.09857789160879</x:v>
+        <x:v>37.09857789160882</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -4621,7 +4621,7 @@
         <x:v>42826</x:v>
       </x:c>
       <x:c r="B425" s="11" t="n">
-        <x:v>178.4466502550969</x:v>
+        <x:v>178.4055416190636</x:v>
       </x:c>
       <x:c r="C425" s="11" t="n">
         <x:v>137.1834894159752</x:v>
@@ -4632,10 +4632,10 @@
         <x:v>42856</x:v>
       </x:c>
       <x:c r="B426" s="11" t="n">
-        <x:v>166.9873054962957</x:v>
+        <x:v>166.9488367418864</x:v>
       </x:c>
       <x:c r="C426" s="11" t="n">
-        <x:v>155.7487078585311</x:v>
+        <x:v>155.748707858531</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -4643,10 +4643,10 @@
         <x:v>42887</x:v>
       </x:c>
       <x:c r="B427" s="11" t="n">
-        <x:v>192.2019128789273</x:v>
+        <x:v>192.1576354521997</x:v>
       </x:c>
       <x:c r="C427" s="11" t="n">
-        <x:v>186.4017355236471</x:v>
+        <x:v>186.401735523647</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -4654,7 +4654,7 @@
         <x:v>42917</x:v>
       </x:c>
       <x:c r="B428" s="11" t="n">
-        <x:v>122.5372289901071</x:v>
+        <x:v>122.5090001702336</x:v>
       </x:c>
       <x:c r="C428" s="11" t="n">
         <x:v>107.5363510745885</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>42948</x:v>
       </x:c>
       <x:c r="B429" s="11" t="n">
-        <x:v>151.9140405889588</x:v>
+        <x:v>151.8790442525524</x:v>
       </x:c>
       <x:c r="C429" s="11" t="n">
         <x:v>179.3700170709379</x:v>
@@ -4676,10 +4676,10 @@
         <x:v>42979</x:v>
       </x:c>
       <x:c r="B430" s="11" t="n">
-        <x:v>153.4367963426283</x:v>
+        <x:v>153.4014492099926</x:v>
       </x:c>
       <x:c r="C430" s="11" t="n">
-        <x:v>150.7567098675538</x:v>
+        <x:v>150.7567098675539</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -4687,7 +4687,7 @@
         <x:v>43009</x:v>
       </x:c>
       <x:c r="B431" s="11" t="n">
-        <x:v>166.626419068857</x:v>
+        <x:v>166.5880334516137</x:v>
       </x:c>
       <x:c r="C431" s="11" t="n">
         <x:v>154.5718603325681</x:v>
@@ -4698,10 +4698,10 @@
         <x:v>43040</x:v>
       </x:c>
       <x:c r="B432" s="11" t="n">
-        <x:v>127.0226260014272</x:v>
+        <x:v>126.99336388363</x:v>
       </x:c>
       <x:c r="C432" s="11" t="n">
-        <x:v>105.55333078557</x:v>
+        <x:v>105.5533307855701</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -4709,7 +4709,7 @@
         <x:v>43070</x:v>
       </x:c>
       <x:c r="B433" s="11" t="n">
-        <x:v>135.3109648736575</x:v>
+        <x:v>135.2797933767515</x:v>
       </x:c>
       <x:c r="C433" s="11" t="n">
         <x:v>129.9864393031961</x:v>
@@ -4720,10 +4720,10 @@
         <x:v>43101</x:v>
       </x:c>
       <x:c r="B434" s="11" t="n">
-        <x:v>118.1434638071949</x:v>
+        <x:v>118.1162471760818</x:v>
       </x:c>
       <x:c r="C434" s="11" t="n">
-        <x:v>114.4784784104427</x:v>
+        <x:v>114.4784784104428</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -4731,10 +4731,10 @@
         <x:v>43132</x:v>
       </x:c>
       <x:c r="B435" s="11" t="n">
-        <x:v>92.6252525193891</x:v>
+        <x:v>92.60391450162373</x:v>
       </x:c>
       <x:c r="C435" s="11" t="n">
-        <x:v>94.47124664558478</x:v>
+        <x:v>94.4712466455848</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -4742,10 +4742,10 @@
         <x:v>43160</x:v>
       </x:c>
       <x:c r="B436" s="11" t="n">
-        <x:v>94.02802812972541</x:v>
+        <x:v>94.0063669554765</x:v>
       </x:c>
       <x:c r="C436" s="11" t="n">
-        <x:v>81.00650623409152</x:v>
+        <x:v>81.00650623409155</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -4753,7 +4753,7 @@
         <x:v>43191</x:v>
       </x:c>
       <x:c r="B437" s="11" t="n">
-        <x:v>116.7704260650431</x:v>
+        <x:v>116.7435257397206</x:v>
       </x:c>
       <x:c r="C437" s="11" t="n">
         <x:v>116.0637715060473</x:v>
@@ -4764,10 +4764,10 @@
         <x:v>43221</x:v>
       </x:c>
       <x:c r="B438" s="11" t="n">
-        <x:v>76.99310076435842</x:v>
+        <x:v>76.97536391498707</x:v>
       </x:c>
       <x:c r="C438" s="11" t="n">
-        <x:v>25.03918518217237</x:v>
+        <x:v>25.03918518217239</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -4775,10 +4775,10 @@
         <x:v>43252</x:v>
       </x:c>
       <x:c r="B439" s="11" t="n">
-        <x:v>106.2962376914739</x:v>
+        <x:v>106.2717502979548</x:v>
       </x:c>
       <x:c r="C439" s="11" t="n">
-        <x:v>64.00023267497818</x:v>
+        <x:v>64.00023267497821</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -4786,7 +4786,7 @@
         <x:v>43282</x:v>
       </x:c>
       <x:c r="B440" s="11" t="n">
-        <x:v>129.3022904498678</x:v>
+        <x:v>129.2725031672891</x:v>
       </x:c>
       <x:c r="C440" s="11" t="n">
         <x:v>105.5594452062976</x:v>
@@ -4797,7 +4797,7 @@
         <x:v>43313</x:v>
       </x:c>
       <x:c r="B441" s="11" t="n">
-        <x:v>117.8536421337953</x:v>
+        <x:v>117.8264922687082</x:v>
       </x:c>
       <x:c r="C441" s="11" t="n">
         <x:v>98.40216773834631</x:v>
@@ -4808,10 +4808,10 @@
         <x:v>43344</x:v>
       </x:c>
       <x:c r="B442" s="11" t="n">
-        <x:v>134.5685245757694</x:v>
+        <x:v>134.5375241143407</x:v>
       </x:c>
       <x:c r="C442" s="11" t="n">
-        <x:v>106.8933912337233</x:v>
+        <x:v>106.8933912337234</x:v>
       </x:c>
     </x:row>
     <x:row r="443">
@@ -4819,10 +4819,10 @@
         <x:v>43374</x:v>
       </x:c>
       <x:c r="B443" s="11" t="n">
-        <x:v>149.8830744506894</x:v>
+        <x:v>149.8485459866004</x:v>
       </x:c>
       <x:c r="C443" s="11" t="n">
-        <x:v>94.46179666506622</x:v>
+        <x:v>94.4617966650662</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -4830,10 +4830,10 @@
         <x:v>43405</x:v>
       </x:c>
       <x:c r="B444" s="11" t="n">
-        <x:v>149.1108980066385</x:v>
+        <x:v>149.0765474283228</x:v>
       </x:c>
       <x:c r="C444" s="11" t="n">
-        <x:v>89.49566303337686</x:v>
+        <x:v>89.49566303337684</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -4841,7 +4841,7 @@
         <x:v>43435</x:v>
       </x:c>
       <x:c r="B445" s="11" t="n">
-        <x:v>202.1454080674293</x:v>
+        <x:v>202.0988399643342</x:v>
       </x:c>
       <x:c r="C445" s="11" t="n">
         <x:v>142.1696325418972</x:v>
@@ -4852,7 +4852,7 @@
         <x:v>43466</x:v>
       </x:c>
       <x:c r="B446" s="11" t="n">
-        <x:v>215.4600868063339</x:v>
+        <x:v>215.4104514095609</x:v>
       </x:c>
       <x:c r="C446" s="11" t="n">
         <x:v>159.9691602983856</x:v>
@@ -4863,7 +4863,7 @@
         <x:v>43497</x:v>
       </x:c>
       <x:c r="B447" s="11" t="n">
-        <x:v>177.1143907075439</x:v>
+        <x:v>177.0735889832557</x:v>
       </x:c>
       <x:c r="C447" s="11" t="n">
         <x:v>138.7280691873053</x:v>
@@ -4874,7 +4874,7 @@
         <x:v>43525</x:v>
       </x:c>
       <x:c r="B448" s="11" t="n">
-        <x:v>194.6804838539193</x:v>
+        <x:v>194.6356354404462</x:v>
       </x:c>
       <x:c r="C448" s="11" t="n">
         <x:v>177.2397482669232</x:v>
@@ -4885,7 +4885,7 @@
         <x:v>43556</x:v>
       </x:c>
       <x:c r="B449" s="11" t="n">
-        <x:v>155.1055617255012</x:v>
+        <x:v>155.0698301604951</x:v>
       </x:c>
       <x:c r="C449" s="11" t="n">
         <x:v>121.8631321270109</x:v>
@@ -4896,10 +4896,10 @@
         <x:v>43586</x:v>
       </x:c>
       <x:c r="B450" s="11" t="n">
-        <x:v>157.6922483092031</x:v>
+        <x:v>157.6559208509306</x:v>
       </x:c>
       <x:c r="C450" s="11" t="n">
-        <x:v>99.41492615211105</x:v>
+        <x:v>99.41492615211108</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -4907,7 +4907,7 @@
         <x:v>43617</x:v>
       </x:c>
       <x:c r="B451" s="11" t="n">
-        <x:v>184.4000091975988</x:v>
+        <x:v>184.3575290902289</x:v>
       </x:c>
       <x:c r="C451" s="11" t="n">
         <x:v>133.7688627811187</x:v>
@@ -4918,7 +4918,7 @@
         <x:v>43647</x:v>
       </x:c>
       <x:c r="B452" s="11" t="n">
-        <x:v>183.6754379682395</x:v>
+        <x:v>183.6331247798613</x:v>
       </x:c>
       <x:c r="C452" s="11" t="n">
         <x:v>141.0878443703235</x:v>
@@ -4929,10 +4929,10 @@
         <x:v>43678</x:v>
       </x:c>
       <x:c r="B453" s="11" t="n">
-        <x:v>255.0843734862317</x:v>
+        <x:v>255.0256098689129</x:v>
       </x:c>
       <x:c r="C453" s="11" t="n">
-        <x:v>207.8579839108186</x:v>
+        <x:v>207.8579839108187</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
@@ -4940,7 +4940,7 @@
         <x:v>43709</x:v>
       </x:c>
       <x:c r="B454" s="11" t="n">
-        <x:v>291.1641522612093</x:v>
+        <x:v>291.0970769692711</x:v>
       </x:c>
       <x:c r="C454" s="11" t="n">
         <x:v>277.6534020452701</x:v>
@@ -4951,10 +4951,10 @@
         <x:v>43739</x:v>
       </x:c>
       <x:c r="B455" s="11" t="n">
-        <x:v>271.2654267115101</x:v>
+        <x:v>271.202935475731</x:v>
       </x:c>
       <x:c r="C455" s="11" t="n">
-        <x:v>257.0059504855193</x:v>
+        <x:v>257.0059504855194</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -4962,10 +4962,10 @@
         <x:v>43770</x:v>
       </x:c>
       <x:c r="B456" s="11" t="n">
-        <x:v>142.4334869005268</x:v>
+        <x:v>142.4006745929628</x:v>
       </x:c>
       <x:c r="C456" s="11" t="n">
-        <x:v>71.3333647327151</x:v>
+        <x:v>71.33336473271508</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -4973,10 +4973,10 @@
         <x:v>43800</x:v>
       </x:c>
       <x:c r="B457" s="11" t="n">
-        <x:v>157.1187689560488</x:v>
+        <x:v>157.0825736098331</x:v>
       </x:c>
       <x:c r="C457" s="11" t="n">
-        <x:v>85.20324429611617</x:v>
+        <x:v>85.20324429611622</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
@@ -4984,7 +4984,7 @@
         <x:v>43831</x:v>
       </x:c>
       <x:c r="B458" s="11" t="n">
-        <x:v>189.5690099627776</x:v>
+        <x:v>189.5253390761422</x:v>
       </x:c>
       <x:c r="C458" s="11" t="n">
         <x:v>161.1583019901426</x:v>
@@ -4995,7 +4995,7 @@
         <x:v>43862</x:v>
       </x:c>
       <x:c r="B459" s="11" t="n">
-        <x:v>135.5479077375222</x:v>
+        <x:v>135.5166816562464</x:v>
       </x:c>
       <x:c r="C459" s="11" t="n">
         <x:v>70.51887951296186</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>43891</x:v>
       </x:c>
       <x:c r="B460" s="11" t="n">
-        <x:v>275.891101757443</x:v>
+        <x:v>275.8275449079827</x:v>
       </x:c>
       <x:c r="C460" s="11" t="n">
         <x:v>108.7249163570365</x:v>
@@ -5017,7 +5017,7 @@
         <x:v>43922</x:v>
       </x:c>
       <x:c r="B461" s="11" t="n">
-        <x:v>329.4356349652739</x:v>
+        <x:v>329.3597430973413</x:v>
       </x:c>
       <x:c r="C461" s="11" t="n">
         <x:v>197.1352061720077</x:v>
@@ -5028,10 +5028,10 @@
         <x:v>43952</x:v>
       </x:c>
       <x:c r="B462" s="11" t="n">
-        <x:v>366.8391230047095</x:v>
+        <x:v>366.7546145201355</x:v>
       </x:c>
       <x:c r="C462" s="11" t="n">
-        <x:v>237.2876204714393</x:v>
+        <x:v>237.2876204714395</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -5039,10 +5039,10 @@
         <x:v>43983</x:v>
       </x:c>
       <x:c r="B463" s="11" t="n">
-        <x:v>286.0198247403231</x:v>
+        <x:v>285.9539345436916</x:v>
       </x:c>
       <x:c r="C463" s="11" t="n">
-        <x:v>195.7381423365739</x:v>
+        <x:v>195.7381423365738</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -5050,10 +5050,10 @@
         <x:v>44013</x:v>
       </x:c>
       <x:c r="B464" s="11" t="n">
-        <x:v>202.9936036251235</x:v>
+        <x:v>202.9468401237824</x:v>
       </x:c>
       <x:c r="C464" s="11" t="n">
-        <x:v>76.9390127722789</x:v>
+        <x:v>76.93901277227896</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -5061,10 +5061,10 @@
         <x:v>44044</x:v>
       </x:c>
       <x:c r="B465" s="11" t="n">
-        <x:v>185.3747528188088</x:v>
+        <x:v>185.3320481603998</x:v>
       </x:c>
       <x:c r="C465" s="11" t="n">
-        <x:v>80.65860709714055</x:v>
+        <x:v>80.65860709714057</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -5072,10 +5072,10 @@
         <x:v>44075</x:v>
       </x:c>
       <x:c r="B466" s="11" t="n">
-        <x:v>179.2069828879861</x:v>
+        <x:v>179.1656990946303</x:v>
       </x:c>
       <x:c r="C466" s="11" t="n">
-        <x:v>70.43480128611631</x:v>
+        <x:v>70.43480128611628</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -5083,7 +5083,7 @@
         <x:v>44105</x:v>
       </x:c>
       <x:c r="B467" s="11" t="n">
-        <x:v>242.8512086778621</x:v>
+        <x:v>242.7952632065769</x:v>
       </x:c>
       <x:c r="C467" s="11" t="n">
         <x:v>135.5895196518088</x:v>
@@ -5094,10 +5094,10 @@
         <x:v>44136</x:v>
       </x:c>
       <x:c r="B468" s="11" t="n">
-        <x:v>172.4035389907606</x:v>
+        <x:v>172.3638225022466</x:v>
       </x:c>
       <x:c r="C468" s="11" t="n">
-        <x:v>12.13680897470802</x:v>
+        <x:v>12.13680897470806</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -5105,10 +5105,10 @@
         <x:v>44166</x:v>
       </x:c>
       <x:c r="B469" s="11" t="n">
-        <x:v>177.8973050191966</x:v>
+        <x:v>177.8563229354596</x:v>
       </x:c>
       <x:c r="C469" s="11" t="n">
-        <x:v>89.16179552174988</x:v>
+        <x:v>89.16179552174984</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -5116,10 +5116,10 @@
         <x:v>44197</x:v>
       </x:c>
       <x:c r="B470" s="11" t="n">
-        <x:v>160.7138943242811</x:v>
+        <x:v>160.6768707714275</x:v>
       </x:c>
       <x:c r="C470" s="11" t="n">
-        <x:v>63.49294682884256</x:v>
+        <x:v>63.49294682884261</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -5127,10 +5127,10 @@
         <x:v>44228</x:v>
       </x:c>
       <x:c r="B471" s="11" t="n">
-        <x:v>175.3855809794591</x:v>
+        <x:v>175.3451775199172</x:v>
       </x:c>
       <x:c r="C471" s="11" t="n">
-        <x:v>133.7251917258529</x:v>
+        <x:v>133.7251917258528</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -5138,10 +5138,10 @@
         <x:v>44256</x:v>
       </x:c>
       <x:c r="B472" s="11" t="n">
-        <x:v>112.0529370630183</x:v>
+        <x:v>112.027123502497</x:v>
       </x:c>
       <x:c r="C472" s="11" t="n">
-        <x:v>48.96100329212265</x:v>
+        <x:v>48.96100329212268</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -5149,10 +5149,10 @@
         <x:v>44287</x:v>
       </x:c>
       <x:c r="B473" s="11" t="n">
-        <x:v>110.3678206981997</x:v>
+        <x:v>110.3423953368136</x:v>
       </x:c>
       <x:c r="C473" s="11" t="n">
-        <x:v>59.80663801442104</x:v>
+        <x:v>59.80663801442103</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
@@ -5160,10 +5160,10 @@
         <x:v>44317</x:v>
       </x:c>
       <x:c r="B474" s="11" t="n">
-        <x:v>76.87307014955394</x:v>
+        <x:v>76.85536095155541</x:v>
       </x:c>
       <x:c r="C474" s="11" t="n">
-        <x:v>27.39508175339009</x:v>
+        <x:v>27.39508175339006</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -5171,7 +5171,7 @@
         <x:v>44348</x:v>
       </x:c>
       <x:c r="B475" s="11" t="n">
-        <x:v>130.5654873325857</x:v>
+        <x:v>130.5354090481819</x:v>
       </x:c>
       <x:c r="C475" s="11" t="n">
         <x:v>100.8558295630177</x:v>
@@ -5182,7 +5182,7 @@
         <x:v>44378</x:v>
       </x:c>
       <x:c r="B476" s="11" t="n">
-        <x:v>143.0221690549752</x:v>
+        <x:v>142.9892211330951</x:v>
       </x:c>
       <x:c r="C476" s="11" t="n">
         <x:v>125.0435894346694</x:v>
@@ -5193,10 +5193,10 @@
         <x:v>44409</x:v>
       </x:c>
       <x:c r="B477" s="11" t="n">
-        <x:v>111.075591775065</x:v>
+        <x:v>111.0500033649271</x:v>
       </x:c>
       <x:c r="C477" s="11" t="n">
-        <x:v>92.7058147631249</x:v>
+        <x:v>92.70581476312493</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -5204,10 +5204,10 @@
         <x:v>44440</x:v>
       </x:c>
       <x:c r="B478" s="11" t="n">
-        <x:v>129.202289793926</x:v>
+        <x:v>129.1725255484318</x:v>
       </x:c>
       <x:c r="C478" s="11" t="n">
-        <x:v>80.51156566687453</x:v>
+        <x:v>80.51156566687456</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -5215,10 +5215,10 @@
         <x:v>44470</x:v>
       </x:c>
       <x:c r="B479" s="11" t="n">
-        <x:v>92.77923088911268</x:v>
+        <x:v>92.75785739945279</x:v>
       </x:c>
       <x:c r="C479" s="11" t="n">
-        <x:v>27.69515582357782</x:v>
+        <x:v>27.69515582357776</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -5226,10 +5226,10 @@
         <x:v>44501</x:v>
       </x:c>
       <x:c r="B480" s="11" t="n">
-        <x:v>91.74485388115308</x:v>
+        <x:v>91.72371868023596</x:v>
       </x:c>
       <x:c r="C480" s="11" t="n">
-        <x:v>9.875998703844559</x:v>
+        <x:v>9.875998703844573</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -5237,10 +5237,10 @@
         <x:v>44531</x:v>
       </x:c>
       <x:c r="B481" s="11" t="n">
-        <x:v>150.9315634877466</x:v>
+        <x:v>150.896793483936</x:v>
       </x:c>
       <x:c r="C481" s="11" t="n">
-        <x:v>75.82835065468358</x:v>
+        <x:v>75.82835065468362</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -5248,10 +5248,10 @@
         <x:v>44562</x:v>
       </x:c>
       <x:c r="B482" s="11" t="n">
-        <x:v>122.6070213154469</x:v>
+        <x:v>122.5787764175619</x:v>
       </x:c>
       <x:c r="C482" s="11" t="n">
-        <x:v>71.20629020440649</x:v>
+        <x:v>71.20629020440654</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -5259,7 +5259,7 @@
         <x:v>44593</x:v>
       </x:c>
       <x:c r="B483" s="11" t="n">
-        <x:v>113.4671099825435</x:v>
+        <x:v>113.4409706399481</x:v>
       </x:c>
       <x:c r="C483" s="11" t="n">
         <x:v>55.36932562314293</x:v>
@@ -5270,10 +5270,10 @@
         <x:v>44621</x:v>
       </x:c>
       <x:c r="B484" s="11" t="n">
-        <x:v>169.5932618413923</x:v>
+        <x:v>169.5541927545544</x:v>
       </x:c>
       <x:c r="C484" s="11" t="n">
-        <x:v>33.02052983748547</x:v>
+        <x:v>33.02052983748554</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -5281,10 +5281,10 @@
         <x:v>44652</x:v>
       </x:c>
       <x:c r="B485" s="11" t="n">
-        <x:v>126.0978430146247</x:v>
+        <x:v>126.0687939384686</x:v>
       </x:c>
       <x:c r="C485" s="11" t="n">
-        <x:v>-15.49043042813082</x:v>
+        <x:v>-15.49043042813085</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -5292,10 +5292,10 @@
         <x:v>44682</x:v>
       </x:c>
       <x:c r="B486" s="11" t="n">
-        <x:v>149.3367380642025</x:v>
+        <x:v>149.3023354592631</x:v>
       </x:c>
       <x:c r="C486" s="11" t="n">
-        <x:v>36.90379864014536</x:v>
+        <x:v>36.90379864014533</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -5303,10 +5303,10 @@
         <x:v>44713</x:v>
       </x:c>
       <x:c r="B487" s="11" t="n">
-        <x:v>179.8298949148259</x:v>
+        <x:v>179.7884676216411</x:v>
       </x:c>
       <x:c r="C487" s="11" t="n">
-        <x:v>79.25537897319022</x:v>
+        <x:v>79.25537897319019</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -5314,10 +5314,10 @@
         <x:v>44743</x:v>
       </x:c>
       <x:c r="B488" s="11" t="n">
-        <x:v>190.8398230921967</x:v>
+        <x:v>190.7958594491867</x:v>
       </x:c>
       <x:c r="C488" s="11" t="n">
-        <x:v>64.37245805517469</x:v>
+        <x:v>64.37245805517475</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -5325,10 +5325,10 @@
         <x:v>44774</x:v>
       </x:c>
       <x:c r="B489" s="11" t="n">
-        <x:v>119.0542032530888</x:v>
+        <x:v>119.0267768155358</x:v>
       </x:c>
       <x:c r="C489" s="11" t="n">
-        <x:v>5.799024927160204</x:v>
+        <x:v>5.799024927160133</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -5336,10 +5336,10 @@
         <x:v>44805</x:v>
       </x:c>
       <x:c r="B490" s="11" t="n">
-        <x:v>188.6900057388202</x:v>
+        <x:v>188.6465373478027</x:v>
       </x:c>
       <x:c r="C490" s="11" t="n">
-        <x:v>86.13111051502318</x:v>
+        <x:v>86.13111051502312</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -5347,10 +5347,10 @@
         <x:v>44835</x:v>
       </x:c>
       <x:c r="B491" s="11" t="n">
-        <x:v>172.0834836270472</x:v>
+        <x:v>172.0438408694743</x:v>
       </x:c>
       <x:c r="C491" s="11" t="n">
-        <x:v>32.87466546043908</x:v>
+        <x:v>32.87466546043902</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -5358,10 +5358,10 @@
         <x:v>44866</x:v>
       </x:c>
       <x:c r="B492" s="11" t="n">
-        <x:v>168.6829223112044</x:v>
+        <x:v>168.6440629386782</x:v>
       </x:c>
       <x:c r="C492" s="11" t="n">
-        <x:v>65.75017755699068</x:v>
+        <x:v>65.75017755699061</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -5369,7 +5369,7 @@
         <x:v>44896</x:v>
       </x:c>
       <x:c r="B493" s="11" t="n">
-        <x:v>199.2818748163436</x:v>
+        <x:v>199.2359663834975</x:v>
       </x:c>
       <x:c r="C493" s="11" t="n">
         <x:v>133.5334721706034</x:v>
@@ -5380,10 +5380,10 @@
         <x:v>44927</x:v>
       </x:c>
       <x:c r="B494" s="11" t="n">
-        <x:v>144.1943496442086</x:v>
+        <x:v>144.1611316878664</x:v>
       </x:c>
       <x:c r="C494" s="11" t="n">
-        <x:v>60.93267460317638</x:v>
+        <x:v>60.93267460317634</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -5391,7 +5391,7 @@
         <x:v>44958</x:v>
       </x:c>
       <x:c r="B495" s="11" t="n">
-        <x:v>104.7382231014779</x:v>
+        <x:v>104.7140946267427</x:v>
       </x:c>
       <x:c r="C495" s="11" t="n">
         <x:v>1.298659345123639</x:v>
@@ -5402,10 +5402,10 @@
         <x:v>44986</x:v>
       </x:c>
       <x:c r="B496" s="11" t="n">
-        <x:v>134.2476947018245</x:v>
+        <x:v>134.2167681497603</x:v>
       </x:c>
       <x:c r="C496" s="11" t="n">
-        <x:v>15.62445501876896</x:v>
+        <x:v>15.62445501876897</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -5413,10 +5413,10 @@
         <x:v>45017</x:v>
       </x:c>
       <x:c r="B497" s="11" t="n">
-        <x:v>100.5423528117416</x:v>
+        <x:v>100.519190936852</x:v>
       </x:c>
       <x:c r="C497" s="11" t="n">
-        <x:v>-23.33505036003993</x:v>
+        <x:v>-23.33505036004001</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -5424,10 +5424,10 @@
         <x:v>45047</x:v>
       </x:c>
       <x:c r="B498" s="11" t="n">
-        <x:v>82.26343431013531</x:v>
+        <x:v>82.2444833375333</x:v>
       </x:c>
       <x:c r="C498" s="11" t="n">
-        <x:v>-27.70150422202937</x:v>
+        <x:v>-27.70150422202939</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -5435,10 +5435,10 @@
         <x:v>45078</x:v>
       </x:c>
       <x:c r="B499" s="11" t="n">
-        <x:v>96.12998119223907</x:v>
+        <x:v>96.10783579246234</x:v>
       </x:c>
       <x:c r="C499" s="11" t="n">
-        <x:v>12.26405768947879</x:v>
+        <x:v>12.26405768947875</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -5446,10 +5446,10 @@
         <x:v>45108</x:v>
       </x:c>
       <x:c r="B500" s="11" t="n">
-        <x:v>88.51943109136097</x:v>
+        <x:v>88.49903892894488</x:v>
       </x:c>
       <x:c r="C500" s="11" t="n">
-        <x:v>6.42402099062619</x:v>
+        <x:v>6.424020990626104</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -5457,10 +5457,10 @@
         <x:v>45139</x:v>
       </x:c>
       <x:c r="B501" s="11" t="n">
-        <x:v>118.1852147122411</x:v>
+        <x:v>118.1579884629998</x:v>
       </x:c>
       <x:c r="C501" s="11" t="n">
-        <x:v>60.7732942401179</x:v>
+        <x:v>60.77329424011792</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -5468,10 +5468,10 @@
         <x:v>45170</x:v>
       </x:c>
       <x:c r="B502" s="11" t="n">
-        <x:v>95.88393518698281</x:v>
+        <x:v>95.86184646866052</x:v>
       </x:c>
       <x:c r="C502" s="11" t="n">
-        <x:v>25.88405597291776</x:v>
+        <x:v>25.88405597291775</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -5479,7 +5479,7 @@
         <x:v>45200</x:v>
       </x:c>
       <x:c r="B503" s="11" t="n">
-        <x:v>125.7654635196491</x:v>
+        <x:v>125.7364910135359</x:v>
       </x:c>
       <x:c r="C503" s="11" t="n">
         <x:v>16.91634273269275</x:v>
@@ -5490,10 +5490,10 @@
         <x:v>45231</x:v>
       </x:c>
       <x:c r="B504" s="11" t="n">
-        <x:v>114.9649528946699</x:v>
+        <x:v>114.9384684949999</x:v>
       </x:c>
       <x:c r="C504" s="11" t="n">
-        <x:v>-4.175556651759379</x:v>
+        <x:v>-4.175556651759365</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -5501,10 +5501,10 @@
         <x:v>45261</x:v>
       </x:c>
       <x:c r="B505" s="11" t="n">
-        <x:v>114.2542346613696</x:v>
+        <x:v>114.2279139893859</x:v>
       </x:c>
       <x:c r="C505" s="11" t="n">
-        <x:v>22.54057176843281</x:v>
+        <x:v>22.54057176843276</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
@@ -5512,10 +5512,10 @@
         <x:v>45292</x:v>
       </x:c>
       <x:c r="B506" s="11" t="n">
-        <x:v>100.7864370184462</x:v>
+        <x:v>100.7632189140404</x:v>
       </x:c>
       <x:c r="C506" s="11" t="n">
-        <x:v>20.58679883400555</x:v>
+        <x:v>20.58679883400551</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -5523,10 +5523,10 @@
         <x:v>45323</x:v>
       </x:c>
       <x:c r="B507" s="11" t="n">
-        <x:v>127.9371746744169</x:v>
+        <x:v>127.9077018726507</x:v>
       </x:c>
       <x:c r="C507" s="11" t="n">
-        <x:v>69.86626347342067</x:v>
+        <x:v>69.8662634734207</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -5534,7 +5534,7 @@
         <x:v>45352</x:v>
       </x:c>
       <x:c r="B508" s="11" t="n">
-        <x:v>128.6570951647557</x:v>
+        <x:v>128.6274565153854</x:v>
       </x:c>
       <x:c r="C508" s="11" t="n">
         <x:v>100.4394277241171</x:v>
@@ -5545,10 +5545,10 @@
         <x:v>45383</x:v>
       </x:c>
       <x:c r="B509" s="11" t="n">
-        <x:v>86.44583692212034</x:v>
+        <x:v>86.42592245221269</x:v>
       </x:c>
       <x:c r="C509" s="11" t="n">
-        <x:v>27.94600357280574</x:v>
+        <x:v>27.94600357280571</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -5556,10 +5556,10 @@
         <x:v>45413</x:v>
       </x:c>
       <x:c r="B510" s="11" t="n">
-        <x:v>101.0932139168384</x:v>
+        <x:v>101.0699251404427</x:v>
       </x:c>
       <x:c r="C510" s="11" t="n">
-        <x:v>36.72145133245466</x:v>
+        <x:v>36.72145133245461</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -5567,10 +5567,10 @@
         <x:v>45444</x:v>
       </x:c>
       <x:c r="B511" s="11" t="n">
-        <x:v>142.3717873177239</x:v>
+        <x:v>142.3389892238517</x:v>
       </x:c>
       <x:c r="C511" s="11" t="n">
-        <x:v>77.50952405642816</x:v>
+        <x:v>77.50952405642819</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -5578,10 +5578,10 @@
         <x:v>45474</x:v>
       </x:c>
       <x:c r="B512" s="11" t="n">
-        <x:v>102.6372153160737</x:v>
+        <x:v>102.6135708491035</x:v>
       </x:c>
       <x:c r="C512" s="11" t="n">
-        <x:v>15.58240766491157</x:v>
+        <x:v>15.58240766491153</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -5589,10 +5589,10 @@
         <x:v>45505</x:v>
       </x:c>
       <x:c r="B513" s="11" t="n">
-        <x:v>80.18897277318052</x:v>
+        <x:v>80.17049969290188</x:v>
       </x:c>
       <x:c r="C513" s="11" t="n">
-        <x:v>-12.23212121897109</x:v>
+        <x:v>-12.23212121897107</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -5600,10 +5600,10 @@
         <x:v>45536</x:v>
       </x:c>
       <x:c r="B514" s="11" t="n">
-        <x:v>101.3674765698955</x:v>
+        <x:v>101.344124611795</x:v>
       </x:c>
       <x:c r="C514" s="11" t="n">
-        <x:v>6.08756423583425</x:v>
+        <x:v>6.087564235834165</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -5611,7 +5611,7 @@
         <x:v>45566</x:v>
       </x:c>
       <x:c r="B515" s="11" t="n">
-        <x:v>99.84821510320693</x:v>
+        <x:v>99.82521313635922</x:v>
       </x:c>
       <x:c r="C515" s="11" t="n">
         <x:v>3.96670508906152</x:v>
@@ -5622,10 +5622,10 @@
         <x:v>45597</x:v>
       </x:c>
       <x:c r="B516" s="11" t="n">
-        <x:v>194.8276768362888</x:v>
+        <x:v>194.7827945140663</x:v>
       </x:c>
       <x:c r="C516" s="11" t="n">
-        <x:v>27.47645152944759</x:v>
+        <x:v>27.47645152944756</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -5633,10 +5633,10 @@
         <x:v>45627</x:v>
       </x:c>
       <x:c r="B517" s="11" t="n">
-        <x:v>254.7595310619064</x:v>
+        <x:v>254.7008422783206</x:v>
       </x:c>
       <x:c r="C517" s="11" t="n">
-        <x:v>83.15839485715834</x:v>
+        <x:v>83.15839485715833</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -5644,10 +5644,10 @@
         <x:v>45658</x:v>
       </x:c>
       <x:c r="B518" s="11" t="n">
-        <x:v>222.2562383146016</x:v>
+        <x:v>222.2050372929296</x:v>
       </x:c>
       <x:c r="C518" s="11" t="n">
-        <x:v>40.78309561066057</x:v>
+        <x:v>40.78309561066064</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -5655,10 +5655,10 @@
         <x:v>45689</x:v>
       </x:c>
       <x:c r="B519" s="11" t="n">
-        <x:v>248.1611946022811</x:v>
+        <x:v>248.1040258730732</x:v>
       </x:c>
       <x:c r="C519" s="11" t="n">
-        <x:v>56.36655941184215</x:v>
+        <x:v>56.36655941184208</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -5666,10 +5666,10 @@
         <x:v>45717</x:v>
       </x:c>
       <x:c r="B520" s="11" t="n">
-        <x:v>346.5596748807886</x:v>
+        <x:v>346.4798381591796</x:v>
       </x:c>
       <x:c r="C520" s="11" t="n">
-        <x:v>41.72731147633383</x:v>
+        <x:v>41.72731147633386</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -5677,7 +5677,7 @@
         <x:v>45748</x:v>
       </x:c>
       <x:c r="B521" s="11" t="n">
-        <x:v>571.1831141354954</x:v>
+        <x:v>571.0515310617096</x:v>
       </x:c>
       <x:c r="C521" s="11" t="n">
         <x:v>259.5692369442042</x:v>
@@ -5688,10 +5688,10 @@
         <x:v>45778</x:v>
       </x:c>
       <x:c r="B522" s="11" t="n">
-        <x:v>337.9282601083809</x:v>
+        <x:v>337.8504118000473</x:v>
       </x:c>
       <x:c r="C522" s="11" t="n">
-        <x:v>50.08144026201203</x:v>
+        <x:v>50.08144026201184</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -5699,7 +5699,7 @@
         <x:v>45809</x:v>
       </x:c>
       <x:c r="B523" s="11" t="n">
-        <x:v>388.6016834494379</x:v>
+        <x:v>388.5121615383009</x:v>
       </x:c>
       <x:c r="C523" s="11" t="n">
         <x:v>234.0307591737169</x:v>
@@ -5710,10 +5710,10 @@
         <x:v>45839</x:v>
       </x:c>
       <x:c r="B524" s="11" t="n">
-        <x:v>463.9812339787034</x:v>
+        <x:v>463.8743469306885</x:v>
       </x:c>
       <x:c r="C524" s="11" t="n">
-        <x:v>289.7451774586032</x:v>
+        <x:v>289.7451774586031</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -5721,10 +5721,10 @@
         <x:v>45870</x:v>
       </x:c>
       <x:c r="B525" s="11" t="n">
-        <x:v>240.4379141805885</x:v>
+        <x:v>240.3825246583502</x:v>
       </x:c>
       <x:c r="C525" s="11" t="n">
-        <x:v>73.69525247655815</x:v>
+        <x:v>73.69525247655807</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -5732,10 +5732,10 @@
         <x:v>45901</x:v>
       </x:c>
       <x:c r="B526" s="11" t="n">
-        <x:v>242.853090581599</x:v>
+        <x:v>242.7971446767809</x:v>
       </x:c>
       <x:c r="C526" s="11" t="n">
-        <x:v>88.32914428838544</x:v>
+        <x:v>88.32914428838535</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -5743,7 +5743,7 @@
         <x:v>45931</x:v>
       </x:c>
       <x:c r="B527" s="11" t="n">
-        <x:v>294.3615149575781</x:v>
+        <x:v>294.2937030913239</x:v>
       </x:c>
       <x:c r="C527" s="11" t="n">
         <x:v>115.7487507898298</x:v>
@@ -5754,10 +5754,10 @@
         <x:v>45962</x:v>
       </x:c>
       <x:c r="B528" s="11" t="n">
-        <x:v>208.5595224856445</x:v>
+        <x:v>208.5114767672806</x:v>
       </x:c>
       <x:c r="C528" s="11" t="n">
-        <x:v>25.68388422758527</x:v>
+        <x:v>25.68388422758517</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -5765,10 +5765,10 @@
         <x:v>45992</x:v>
       </x:c>
       <x:c r="B529" s="11" t="n">
-        <x:v>263.8704227659849</x:v>
+        <x:v>263.809635112342</x:v>
       </x:c>
       <x:c r="C529" s="11" t="n">
-        <x:v>147.6353739934369</x:v>
+        <x:v>147.6353739934368</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -5776,10 +5776,10 @@
         <x:v>46023</x:v>
       </x:c>
       <x:c r="B530" s="11" t="n">
-        <x:v>253.2996665389179</x:v>
+        <x:v>253.2413140633504</x:v>
       </x:c>
       <x:c r="C530" s="11" t="n">
-        <x:v>61.83750548698301</x:v>
+        <x:v>61.83750548698288</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -5787,10 +5787,10 @@
         <x:v>46054</x:v>
       </x:c>
       <x:c r="B531" s="11" t="n">
-        <x:v>202.115831700926</x:v>
+        <x:v>202.0692704113188</x:v>
       </x:c>
       <x:c r="C531" s="11" t="n">
-        <x:v>21.87961834992564</x:v>
+        <x:v>21.87961834992551</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -5798,10 +5798,10 @@
         <x:v>46082</x:v>
       </x:c>
       <x:c r="B532" s="11" t="n">
-        <x:v>279.7020928538815</x:v>
+        <x:v>279.6376580689392</x:v>
       </x:c>
       <x:c r="C532" s="11" t="n">
-        <x:v>60.98282630318916</x:v>
+        <x:v>60.98282630318931</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -5809,7 +5809,7 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="B533" s="11" t="n">
-        <x:v>294.0804168546064</x:v>
+        <x:v>294.0126697447351</x:v>
       </x:c>
       <x:c r="C533" s="11" t="n">
         <x:v>108.93288840874</x:v>
@@ -5820,10 +5820,10 @@
         <x:v>46143</x:v>
       </x:c>
       <x:c r="B534" s="11" t="n">
-        <x:v>209.6797795363376</x:v>
+        <x:v>209.6314757451026</x:v>
       </x:c>
       <x:c r="C534" s="11" t="n">
-        <x:v>19.29625447194425</x:v>
+        <x:v>19.29625447194415</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -5831,10 +5831,10 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B535" s="11" t="n">
-        <x:v>189.7060513114415</x:v>
+        <x:v>189.6623488546819</x:v>
       </x:c>
       <x:c r="C535" s="11" t="n">
-        <x:v>27.54781087730788</x:v>
+        <x:v>27.54781087730775</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -5842,10 +5842,10 @@
         <x:v>46204</x:v>
       </x:c>
       <x:c r="B536" s="11" t="n">
-        <x:v>151.5301873337048</x:v>
+        <x:v>151.4952794253173</x:v>
       </x:c>
       <x:c r="C536" s="11" t="n">
-        <x:v>24.61251930021194</x:v>
+        <x:v>24.61251930021189</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -5853,7 +5853,7 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B537" s="13" t="n">
-        <x:v>90.70585639739723</x:v>
+        <x:v>103.0327568699062</x:v>
       </x:c>
       <x:c r="C537" s="13"/>
     </x:row>
